--- a/3.Study status-2026.xlsx
+++ b/3.Study status-2026.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="369">
   <si>
     <t>hours studied</t>
   </si>
@@ -1095,9 +1095,6 @@
     <t>hospital-semn androgen, hair cut-1,hosp-1</t>
   </si>
   <si>
-    <t>house related shopping- veg buy, millet shop buy</t>
-  </si>
-  <si>
     <t>kitchen , house work-, bathroom cleaning</t>
   </si>
   <si>
@@ -1107,9 +1104,6 @@
     <t xml:space="preserve">use unhook chrome exetnsion -- to hide recommendations,home page videos  in youtube </t>
   </si>
   <si>
-    <t>movies (prev march month saw 6 movies) -bhartha mahasayulaku</t>
-  </si>
-  <si>
     <t>aws 96-103, spr 20-22</t>
   </si>
   <si>
@@ -1122,13 +1116,88 @@
     <t>r-3.5,aws 104-112</t>
   </si>
   <si>
-    <t>hosp related- claims 1.5</t>
-  </si>
-  <si>
     <t>personal shoping-chari 0.5</t>
   </si>
   <si>
     <t>1.5- submit medibudy claim amounts, 0.5- chair shopping</t>
+  </si>
+  <si>
+    <t>house related shopping- veg buy1, millet shop buy</t>
+  </si>
+  <si>
+    <t>tcs interviews</t>
+  </si>
+  <si>
+    <t>9-230</t>
+  </si>
+  <si>
+    <t>tcs interview,5- interview</t>
+  </si>
+  <si>
+    <t>11-3 charan institution visit -10k coders</t>
+  </si>
+  <si>
+    <t>11-3 charan institution visit -code gnan,1-anj call ,1-financial</t>
+  </si>
+  <si>
+    <t>0.5- house shopping</t>
+  </si>
+  <si>
+    <t>aws 123-127</t>
+  </si>
+  <si>
+    <t>1-house work, water,1- sailu calls</t>
+  </si>
+  <si>
+    <t>react-4th video</t>
+  </si>
+  <si>
+    <t>charan institution  visit, sailu cab</t>
+  </si>
+  <si>
+    <t>aws 116-118</t>
+  </si>
+  <si>
+    <t>fnds meet-aswin</t>
+  </si>
+  <si>
+    <t>1-aswin meet,1- kitchen help</t>
+  </si>
+  <si>
+    <t>aws 136-137</t>
+  </si>
+  <si>
+    <t>movies (prev march month saw 6 movies) -bhartha mahasayulaku,LIK, sabdam</t>
+  </si>
+  <si>
+    <t>2.5- sabdam movie,1- groc shopping, dmart,3.5- BCB sleep, 1.5 kitchne help, 1.5- podium mall</t>
+  </si>
+  <si>
+    <t>time pass, went to podium mall</t>
+  </si>
+  <si>
+    <t>aws 133-135</t>
+  </si>
+  <si>
+    <t>0.75 - hosp blood booking,3-insurance docs</t>
+  </si>
+  <si>
+    <t>read insurance docs</t>
+  </si>
+  <si>
+    <t>react-7</t>
+  </si>
+  <si>
+    <t>1- listening songs ,1-BCB,0.5- hosp research</t>
+  </si>
+  <si>
+    <t>hosp related- claims 1.5, SMA test research -0.5</t>
+  </si>
+  <si>
+    <t>2-hosp santu blood, my-androcare</t>
+  </si>
+  <si>
+    <t>aws 139- 141</t>
   </si>
 </sst>
 </file>
@@ -3026,38 +3095,49 @@
     <xf numFmtId="0" fontId="7" fillId="37" borderId="0" xfId="27" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="34" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="11" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="9" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="36" borderId="0" xfId="26" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="3" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3098,46 +3178,35 @@
     <xf numFmtId="0" fontId="29" fillId="11" borderId="16" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="11" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="4" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="9" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="36" borderId="0" xfId="26" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4953,11 +5022,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1301357760"/>
-        <c:axId val="1301352864"/>
+        <c:axId val="1678494480"/>
+        <c:axId val="1678487952"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1301357760"/>
+        <c:axId val="1678494480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4997,14 +5066,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301352864"/>
+        <c:crossAx val="1678487952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1301352864"/>
+        <c:axId val="1678487952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5052,7 +5121,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301357760"/>
+        <c:crossAx val="1678494480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5346,11 +5415,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1274642512"/>
-        <c:axId val="1274627824"/>
+        <c:axId val="1785978272"/>
+        <c:axId val="1785982080"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1274642512"/>
+        <c:axId val="1785978272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5390,14 +5459,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274627824"/>
+        <c:crossAx val="1785982080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1274627824"/>
+        <c:axId val="1785982080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5445,7 +5514,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274642512"/>
+        <c:crossAx val="1785978272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5736,11 +5805,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1274637616"/>
-        <c:axId val="1274632176"/>
+        <c:axId val="1785983168"/>
+        <c:axId val="1785993504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1274637616"/>
+        <c:axId val="1785983168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5780,14 +5849,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274632176"/>
+        <c:crossAx val="1785993504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1274632176"/>
+        <c:axId val="1785993504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5835,7 +5904,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274637616"/>
+        <c:crossAx val="1785983168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6132,11 +6201,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1274639792"/>
-        <c:axId val="1274630000"/>
+        <c:axId val="1785985888"/>
+        <c:axId val="1785988608"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1274639792"/>
+        <c:axId val="1785985888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6176,14 +6245,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274630000"/>
+        <c:crossAx val="1785988608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1274630000"/>
+        <c:axId val="1785988608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6231,7 +6300,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274639792"/>
+        <c:crossAx val="1785985888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6561,11 +6630,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1301361568"/>
-        <c:axId val="1301359936"/>
+        <c:axId val="1678495024"/>
+        <c:axId val="1678492848"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1301361568"/>
+        <c:axId val="1678495024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6605,14 +6674,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301359936"/>
+        <c:crossAx val="1678492848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1301359936"/>
+        <c:axId val="1678492848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6660,7 +6729,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301361568"/>
+        <c:crossAx val="1678495024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7008,11 +7077,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1301347424"/>
-        <c:axId val="1301353952"/>
+        <c:axId val="1678497200"/>
+        <c:axId val="1678490672"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1301347424"/>
+        <c:axId val="1678497200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7052,14 +7121,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301353952"/>
+        <c:crossAx val="1678490672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1301353952"/>
+        <c:axId val="1678490672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7107,7 +7176,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301347424"/>
+        <c:crossAx val="1678497200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7389,6 +7458,30 @@
                 <c:pt idx="5">
                   <c:v>2</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7404,11 +7497,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1301356128"/>
-        <c:axId val="1301362112"/>
+        <c:axId val="1678498832"/>
+        <c:axId val="1678498288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1301356128"/>
+        <c:axId val="1678498832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7448,14 +7541,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301362112"/>
+        <c:crossAx val="1678498288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1301362112"/>
+        <c:axId val="1678498288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7503,7 +7596,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301356128"/>
+        <c:crossAx val="1678498832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7788,11 +7881,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1301349056"/>
-        <c:axId val="1301349600"/>
+        <c:axId val="1678491760"/>
+        <c:axId val="1678499376"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1301349056"/>
+        <c:axId val="1678491760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7832,14 +7925,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301349600"/>
+        <c:crossAx val="1678499376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1301349600"/>
+        <c:axId val="1678499376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7887,7 +7980,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1301349056"/>
+        <c:crossAx val="1678491760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8169,11 +8262,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1274639248"/>
-        <c:axId val="1274627280"/>
+        <c:axId val="1678493936"/>
+        <c:axId val="1557304512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1274639248"/>
+        <c:axId val="1678493936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8213,14 +8306,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274627280"/>
+        <c:crossAx val="1557304512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1274627280"/>
+        <c:axId val="1557304512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8268,7 +8361,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274639248"/>
+        <c:crossAx val="1678493936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8562,11 +8655,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1274636528"/>
-        <c:axId val="1274640880"/>
+        <c:axId val="1785980992"/>
+        <c:axId val="1785983712"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1274636528"/>
+        <c:axId val="1785980992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8606,14 +8699,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274640880"/>
+        <c:crossAx val="1785983712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1274640880"/>
+        <c:axId val="1785983712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8661,7 +8754,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274636528"/>
+        <c:crossAx val="1785980992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8955,11 +9048,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1274631632"/>
-        <c:axId val="1274633808"/>
+        <c:axId val="1785990240"/>
+        <c:axId val="1785981536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1274631632"/>
+        <c:axId val="1785990240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8999,14 +9092,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274633808"/>
+        <c:crossAx val="1785981536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1274633808"/>
+        <c:axId val="1785981536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9054,7 +9147,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274631632"/>
+        <c:crossAx val="1785990240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9345,11 +9438,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1274641424"/>
-        <c:axId val="1274632720"/>
+        <c:axId val="1785987520"/>
+        <c:axId val="1785985344"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1274641424"/>
+        <c:axId val="1785987520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9389,14 +9482,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274632720"/>
+        <c:crossAx val="1785985344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1274632720"/>
+        <c:axId val="1785985344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9444,7 +9537,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1274641424"/>
+        <c:crossAx val="1785987520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16448,982 +16541,1024 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:21" ht="16.5">
-      <c r="B1" s="343" t="s">
+      <c r="B1" s="350" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="343"/>
-      <c r="D1" s="343"/>
-      <c r="E1" s="343"/>
-      <c r="F1" s="343"/>
-      <c r="G1" s="343"/>
-      <c r="H1" s="343"/>
-      <c r="I1" s="343"/>
-      <c r="J1" s="343"/>
-      <c r="L1" s="348" t="s">
+      <c r="C1" s="350"/>
+      <c r="D1" s="350"/>
+      <c r="E1" s="350"/>
+      <c r="F1" s="350"/>
+      <c r="G1" s="350"/>
+      <c r="H1" s="350"/>
+      <c r="I1" s="350"/>
+      <c r="J1" s="350"/>
+      <c r="L1" s="372" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="348"/>
-      <c r="N1" s="348"/>
-      <c r="O1" s="348"/>
-      <c r="P1" s="348"/>
-      <c r="Q1" s="348"/>
-      <c r="R1" s="348"/>
-      <c r="S1" s="348"/>
-      <c r="T1" s="348"/>
-      <c r="U1" s="348"/>
+      <c r="M1" s="372"/>
+      <c r="N1" s="372"/>
+      <c r="O1" s="372"/>
+      <c r="P1" s="372"/>
+      <c r="Q1" s="372"/>
+      <c r="R1" s="372"/>
+      <c r="S1" s="372"/>
+      <c r="T1" s="372"/>
+      <c r="U1" s="372"/>
     </row>
     <row r="2" spans="2:21" ht="16.5">
-      <c r="B2" s="371" t="s">
+      <c r="B2" s="343" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
-      <c r="F2" s="371"/>
-      <c r="G2" s="371"/>
-      <c r="H2" s="371"/>
-      <c r="I2" s="371"/>
-      <c r="J2" s="371"/>
-      <c r="L2" s="351" t="s">
+      <c r="C2" s="343"/>
+      <c r="D2" s="343"/>
+      <c r="E2" s="343"/>
+      <c r="F2" s="343"/>
+      <c r="G2" s="343"/>
+      <c r="H2" s="343"/>
+      <c r="I2" s="343"/>
+      <c r="J2" s="343"/>
+      <c r="L2" s="375" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="352"/>
-      <c r="N2" s="352"/>
-      <c r="O2" s="352"/>
-      <c r="P2" s="352"/>
-      <c r="Q2" s="352"/>
-      <c r="R2" s="352"/>
-      <c r="S2" s="352"/>
-      <c r="T2" s="352"/>
-      <c r="U2" s="352"/>
+      <c r="M2" s="376"/>
+      <c r="N2" s="376"/>
+      <c r="O2" s="376"/>
+      <c r="P2" s="376"/>
+      <c r="Q2" s="376"/>
+      <c r="R2" s="376"/>
+      <c r="S2" s="376"/>
+      <c r="T2" s="376"/>
+      <c r="U2" s="376"/>
     </row>
     <row r="3" spans="2:21">
-      <c r="B3" s="378" t="s">
+      <c r="B3" s="352" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="378"/>
-      <c r="D3" s="378"/>
-      <c r="E3" s="378"/>
-      <c r="F3" s="378"/>
-      <c r="G3" s="378"/>
-      <c r="H3" s="378"/>
-      <c r="I3" s="378"/>
-      <c r="J3" s="378"/>
+      <c r="C3" s="352"/>
+      <c r="D3" s="352"/>
+      <c r="E3" s="352"/>
+      <c r="F3" s="352"/>
+      <c r="G3" s="352"/>
+      <c r="H3" s="352"/>
+      <c r="I3" s="352"/>
+      <c r="J3" s="352"/>
       <c r="K3" s="75"/>
-      <c r="L3" s="353" t="s">
+      <c r="L3" s="377" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="353"/>
-      <c r="N3" s="353"/>
-      <c r="O3" s="353"/>
-      <c r="P3" s="353"/>
-      <c r="Q3" s="353"/>
-      <c r="R3" s="353"/>
-      <c r="S3" s="353"/>
-      <c r="T3" s="353"/>
-      <c r="U3" s="353"/>
+      <c r="M3" s="377"/>
+      <c r="N3" s="377"/>
+      <c r="O3" s="377"/>
+      <c r="P3" s="377"/>
+      <c r="Q3" s="377"/>
+      <c r="R3" s="377"/>
+      <c r="S3" s="377"/>
+      <c r="T3" s="377"/>
+      <c r="U3" s="377"/>
     </row>
     <row r="4" spans="2:21" ht="15" customHeight="1">
-      <c r="B4" s="372" t="s">
+      <c r="B4" s="344" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="372"/>
-      <c r="D4" s="372"/>
-      <c r="E4" s="372"/>
-      <c r="F4" s="372"/>
-      <c r="G4" s="372"/>
-      <c r="H4" s="372"/>
-      <c r="I4" s="372"/>
-      <c r="J4" s="372"/>
+      <c r="C4" s="344"/>
+      <c r="D4" s="344"/>
+      <c r="E4" s="344"/>
+      <c r="F4" s="344"/>
+      <c r="G4" s="344"/>
+      <c r="H4" s="344"/>
+      <c r="I4" s="344"/>
+      <c r="J4" s="344"/>
       <c r="K4" s="75"/>
-      <c r="L4" s="353"/>
-      <c r="M4" s="353"/>
-      <c r="N4" s="353"/>
-      <c r="O4" s="353"/>
-      <c r="P4" s="353"/>
-      <c r="Q4" s="353"/>
-      <c r="R4" s="353"/>
-      <c r="S4" s="353"/>
-      <c r="T4" s="353"/>
-      <c r="U4" s="353"/>
+      <c r="L4" s="377"/>
+      <c r="M4" s="377"/>
+      <c r="N4" s="377"/>
+      <c r="O4" s="377"/>
+      <c r="P4" s="377"/>
+      <c r="Q4" s="377"/>
+      <c r="R4" s="377"/>
+      <c r="S4" s="377"/>
+      <c r="T4" s="377"/>
+      <c r="U4" s="377"/>
     </row>
     <row r="5" spans="2:21" ht="15" customHeight="1">
-      <c r="B5" s="372"/>
-      <c r="C5" s="372"/>
-      <c r="D5" s="372"/>
-      <c r="E5" s="372"/>
-      <c r="F5" s="372"/>
-      <c r="G5" s="372"/>
-      <c r="H5" s="372"/>
-      <c r="I5" s="372"/>
-      <c r="J5" s="372"/>
+      <c r="B5" s="344"/>
+      <c r="C5" s="344"/>
+      <c r="D5" s="344"/>
+      <c r="E5" s="344"/>
+      <c r="F5" s="344"/>
+      <c r="G5" s="344"/>
+      <c r="H5" s="344"/>
+      <c r="I5" s="344"/>
+      <c r="J5" s="344"/>
       <c r="K5" s="75"/>
-      <c r="L5" s="343" t="s">
+      <c r="L5" s="350" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="343"/>
-      <c r="N5" s="343"/>
-      <c r="O5" s="343"/>
-      <c r="P5" s="343"/>
-      <c r="Q5" s="343"/>
-      <c r="R5" s="343"/>
-      <c r="S5" s="343"/>
-      <c r="T5" s="343"/>
-      <c r="U5" s="343"/>
+      <c r="M5" s="350"/>
+      <c r="N5" s="350"/>
+      <c r="O5" s="350"/>
+      <c r="P5" s="350"/>
+      <c r="Q5" s="350"/>
+      <c r="R5" s="350"/>
+      <c r="S5" s="350"/>
+      <c r="T5" s="350"/>
+      <c r="U5" s="350"/>
     </row>
     <row r="6" spans="2:21" ht="35.25" customHeight="1">
-      <c r="B6" s="372"/>
-      <c r="C6" s="372"/>
-      <c r="D6" s="372"/>
-      <c r="E6" s="372"/>
-      <c r="F6" s="372"/>
-      <c r="G6" s="372"/>
-      <c r="H6" s="372"/>
-      <c r="I6" s="372"/>
-      <c r="J6" s="372"/>
+      <c r="B6" s="344"/>
+      <c r="C6" s="344"/>
+      <c r="D6" s="344"/>
+      <c r="E6" s="344"/>
+      <c r="F6" s="344"/>
+      <c r="G6" s="344"/>
+      <c r="H6" s="344"/>
+      <c r="I6" s="344"/>
+      <c r="J6" s="344"/>
       <c r="K6" s="75"/>
-      <c r="L6" s="349" t="s">
+      <c r="L6" s="373" t="s">
         <v>167</v>
       </c>
-      <c r="M6" s="349"/>
-      <c r="N6" s="349"/>
-      <c r="O6" s="349"/>
-      <c r="P6" s="349"/>
-      <c r="Q6" s="349"/>
-      <c r="R6" s="349"/>
-      <c r="S6" s="349"/>
-      <c r="T6" s="349"/>
-      <c r="U6" s="349"/>
+      <c r="M6" s="373"/>
+      <c r="N6" s="373"/>
+      <c r="O6" s="373"/>
+      <c r="P6" s="373"/>
+      <c r="Q6" s="373"/>
+      <c r="R6" s="373"/>
+      <c r="S6" s="373"/>
+      <c r="T6" s="373"/>
+      <c r="U6" s="373"/>
     </row>
     <row r="7" spans="2:21" ht="15.75" thickBot="1">
-      <c r="B7" s="346" t="s">
+      <c r="B7" s="380" t="s">
         <v>159</v>
       </c>
-      <c r="C7" s="346"/>
-      <c r="D7" s="346"/>
-      <c r="E7" s="346"/>
-      <c r="F7" s="346"/>
-      <c r="G7" s="346"/>
-      <c r="H7" s="346"/>
-      <c r="I7" s="346"/>
-      <c r="J7" s="346"/>
-      <c r="K7" s="346"/>
-      <c r="L7" s="343"/>
-      <c r="M7" s="343"/>
-      <c r="N7" s="343"/>
-      <c r="O7" s="343"/>
-      <c r="P7" s="343"/>
-      <c r="Q7" s="343"/>
-      <c r="R7" s="343"/>
-      <c r="S7" s="343"/>
-      <c r="T7" s="343"/>
-      <c r="U7" s="343"/>
+      <c r="C7" s="380"/>
+      <c r="D7" s="380"/>
+      <c r="E7" s="380"/>
+      <c r="F7" s="380"/>
+      <c r="G7" s="380"/>
+      <c r="H7" s="380"/>
+      <c r="I7" s="380"/>
+      <c r="J7" s="380"/>
+      <c r="K7" s="380"/>
+      <c r="L7" s="350"/>
+      <c r="M7" s="350"/>
+      <c r="N7" s="350"/>
+      <c r="O7" s="350"/>
+      <c r="P7" s="350"/>
+      <c r="Q7" s="350"/>
+      <c r="R7" s="350"/>
+      <c r="S7" s="350"/>
+      <c r="T7" s="350"/>
+      <c r="U7" s="350"/>
     </row>
     <row r="8" spans="2:21" ht="88.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B8" s="373" t="s">
+      <c r="B8" s="345" t="s">
         <v>309</v>
       </c>
-      <c r="C8" s="373"/>
-      <c r="D8" s="373"/>
-      <c r="E8" s="373"/>
-      <c r="F8" s="373"/>
-      <c r="G8" s="373"/>
-      <c r="H8" s="373"/>
-      <c r="I8" s="373"/>
-      <c r="J8" s="373"/>
-      <c r="L8" s="350" t="s">
+      <c r="C8" s="345"/>
+      <c r="D8" s="345"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
+      <c r="G8" s="345"/>
+      <c r="H8" s="345"/>
+      <c r="I8" s="345"/>
+      <c r="J8" s="345"/>
+      <c r="L8" s="374" t="s">
         <v>146</v>
       </c>
-      <c r="M8" s="350"/>
-      <c r="N8" s="350"/>
-      <c r="O8" s="350"/>
-      <c r="P8" s="350"/>
-      <c r="Q8" s="350"/>
-      <c r="R8" s="350"/>
-      <c r="S8" s="350"/>
-      <c r="T8" s="350"/>
-      <c r="U8" s="350"/>
+      <c r="M8" s="374"/>
+      <c r="N8" s="374"/>
+      <c r="O8" s="374"/>
+      <c r="P8" s="374"/>
+      <c r="Q8" s="374"/>
+      <c r="R8" s="374"/>
+      <c r="S8" s="374"/>
+      <c r="T8" s="374"/>
+      <c r="U8" s="374"/>
     </row>
     <row r="9" spans="2:21" ht="15.75" thickTop="1">
-      <c r="B9" s="374" t="s">
+      <c r="B9" s="346" t="s">
         <v>203</v>
       </c>
-      <c r="C9" s="374"/>
-      <c r="D9" s="374"/>
-      <c r="E9" s="374"/>
-      <c r="F9" s="374"/>
-      <c r="G9" s="374"/>
-      <c r="H9" s="374"/>
-      <c r="I9" s="374"/>
-      <c r="J9" s="374"/>
-      <c r="L9" s="343"/>
-      <c r="M9" s="343"/>
-      <c r="N9" s="343"/>
-      <c r="O9" s="343"/>
-      <c r="P9" s="343"/>
-      <c r="Q9" s="343"/>
-      <c r="R9" s="343"/>
-      <c r="S9" s="343"/>
-      <c r="T9" s="343"/>
-      <c r="U9" s="343"/>
+      <c r="C9" s="346"/>
+      <c r="D9" s="346"/>
+      <c r="E9" s="346"/>
+      <c r="F9" s="346"/>
+      <c r="G9" s="346"/>
+      <c r="H9" s="346"/>
+      <c r="I9" s="346"/>
+      <c r="J9" s="346"/>
+      <c r="L9" s="350"/>
+      <c r="M9" s="350"/>
+      <c r="N9" s="350"/>
+      <c r="O9" s="350"/>
+      <c r="P9" s="350"/>
+      <c r="Q9" s="350"/>
+      <c r="R9" s="350"/>
+      <c r="S9" s="350"/>
+      <c r="T9" s="350"/>
+      <c r="U9" s="350"/>
     </row>
     <row r="10" spans="2:21">
-      <c r="B10" s="379" t="s">
+      <c r="B10" s="353" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="380"/>
-      <c r="D10" s="380"/>
-      <c r="E10" s="380"/>
-      <c r="F10" s="380"/>
-      <c r="G10" s="380"/>
-      <c r="H10" s="380"/>
-      <c r="I10" s="380"/>
-      <c r="J10" s="380"/>
-      <c r="L10" s="343" t="s">
+      <c r="C10" s="354"/>
+      <c r="D10" s="354"/>
+      <c r="E10" s="354"/>
+      <c r="F10" s="354"/>
+      <c r="G10" s="354"/>
+      <c r="H10" s="354"/>
+      <c r="I10" s="354"/>
+      <c r="J10" s="354"/>
+      <c r="L10" s="350" t="s">
         <v>6</v>
       </c>
-      <c r="M10" s="343"/>
-      <c r="N10" s="343"/>
-      <c r="O10" s="343"/>
-      <c r="P10" s="343"/>
-      <c r="Q10" s="343"/>
-      <c r="R10" s="343"/>
-      <c r="S10" s="343"/>
-      <c r="T10" s="343"/>
-      <c r="U10" s="343"/>
+      <c r="M10" s="350"/>
+      <c r="N10" s="350"/>
+      <c r="O10" s="350"/>
+      <c r="P10" s="350"/>
+      <c r="Q10" s="350"/>
+      <c r="R10" s="350"/>
+      <c r="S10" s="350"/>
+      <c r="T10" s="350"/>
+      <c r="U10" s="350"/>
     </row>
     <row r="11" spans="2:21">
-      <c r="B11" s="380"/>
-      <c r="C11" s="380"/>
-      <c r="D11" s="380"/>
-      <c r="E11" s="380"/>
-      <c r="F11" s="380"/>
-      <c r="G11" s="380"/>
-      <c r="H11" s="380"/>
-      <c r="I11" s="380"/>
-      <c r="J11" s="380"/>
-      <c r="L11" s="343"/>
-      <c r="M11" s="343"/>
-      <c r="N11" s="343"/>
-      <c r="O11" s="343"/>
-      <c r="P11" s="343"/>
-      <c r="Q11" s="343"/>
-      <c r="R11" s="343"/>
-      <c r="S11" s="343"/>
-      <c r="T11" s="343"/>
-      <c r="U11" s="343"/>
+      <c r="B11" s="354"/>
+      <c r="C11" s="354"/>
+      <c r="D11" s="354"/>
+      <c r="E11" s="354"/>
+      <c r="F11" s="354"/>
+      <c r="G11" s="354"/>
+      <c r="H11" s="354"/>
+      <c r="I11" s="354"/>
+      <c r="J11" s="354"/>
+      <c r="L11" s="350"/>
+      <c r="M11" s="350"/>
+      <c r="N11" s="350"/>
+      <c r="O11" s="350"/>
+      <c r="P11" s="350"/>
+      <c r="Q11" s="350"/>
+      <c r="R11" s="350"/>
+      <c r="S11" s="350"/>
+      <c r="T11" s="350"/>
+      <c r="U11" s="350"/>
     </row>
     <row r="12" spans="2:21" ht="15" customHeight="1">
-      <c r="B12" s="381" t="s">
-        <v>337</v>
-      </c>
-      <c r="C12" s="381"/>
-      <c r="D12" s="381"/>
-      <c r="E12" s="381"/>
-      <c r="F12" s="381"/>
-      <c r="G12" s="381"/>
-      <c r="H12" s="381"/>
-      <c r="I12" s="381"/>
-      <c r="J12" s="381"/>
-      <c r="L12" s="347" t="s">
+      <c r="B12" s="355" t="s">
+        <v>336</v>
+      </c>
+      <c r="C12" s="355"/>
+      <c r="D12" s="355"/>
+      <c r="E12" s="355"/>
+      <c r="F12" s="355"/>
+      <c r="G12" s="355"/>
+      <c r="H12" s="355"/>
+      <c r="I12" s="355"/>
+      <c r="J12" s="355"/>
+      <c r="L12" s="381" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="347"/>
-      <c r="N12" s="347"/>
-      <c r="O12" s="347"/>
-      <c r="P12" s="347"/>
-      <c r="Q12" s="347"/>
-      <c r="R12" s="347"/>
-      <c r="S12" s="347"/>
-      <c r="T12" s="347"/>
-      <c r="U12" s="347"/>
+      <c r="M12" s="381"/>
+      <c r="N12" s="381"/>
+      <c r="O12" s="381"/>
+      <c r="P12" s="381"/>
+      <c r="Q12" s="381"/>
+      <c r="R12" s="381"/>
+      <c r="S12" s="381"/>
+      <c r="T12" s="381"/>
+      <c r="U12" s="381"/>
     </row>
     <row r="13" spans="2:21" ht="16.5">
-      <c r="B13" s="367"/>
-      <c r="C13" s="367"/>
-      <c r="D13" s="367"/>
-      <c r="E13" s="367"/>
-      <c r="F13" s="367"/>
-      <c r="G13" s="367"/>
-      <c r="H13" s="367"/>
-      <c r="I13" s="367"/>
-      <c r="J13" s="367"/>
-      <c r="L13" s="347"/>
-      <c r="M13" s="347"/>
-      <c r="N13" s="347"/>
-      <c r="O13" s="347"/>
-      <c r="P13" s="347"/>
-      <c r="Q13" s="347"/>
-      <c r="R13" s="347"/>
-      <c r="S13" s="347"/>
-      <c r="T13" s="347"/>
-      <c r="U13" s="347"/>
+      <c r="B13" s="356"/>
+      <c r="C13" s="356"/>
+      <c r="D13" s="356"/>
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="G13" s="356"/>
+      <c r="H13" s="356"/>
+      <c r="I13" s="356"/>
+      <c r="J13" s="356"/>
+      <c r="L13" s="381"/>
+      <c r="M13" s="381"/>
+      <c r="N13" s="381"/>
+      <c r="O13" s="381"/>
+      <c r="P13" s="381"/>
+      <c r="Q13" s="381"/>
+      <c r="R13" s="381"/>
+      <c r="S13" s="381"/>
+      <c r="T13" s="381"/>
+      <c r="U13" s="381"/>
     </row>
     <row r="14" spans="2:21" ht="16.5">
-      <c r="B14" s="368" t="s">
+      <c r="B14" s="357" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="368"/>
-      <c r="D14" s="368"/>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
-      <c r="G14" s="368"/>
-      <c r="H14" s="368"/>
-      <c r="I14" s="368"/>
-      <c r="J14" s="368"/>
-      <c r="L14" s="347"/>
-      <c r="M14" s="347"/>
-      <c r="N14" s="347"/>
-      <c r="O14" s="347"/>
-      <c r="P14" s="347"/>
-      <c r="Q14" s="347"/>
-      <c r="R14" s="347"/>
-      <c r="S14" s="347"/>
-      <c r="T14" s="347"/>
-      <c r="U14" s="347"/>
+      <c r="C14" s="357"/>
+      <c r="D14" s="357"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
+      <c r="G14" s="357"/>
+      <c r="H14" s="357"/>
+      <c r="I14" s="357"/>
+      <c r="J14" s="357"/>
+      <c r="L14" s="381"/>
+      <c r="M14" s="381"/>
+      <c r="N14" s="381"/>
+      <c r="O14" s="381"/>
+      <c r="P14" s="381"/>
+      <c r="Q14" s="381"/>
+      <c r="R14" s="381"/>
+      <c r="S14" s="381"/>
+      <c r="T14" s="381"/>
+      <c r="U14" s="381"/>
     </row>
     <row r="15" spans="2:21" ht="18">
-      <c r="B15" s="369" t="s">
+      <c r="B15" s="358" t="s">
         <v>160</v>
       </c>
-      <c r="C15" s="369"/>
-      <c r="D15" s="369"/>
-      <c r="E15" s="369"/>
-      <c r="F15" s="369"/>
-      <c r="G15" s="369"/>
-      <c r="H15" s="369"/>
-      <c r="I15" s="369"/>
-      <c r="J15" s="369"/>
-      <c r="L15" s="347"/>
-      <c r="M15" s="347"/>
-      <c r="N15" s="347"/>
-      <c r="O15" s="347"/>
-      <c r="P15" s="347"/>
-      <c r="Q15" s="347"/>
-      <c r="R15" s="347"/>
-      <c r="S15" s="347"/>
-      <c r="T15" s="347"/>
-      <c r="U15" s="347"/>
+      <c r="C15" s="358"/>
+      <c r="D15" s="358"/>
+      <c r="E15" s="358"/>
+      <c r="F15" s="358"/>
+      <c r="G15" s="358"/>
+      <c r="H15" s="358"/>
+      <c r="I15" s="358"/>
+      <c r="J15" s="358"/>
+      <c r="L15" s="381"/>
+      <c r="M15" s="381"/>
+      <c r="N15" s="381"/>
+      <c r="O15" s="381"/>
+      <c r="P15" s="381"/>
+      <c r="Q15" s="381"/>
+      <c r="R15" s="381"/>
+      <c r="S15" s="381"/>
+      <c r="T15" s="381"/>
+      <c r="U15" s="381"/>
     </row>
     <row r="16" spans="2:21" ht="18">
-      <c r="B16" s="369" t="s">
+      <c r="B16" s="358" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="369"/>
-      <c r="D16" s="369"/>
-      <c r="E16" s="369"/>
-      <c r="F16" s="369"/>
-      <c r="G16" s="369"/>
-      <c r="H16" s="369"/>
-      <c r="I16" s="369"/>
-      <c r="J16" s="369"/>
-      <c r="L16" s="347"/>
-      <c r="M16" s="347"/>
-      <c r="N16" s="347"/>
-      <c r="O16" s="347"/>
-      <c r="P16" s="347"/>
-      <c r="Q16" s="347"/>
-      <c r="R16" s="347"/>
-      <c r="S16" s="347"/>
-      <c r="T16" s="347"/>
-      <c r="U16" s="347"/>
+      <c r="C16" s="358"/>
+      <c r="D16" s="358"/>
+      <c r="E16" s="358"/>
+      <c r="F16" s="358"/>
+      <c r="G16" s="358"/>
+      <c r="H16" s="358"/>
+      <c r="I16" s="358"/>
+      <c r="J16" s="358"/>
+      <c r="L16" s="381"/>
+      <c r="M16" s="381"/>
+      <c r="N16" s="381"/>
+      <c r="O16" s="381"/>
+      <c r="P16" s="381"/>
+      <c r="Q16" s="381"/>
+      <c r="R16" s="381"/>
+      <c r="S16" s="381"/>
+      <c r="T16" s="381"/>
+      <c r="U16" s="381"/>
     </row>
     <row r="17" spans="2:21">
-      <c r="B17" s="343" t="s">
+      <c r="B17" s="350" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="343"/>
-      <c r="D17" s="343"/>
-      <c r="E17" s="343"/>
-      <c r="F17" s="343"/>
-      <c r="G17" s="343"/>
-      <c r="H17" s="343"/>
-      <c r="I17" s="343"/>
-      <c r="J17" s="343"/>
-      <c r="L17" s="347"/>
-      <c r="M17" s="347"/>
-      <c r="N17" s="347"/>
-      <c r="O17" s="347"/>
-      <c r="P17" s="347"/>
-      <c r="Q17" s="347"/>
-      <c r="R17" s="347"/>
-      <c r="S17" s="347"/>
-      <c r="T17" s="347"/>
-      <c r="U17" s="347"/>
+      <c r="C17" s="350"/>
+      <c r="D17" s="350"/>
+      <c r="E17" s="350"/>
+      <c r="F17" s="350"/>
+      <c r="G17" s="350"/>
+      <c r="H17" s="350"/>
+      <c r="I17" s="350"/>
+      <c r="J17" s="350"/>
+      <c r="L17" s="381"/>
+      <c r="M17" s="381"/>
+      <c r="N17" s="381"/>
+      <c r="O17" s="381"/>
+      <c r="P17" s="381"/>
+      <c r="Q17" s="381"/>
+      <c r="R17" s="381"/>
+      <c r="S17" s="381"/>
+      <c r="T17" s="381"/>
+      <c r="U17" s="381"/>
     </row>
     <row r="18" spans="2:21">
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="351" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="370"/>
-      <c r="D18" s="370"/>
-      <c r="E18" s="370"/>
-      <c r="F18" s="370"/>
-      <c r="G18" s="370"/>
-      <c r="H18" s="370"/>
-      <c r="I18" s="370"/>
-      <c r="J18" s="370"/>
-      <c r="L18" s="347"/>
-      <c r="M18" s="347"/>
-      <c r="N18" s="347"/>
-      <c r="O18" s="347"/>
-      <c r="P18" s="347"/>
-      <c r="Q18" s="347"/>
-      <c r="R18" s="347"/>
-      <c r="S18" s="347"/>
-      <c r="T18" s="347"/>
-      <c r="U18" s="347"/>
+      <c r="C18" s="351"/>
+      <c r="D18" s="351"/>
+      <c r="E18" s="351"/>
+      <c r="F18" s="351"/>
+      <c r="G18" s="351"/>
+      <c r="H18" s="351"/>
+      <c r="I18" s="351"/>
+      <c r="J18" s="351"/>
+      <c r="L18" s="381"/>
+      <c r="M18" s="381"/>
+      <c r="N18" s="381"/>
+      <c r="O18" s="381"/>
+      <c r="P18" s="381"/>
+      <c r="Q18" s="381"/>
+      <c r="R18" s="381"/>
+      <c r="S18" s="381"/>
+      <c r="T18" s="381"/>
+      <c r="U18" s="381"/>
     </row>
     <row r="19" spans="2:21">
-      <c r="B19" s="370" t="s">
+      <c r="B19" s="351" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="370"/>
-      <c r="D19" s="370"/>
-      <c r="E19" s="370"/>
-      <c r="F19" s="370"/>
-      <c r="G19" s="370"/>
-      <c r="H19" s="370"/>
-      <c r="I19" s="370"/>
-      <c r="J19" s="370"/>
-      <c r="L19" s="347"/>
-      <c r="M19" s="347"/>
-      <c r="N19" s="347"/>
-      <c r="O19" s="347"/>
-      <c r="P19" s="347"/>
-      <c r="Q19" s="347"/>
-      <c r="R19" s="347"/>
-      <c r="S19" s="347"/>
-      <c r="T19" s="347"/>
-      <c r="U19" s="347"/>
+      <c r="C19" s="351"/>
+      <c r="D19" s="351"/>
+      <c r="E19" s="351"/>
+      <c r="F19" s="351"/>
+      <c r="G19" s="351"/>
+      <c r="H19" s="351"/>
+      <c r="I19" s="351"/>
+      <c r="J19" s="351"/>
+      <c r="L19" s="381"/>
+      <c r="M19" s="381"/>
+      <c r="N19" s="381"/>
+      <c r="O19" s="381"/>
+      <c r="P19" s="381"/>
+      <c r="Q19" s="381"/>
+      <c r="R19" s="381"/>
+      <c r="S19" s="381"/>
+      <c r="T19" s="381"/>
+      <c r="U19" s="381"/>
     </row>
     <row r="20" spans="2:21" ht="15" customHeight="1">
-      <c r="B20" s="343" t="s">
+      <c r="B20" s="350" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="343"/>
-      <c r="D20" s="343"/>
-      <c r="E20" s="343"/>
-      <c r="F20" s="343"/>
-      <c r="G20" s="343"/>
-      <c r="H20" s="343"/>
-      <c r="I20" s="343"/>
-      <c r="J20" s="343"/>
-      <c r="L20" s="343"/>
-      <c r="M20" s="343"/>
-      <c r="N20" s="343"/>
-      <c r="O20" s="343"/>
-      <c r="P20" s="343"/>
-      <c r="Q20" s="343"/>
-      <c r="R20" s="343"/>
-      <c r="S20" s="343"/>
-      <c r="T20" s="343"/>
-      <c r="U20" s="343"/>
+      <c r="C20" s="350"/>
+      <c r="D20" s="350"/>
+      <c r="E20" s="350"/>
+      <c r="F20" s="350"/>
+      <c r="G20" s="350"/>
+      <c r="H20" s="350"/>
+      <c r="I20" s="350"/>
+      <c r="J20" s="350"/>
+      <c r="L20" s="350"/>
+      <c r="M20" s="350"/>
+      <c r="N20" s="350"/>
+      <c r="O20" s="350"/>
+      <c r="P20" s="350"/>
+      <c r="Q20" s="350"/>
+      <c r="R20" s="350"/>
+      <c r="S20" s="350"/>
+      <c r="T20" s="350"/>
+      <c r="U20" s="350"/>
     </row>
     <row r="21" spans="2:21">
-      <c r="L21" s="343"/>
-      <c r="M21" s="343"/>
-      <c r="N21" s="343"/>
-      <c r="O21" s="343"/>
-      <c r="P21" s="343"/>
-      <c r="Q21" s="343"/>
-      <c r="R21" s="343"/>
-      <c r="S21" s="343"/>
-      <c r="T21" s="343"/>
-      <c r="U21" s="343"/>
+      <c r="L21" s="350"/>
+      <c r="M21" s="350"/>
+      <c r="N21" s="350"/>
+      <c r="O21" s="350"/>
+      <c r="P21" s="350"/>
+      <c r="Q21" s="350"/>
+      <c r="R21" s="350"/>
+      <c r="S21" s="350"/>
+      <c r="T21" s="350"/>
+      <c r="U21" s="350"/>
     </row>
     <row r="22" spans="2:21" ht="15" customHeight="1">
-      <c r="B22" s="343"/>
-      <c r="C22" s="343"/>
-      <c r="D22" s="343"/>
-      <c r="E22" s="343"/>
-      <c r="F22" s="343"/>
-      <c r="G22" s="343"/>
-      <c r="H22" s="343"/>
-      <c r="I22" s="343"/>
-      <c r="J22" s="343"/>
-      <c r="L22" s="344" t="s">
+      <c r="B22" s="350"/>
+      <c r="C22" s="350"/>
+      <c r="D22" s="350"/>
+      <c r="E22" s="350"/>
+      <c r="F22" s="350"/>
+      <c r="G22" s="350"/>
+      <c r="H22" s="350"/>
+      <c r="I22" s="350"/>
+      <c r="J22" s="350"/>
+      <c r="L22" s="378" t="s">
         <v>39</v>
       </c>
-      <c r="M22" s="344"/>
-      <c r="N22" s="344"/>
-      <c r="O22" s="344"/>
-      <c r="P22" s="344"/>
-      <c r="Q22" s="344"/>
-      <c r="R22" s="344"/>
-      <c r="S22" s="344"/>
-      <c r="T22" s="344"/>
-      <c r="U22" s="344"/>
+      <c r="M22" s="378"/>
+      <c r="N22" s="378"/>
+      <c r="O22" s="378"/>
+      <c r="P22" s="378"/>
+      <c r="Q22" s="378"/>
+      <c r="R22" s="378"/>
+      <c r="S22" s="378"/>
+      <c r="T22" s="378"/>
+      <c r="U22" s="378"/>
     </row>
     <row r="23" spans="2:21">
-      <c r="B23" s="343" t="s">
+      <c r="B23" s="350" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="343"/>
-      <c r="D23" s="343"/>
-      <c r="E23" s="343"/>
-      <c r="F23" s="343"/>
-      <c r="G23" s="343"/>
-      <c r="H23" s="343"/>
-      <c r="I23" s="343"/>
-      <c r="J23" s="343"/>
-      <c r="L23" s="344"/>
-      <c r="M23" s="344"/>
-      <c r="N23" s="344"/>
-      <c r="O23" s="344"/>
-      <c r="P23" s="344"/>
-      <c r="Q23" s="344"/>
-      <c r="R23" s="344"/>
-      <c r="S23" s="344"/>
-      <c r="T23" s="344"/>
-      <c r="U23" s="344"/>
+      <c r="C23" s="350"/>
+      <c r="D23" s="350"/>
+      <c r="E23" s="350"/>
+      <c r="F23" s="350"/>
+      <c r="G23" s="350"/>
+      <c r="H23" s="350"/>
+      <c r="I23" s="350"/>
+      <c r="J23" s="350"/>
+      <c r="L23" s="378"/>
+      <c r="M23" s="378"/>
+      <c r="N23" s="378"/>
+      <c r="O23" s="378"/>
+      <c r="P23" s="378"/>
+      <c r="Q23" s="378"/>
+      <c r="R23" s="378"/>
+      <c r="S23" s="378"/>
+      <c r="T23" s="378"/>
+      <c r="U23" s="378"/>
     </row>
     <row r="24" spans="2:21" ht="30" customHeight="1">
-      <c r="B24" s="361" t="s">
+      <c r="B24" s="366" t="s">
         <v>294</v>
       </c>
-      <c r="C24" s="362"/>
-      <c r="D24" s="362"/>
-      <c r="E24" s="362"/>
-      <c r="F24" s="362"/>
-      <c r="G24" s="362"/>
-      <c r="H24" s="362"/>
-      <c r="I24" s="362"/>
-      <c r="J24" s="363"/>
-      <c r="L24" s="344"/>
-      <c r="M24" s="344"/>
-      <c r="N24" s="344"/>
-      <c r="O24" s="344"/>
-      <c r="P24" s="344"/>
-      <c r="Q24" s="344"/>
-      <c r="R24" s="344"/>
-      <c r="S24" s="344"/>
-      <c r="T24" s="344"/>
-      <c r="U24" s="344"/>
+      <c r="C24" s="367"/>
+      <c r="D24" s="367"/>
+      <c r="E24" s="367"/>
+      <c r="F24" s="367"/>
+      <c r="G24" s="367"/>
+      <c r="H24" s="367"/>
+      <c r="I24" s="367"/>
+      <c r="J24" s="368"/>
+      <c r="L24" s="378"/>
+      <c r="M24" s="378"/>
+      <c r="N24" s="378"/>
+      <c r="O24" s="378"/>
+      <c r="P24" s="378"/>
+      <c r="Q24" s="378"/>
+      <c r="R24" s="378"/>
+      <c r="S24" s="378"/>
+      <c r="T24" s="378"/>
+      <c r="U24" s="378"/>
     </row>
     <row r="25" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B25" s="364"/>
-      <c r="C25" s="365"/>
-      <c r="D25" s="365"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
-      <c r="G25" s="365"/>
-      <c r="H25" s="365"/>
-      <c r="I25" s="365"/>
-      <c r="J25" s="366"/>
-      <c r="L25" s="344"/>
-      <c r="M25" s="344"/>
-      <c r="N25" s="344"/>
-      <c r="O25" s="344"/>
-      <c r="P25" s="344"/>
-      <c r="Q25" s="344"/>
-      <c r="R25" s="344"/>
-      <c r="S25" s="344"/>
-      <c r="T25" s="344"/>
-      <c r="U25" s="344"/>
+      <c r="B25" s="369"/>
+      <c r="C25" s="370"/>
+      <c r="D25" s="370"/>
+      <c r="E25" s="370"/>
+      <c r="F25" s="370"/>
+      <c r="G25" s="370"/>
+      <c r="H25" s="370"/>
+      <c r="I25" s="370"/>
+      <c r="J25" s="371"/>
+      <c r="L25" s="378"/>
+      <c r="M25" s="378"/>
+      <c r="N25" s="378"/>
+      <c r="O25" s="378"/>
+      <c r="P25" s="378"/>
+      <c r="Q25" s="378"/>
+      <c r="R25" s="378"/>
+      <c r="S25" s="378"/>
+      <c r="T25" s="378"/>
+      <c r="U25" s="378"/>
     </row>
     <row r="26" spans="2:21" ht="15.75">
-      <c r="B26" s="354" t="s">
+      <c r="B26" s="359" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="355"/>
-      <c r="D26" s="355"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
-      <c r="G26" s="355"/>
-      <c r="H26" s="355"/>
-      <c r="I26" s="355"/>
-      <c r="J26" s="356"/>
-      <c r="L26" s="344"/>
-      <c r="M26" s="344"/>
-      <c r="N26" s="344"/>
-      <c r="O26" s="344"/>
-      <c r="P26" s="344"/>
-      <c r="Q26" s="344"/>
-      <c r="R26" s="344"/>
-      <c r="S26" s="344"/>
-      <c r="T26" s="344"/>
-      <c r="U26" s="344"/>
+      <c r="C26" s="360"/>
+      <c r="D26" s="360"/>
+      <c r="E26" s="360"/>
+      <c r="F26" s="360"/>
+      <c r="G26" s="360"/>
+      <c r="H26" s="360"/>
+      <c r="I26" s="360"/>
+      <c r="J26" s="361"/>
+      <c r="L26" s="378"/>
+      <c r="M26" s="378"/>
+      <c r="N26" s="378"/>
+      <c r="O26" s="378"/>
+      <c r="P26" s="378"/>
+      <c r="Q26" s="378"/>
+      <c r="R26" s="378"/>
+      <c r="S26" s="378"/>
+      <c r="T26" s="378"/>
+      <c r="U26" s="378"/>
     </row>
     <row r="27" spans="2:21">
-      <c r="B27" s="357" t="s">
+      <c r="B27" s="362" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="358"/>
-      <c r="D27" s="358"/>
-      <c r="E27" s="358"/>
-      <c r="F27" s="358"/>
-      <c r="G27" s="358"/>
-      <c r="H27" s="358"/>
-      <c r="I27" s="358"/>
-      <c r="J27" s="359"/>
-      <c r="L27" s="344"/>
-      <c r="M27" s="344"/>
-      <c r="N27" s="344"/>
-      <c r="O27" s="344"/>
-      <c r="P27" s="344"/>
-      <c r="Q27" s="344"/>
-      <c r="R27" s="344"/>
-      <c r="S27" s="344"/>
-      <c r="T27" s="344"/>
-      <c r="U27" s="344"/>
+      <c r="C27" s="363"/>
+      <c r="D27" s="363"/>
+      <c r="E27" s="363"/>
+      <c r="F27" s="363"/>
+      <c r="G27" s="363"/>
+      <c r="H27" s="363"/>
+      <c r="I27" s="363"/>
+      <c r="J27" s="364"/>
+      <c r="L27" s="378"/>
+      <c r="M27" s="378"/>
+      <c r="N27" s="378"/>
+      <c r="O27" s="378"/>
+      <c r="P27" s="378"/>
+      <c r="Q27" s="378"/>
+      <c r="R27" s="378"/>
+      <c r="S27" s="378"/>
+      <c r="T27" s="378"/>
+      <c r="U27" s="378"/>
     </row>
     <row r="28" spans="2:21">
-      <c r="B28" s="360" t="s">
+      <c r="B28" s="365" t="s">
         <v>249</v>
       </c>
-      <c r="C28" s="360"/>
-      <c r="D28" s="360"/>
-      <c r="E28" s="360"/>
-      <c r="F28" s="360"/>
-      <c r="G28" s="360"/>
-      <c r="H28" s="360"/>
-      <c r="I28" s="360"/>
-      <c r="J28" s="360"/>
-      <c r="L28" s="344"/>
-      <c r="M28" s="344"/>
-      <c r="N28" s="344"/>
-      <c r="O28" s="344"/>
-      <c r="P28" s="344"/>
-      <c r="Q28" s="344"/>
-      <c r="R28" s="344"/>
-      <c r="S28" s="344"/>
-      <c r="T28" s="344"/>
-      <c r="U28" s="344"/>
+      <c r="C28" s="365"/>
+      <c r="D28" s="365"/>
+      <c r="E28" s="365"/>
+      <c r="F28" s="365"/>
+      <c r="G28" s="365"/>
+      <c r="H28" s="365"/>
+      <c r="I28" s="365"/>
+      <c r="J28" s="365"/>
+      <c r="L28" s="378"/>
+      <c r="M28" s="378"/>
+      <c r="N28" s="378"/>
+      <c r="O28" s="378"/>
+      <c r="P28" s="378"/>
+      <c r="Q28" s="378"/>
+      <c r="R28" s="378"/>
+      <c r="S28" s="378"/>
+      <c r="T28" s="378"/>
+      <c r="U28" s="378"/>
     </row>
     <row r="29" spans="2:21">
-      <c r="B29" s="343"/>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-      <c r="G29" s="343"/>
-      <c r="H29" s="343"/>
-      <c r="I29" s="343"/>
-      <c r="J29" s="343"/>
-      <c r="L29" s="344"/>
-      <c r="M29" s="344"/>
-      <c r="N29" s="344"/>
-      <c r="O29" s="344"/>
-      <c r="P29" s="344"/>
-      <c r="Q29" s="344"/>
-      <c r="R29" s="344"/>
-      <c r="S29" s="344"/>
-      <c r="T29" s="344"/>
-      <c r="U29" s="344"/>
+      <c r="B29" s="350"/>
+      <c r="C29" s="350"/>
+      <c r="D29" s="350"/>
+      <c r="E29" s="350"/>
+      <c r="F29" s="350"/>
+      <c r="G29" s="350"/>
+      <c r="H29" s="350"/>
+      <c r="I29" s="350"/>
+      <c r="J29" s="350"/>
+      <c r="L29" s="378"/>
+      <c r="M29" s="378"/>
+      <c r="N29" s="378"/>
+      <c r="O29" s="378"/>
+      <c r="P29" s="378"/>
+      <c r="Q29" s="378"/>
+      <c r="R29" s="378"/>
+      <c r="S29" s="378"/>
+      <c r="T29" s="378"/>
+      <c r="U29" s="378"/>
     </row>
     <row r="30" spans="2:21">
-      <c r="B30" s="343"/>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-      <c r="G30" s="343"/>
-      <c r="H30" s="343"/>
-      <c r="I30" s="343"/>
-      <c r="J30" s="343"/>
-      <c r="L30" s="344"/>
-      <c r="M30" s="344"/>
-      <c r="N30" s="344"/>
-      <c r="O30" s="344"/>
-      <c r="P30" s="344"/>
-      <c r="Q30" s="344"/>
-      <c r="R30" s="344"/>
-      <c r="S30" s="344"/>
-      <c r="T30" s="344"/>
-      <c r="U30" s="344"/>
+      <c r="B30" s="350"/>
+      <c r="C30" s="350"/>
+      <c r="D30" s="350"/>
+      <c r="E30" s="350"/>
+      <c r="F30" s="350"/>
+      <c r="G30" s="350"/>
+      <c r="H30" s="350"/>
+      <c r="I30" s="350"/>
+      <c r="J30" s="350"/>
+      <c r="L30" s="378"/>
+      <c r="M30" s="378"/>
+      <c r="N30" s="378"/>
+      <c r="O30" s="378"/>
+      <c r="P30" s="378"/>
+      <c r="Q30" s="378"/>
+      <c r="R30" s="378"/>
+      <c r="S30" s="378"/>
+      <c r="T30" s="378"/>
+      <c r="U30" s="378"/>
     </row>
     <row r="31" spans="2:21">
-      <c r="B31" s="343" t="s">
+      <c r="B31" s="350" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="343"/>
-      <c r="D31" s="343"/>
-      <c r="E31" s="343"/>
-      <c r="F31" s="343"/>
-      <c r="G31" s="343"/>
-      <c r="H31" s="343"/>
-      <c r="I31" s="343"/>
-      <c r="J31" s="343"/>
-      <c r="L31" s="344"/>
-      <c r="M31" s="344"/>
-      <c r="N31" s="344"/>
-      <c r="O31" s="344"/>
-      <c r="P31" s="344"/>
-      <c r="Q31" s="344"/>
-      <c r="R31" s="344"/>
-      <c r="S31" s="344"/>
-      <c r="T31" s="344"/>
-      <c r="U31" s="344"/>
+      <c r="C31" s="350"/>
+      <c r="D31" s="350"/>
+      <c r="E31" s="350"/>
+      <c r="F31" s="350"/>
+      <c r="G31" s="350"/>
+      <c r="H31" s="350"/>
+      <c r="I31" s="350"/>
+      <c r="J31" s="350"/>
+      <c r="L31" s="378"/>
+      <c r="M31" s="378"/>
+      <c r="N31" s="378"/>
+      <c r="O31" s="378"/>
+      <c r="P31" s="378"/>
+      <c r="Q31" s="378"/>
+      <c r="R31" s="378"/>
+      <c r="S31" s="378"/>
+      <c r="T31" s="378"/>
+      <c r="U31" s="378"/>
     </row>
     <row r="32" spans="2:21">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="350" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-      <c r="G32" s="343"/>
-      <c r="H32" s="343"/>
-      <c r="I32" s="343"/>
-      <c r="J32" s="343"/>
-      <c r="L32" s="344"/>
-      <c r="M32" s="344"/>
-      <c r="N32" s="344"/>
-      <c r="O32" s="344"/>
-      <c r="P32" s="344"/>
-      <c r="Q32" s="344"/>
-      <c r="R32" s="344"/>
-      <c r="S32" s="344"/>
-      <c r="T32" s="344"/>
-      <c r="U32" s="344"/>
+      <c r="C32" s="350"/>
+      <c r="D32" s="350"/>
+      <c r="E32" s="350"/>
+      <c r="F32" s="350"/>
+      <c r="G32" s="350"/>
+      <c r="H32" s="350"/>
+      <c r="I32" s="350"/>
+      <c r="J32" s="350"/>
+      <c r="L32" s="378"/>
+      <c r="M32" s="378"/>
+      <c r="N32" s="378"/>
+      <c r="O32" s="378"/>
+      <c r="P32" s="378"/>
+      <c r="Q32" s="378"/>
+      <c r="R32" s="378"/>
+      <c r="S32" s="378"/>
+      <c r="T32" s="378"/>
+      <c r="U32" s="378"/>
     </row>
     <row r="34" spans="3:21">
-      <c r="C34" s="377" t="s">
+      <c r="C34" s="349" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="377"/>
+      <c r="D34" s="349"/>
       <c r="E34" s="35"/>
       <c r="G34" s="238" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="35" spans="3:21">
-      <c r="C35" s="377" t="s">
+      <c r="C35" s="349" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="377"/>
+      <c r="D35" s="349"/>
       <c r="E35" s="35"/>
       <c r="G35" s="238" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="36" spans="3:21">
-      <c r="C36" s="377" t="s">
+      <c r="C36" s="349" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="377"/>
+      <c r="D36" s="349"/>
       <c r="E36" s="35"/>
       <c r="G36" s="238" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="37" spans="3:21">
-      <c r="C37" s="377" t="s">
+      <c r="C37" s="349" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="377"/>
+      <c r="D37" s="349"/>
       <c r="E37" s="35"/>
       <c r="G37" s="238" t="s">
         <v>121</v>
       </c>
-      <c r="L37" s="343" t="s">
+      <c r="L37" s="350" t="s">
         <v>7</v>
       </c>
-      <c r="M37" s="343"/>
-      <c r="N37" s="343"/>
-      <c r="O37" s="343"/>
-      <c r="P37" s="343"/>
-      <c r="Q37" s="343"/>
-      <c r="R37" s="343"/>
-      <c r="S37" s="343"/>
-      <c r="T37" s="343"/>
-      <c r="U37" s="343"/>
+      <c r="M37" s="350"/>
+      <c r="N37" s="350"/>
+      <c r="O37" s="350"/>
+      <c r="P37" s="350"/>
+      <c r="Q37" s="350"/>
+      <c r="R37" s="350"/>
+      <c r="S37" s="350"/>
+      <c r="T37" s="350"/>
+      <c r="U37" s="350"/>
     </row>
     <row r="38" spans="3:21">
-      <c r="C38" s="377" t="s">
+      <c r="C38" s="349" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="377"/>
+      <c r="D38" s="349"/>
       <c r="E38" s="35"/>
-      <c r="L38" s="343" t="s">
+      <c r="L38" s="350" t="s">
         <v>8</v>
       </c>
-      <c r="M38" s="343"/>
-      <c r="N38" s="343"/>
-      <c r="O38" s="343"/>
-      <c r="P38" s="343"/>
-      <c r="Q38" s="343"/>
-      <c r="R38" s="343"/>
-      <c r="S38" s="343"/>
-      <c r="T38" s="343"/>
-      <c r="U38" s="343"/>
+      <c r="M38" s="350"/>
+      <c r="N38" s="350"/>
+      <c r="O38" s="350"/>
+      <c r="P38" s="350"/>
+      <c r="Q38" s="350"/>
+      <c r="R38" s="350"/>
+      <c r="S38" s="350"/>
+      <c r="T38" s="350"/>
+      <c r="U38" s="350"/>
     </row>
     <row r="39" spans="3:21">
-      <c r="L39" s="343" t="s">
+      <c r="L39" s="350" t="s">
         <v>9</v>
       </c>
-      <c r="M39" s="343"/>
-      <c r="N39" s="343"/>
-      <c r="O39" s="343"/>
-      <c r="P39" s="343"/>
-      <c r="Q39" s="343"/>
-      <c r="R39" s="343"/>
-      <c r="S39" s="343"/>
-      <c r="T39" s="343"/>
-      <c r="U39" s="343"/>
+      <c r="M39" s="350"/>
+      <c r="N39" s="350"/>
+      <c r="O39" s="350"/>
+      <c r="P39" s="350"/>
+      <c r="Q39" s="350"/>
+      <c r="R39" s="350"/>
+      <c r="S39" s="350"/>
+      <c r="T39" s="350"/>
+      <c r="U39" s="350"/>
     </row>
     <row r="40" spans="3:21">
-      <c r="L40" s="343" t="s">
+      <c r="L40" s="350" t="s">
         <v>11</v>
       </c>
-      <c r="M40" s="343"/>
-      <c r="N40" s="343"/>
-      <c r="O40" s="343"/>
-      <c r="P40" s="343"/>
-      <c r="Q40" s="343"/>
-      <c r="R40" s="343"/>
-      <c r="S40" s="343"/>
-      <c r="T40" s="343"/>
-      <c r="U40" s="343"/>
+      <c r="M40" s="350"/>
+      <c r="N40" s="350"/>
+      <c r="O40" s="350"/>
+      <c r="P40" s="350"/>
+      <c r="Q40" s="350"/>
+      <c r="R40" s="350"/>
+      <c r="S40" s="350"/>
+      <c r="T40" s="350"/>
+      <c r="U40" s="350"/>
     </row>
     <row r="41" spans="3:21">
-      <c r="E41" s="375" t="s">
+      <c r="E41" s="347" t="s">
         <v>149</v>
       </c>
-      <c r="F41" s="376"/>
-      <c r="G41" s="376"/>
-      <c r="H41" s="376"/>
-      <c r="I41" s="376"/>
-      <c r="J41" s="376"/>
-      <c r="L41" s="345" t="s">
+      <c r="F41" s="348"/>
+      <c r="G41" s="348"/>
+      <c r="H41" s="348"/>
+      <c r="I41" s="348"/>
+      <c r="J41" s="348"/>
+      <c r="L41" s="379" t="s">
         <v>18</v>
       </c>
-      <c r="M41" s="343"/>
-      <c r="N41" s="343"/>
-      <c r="O41" s="343"/>
-      <c r="P41" s="343"/>
-      <c r="Q41" s="343"/>
-      <c r="R41" s="343"/>
-      <c r="S41" s="343"/>
-      <c r="T41" s="343"/>
-      <c r="U41" s="343"/>
+      <c r="M41" s="350"/>
+      <c r="N41" s="350"/>
+      <c r="O41" s="350"/>
+      <c r="P41" s="350"/>
+      <c r="Q41" s="350"/>
+      <c r="R41" s="350"/>
+      <c r="S41" s="350"/>
+      <c r="T41" s="350"/>
+      <c r="U41" s="350"/>
     </row>
     <row r="42" spans="3:21">
-      <c r="E42" s="376"/>
-      <c r="F42" s="376"/>
-      <c r="G42" s="376"/>
-      <c r="H42" s="376"/>
-      <c r="I42" s="376"/>
-      <c r="J42" s="376"/>
-      <c r="L42" s="343"/>
-      <c r="M42" s="343"/>
-      <c r="N42" s="343"/>
-      <c r="O42" s="343"/>
-      <c r="P42" s="343"/>
-      <c r="Q42" s="343"/>
-      <c r="R42" s="343"/>
-      <c r="S42" s="343"/>
-      <c r="T42" s="343"/>
-      <c r="U42" s="343"/>
+      <c r="E42" s="348"/>
+      <c r="F42" s="348"/>
+      <c r="G42" s="348"/>
+      <c r="H42" s="348"/>
+      <c r="I42" s="348"/>
+      <c r="J42" s="348"/>
+      <c r="L42" s="350"/>
+      <c r="M42" s="350"/>
+      <c r="N42" s="350"/>
+      <c r="O42" s="350"/>
+      <c r="P42" s="350"/>
+      <c r="Q42" s="350"/>
+      <c r="R42" s="350"/>
+      <c r="S42" s="350"/>
+      <c r="T42" s="350"/>
+      <c r="U42" s="350"/>
     </row>
     <row r="43" spans="3:21">
-      <c r="E43" s="376"/>
-      <c r="F43" s="376"/>
-      <c r="G43" s="376"/>
-      <c r="H43" s="376"/>
-      <c r="I43" s="376"/>
-      <c r="J43" s="376"/>
-      <c r="L43" s="343"/>
-      <c r="M43" s="343"/>
-      <c r="N43" s="343"/>
-      <c r="O43" s="343"/>
-      <c r="P43" s="343"/>
-      <c r="Q43" s="343"/>
-      <c r="R43" s="343"/>
-      <c r="S43" s="343"/>
-      <c r="T43" s="343"/>
-      <c r="U43" s="343"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
+      <c r="G43" s="348"/>
+      <c r="H43" s="348"/>
+      <c r="I43" s="348"/>
+      <c r="J43" s="348"/>
+      <c r="L43" s="350"/>
+      <c r="M43" s="350"/>
+      <c r="N43" s="350"/>
+      <c r="O43" s="350"/>
+      <c r="P43" s="350"/>
+      <c r="Q43" s="350"/>
+      <c r="R43" s="350"/>
+      <c r="S43" s="350"/>
+      <c r="T43" s="350"/>
+      <c r="U43" s="350"/>
     </row>
     <row r="44" spans="3:21">
-      <c r="E44" s="376"/>
-      <c r="F44" s="376"/>
-      <c r="G44" s="376"/>
-      <c r="H44" s="376"/>
-      <c r="I44" s="376"/>
-      <c r="J44" s="376"/>
+      <c r="E44" s="348"/>
+      <c r="F44" s="348"/>
+      <c r="G44" s="348"/>
+      <c r="H44" s="348"/>
+      <c r="I44" s="348"/>
+      <c r="J44" s="348"/>
     </row>
     <row r="45" spans="3:21">
-      <c r="E45" s="376"/>
-      <c r="F45" s="376"/>
-      <c r="G45" s="376"/>
-      <c r="H45" s="376"/>
-      <c r="I45" s="376"/>
-      <c r="J45" s="376"/>
-      <c r="L45" s="343"/>
-      <c r="M45" s="343"/>
-      <c r="N45" s="343"/>
-      <c r="O45" s="343"/>
-      <c r="P45" s="343"/>
-      <c r="Q45" s="343"/>
-      <c r="R45" s="343"/>
-      <c r="S45" s="343"/>
-      <c r="T45" s="343"/>
-      <c r="U45" s="343"/>
+      <c r="E45" s="348"/>
+      <c r="F45" s="348"/>
+      <c r="G45" s="348"/>
+      <c r="H45" s="348"/>
+      <c r="I45" s="348"/>
+      <c r="J45" s="348"/>
+      <c r="L45" s="350"/>
+      <c r="M45" s="350"/>
+      <c r="N45" s="350"/>
+      <c r="O45" s="350"/>
+      <c r="P45" s="350"/>
+      <c r="Q45" s="350"/>
+      <c r="R45" s="350"/>
+      <c r="S45" s="350"/>
+      <c r="T45" s="350"/>
+      <c r="U45" s="350"/>
     </row>
     <row r="46" spans="3:21">
-      <c r="E46" s="376"/>
-      <c r="F46" s="376"/>
-      <c r="G46" s="376"/>
-      <c r="H46" s="376"/>
-      <c r="I46" s="376"/>
-      <c r="J46" s="376"/>
-      <c r="L46" s="343"/>
-      <c r="M46" s="343"/>
-      <c r="N46" s="343"/>
-      <c r="O46" s="343"/>
-      <c r="P46" s="343"/>
-      <c r="Q46" s="343"/>
-      <c r="R46" s="343"/>
-      <c r="S46" s="343"/>
-      <c r="T46" s="343"/>
-      <c r="U46" s="343"/>
+      <c r="E46" s="348"/>
+      <c r="F46" s="348"/>
+      <c r="G46" s="348"/>
+      <c r="H46" s="348"/>
+      <c r="I46" s="348"/>
+      <c r="J46" s="348"/>
+      <c r="L46" s="350"/>
+      <c r="M46" s="350"/>
+      <c r="N46" s="350"/>
+      <c r="O46" s="350"/>
+      <c r="P46" s="350"/>
+      <c r="Q46" s="350"/>
+      <c r="R46" s="350"/>
+      <c r="S46" s="350"/>
+      <c r="T46" s="350"/>
+      <c r="U46" s="350"/>
     </row>
     <row r="47" spans="3:21">
-      <c r="E47" s="376"/>
-      <c r="F47" s="376"/>
-      <c r="G47" s="376"/>
-      <c r="H47" s="376"/>
-      <c r="I47" s="376"/>
-      <c r="J47" s="376"/>
-      <c r="L47" s="343"/>
-      <c r="M47" s="343"/>
-      <c r="N47" s="343"/>
-      <c r="O47" s="343"/>
-      <c r="P47" s="343"/>
-      <c r="Q47" s="343"/>
-      <c r="R47" s="343"/>
-      <c r="S47" s="343"/>
-      <c r="T47" s="343"/>
-      <c r="U47" s="343"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
+      <c r="G47" s="348"/>
+      <c r="H47" s="348"/>
+      <c r="I47" s="348"/>
+      <c r="J47" s="348"/>
+      <c r="L47" s="350"/>
+      <c r="M47" s="350"/>
+      <c r="N47" s="350"/>
+      <c r="O47" s="350"/>
+      <c r="P47" s="350"/>
+      <c r="Q47" s="350"/>
+      <c r="R47" s="350"/>
+      <c r="S47" s="350"/>
+      <c r="T47" s="350"/>
+      <c r="U47" s="350"/>
     </row>
     <row r="48" spans="3:21">
-      <c r="E48" s="376"/>
-      <c r="F48" s="376"/>
-      <c r="G48" s="376"/>
-      <c r="H48" s="376"/>
-      <c r="I48" s="376"/>
-      <c r="J48" s="376"/>
+      <c r="E48" s="348"/>
+      <c r="F48" s="348"/>
+      <c r="G48" s="348"/>
+      <c r="H48" s="348"/>
+      <c r="I48" s="348"/>
+      <c r="J48" s="348"/>
     </row>
     <row r="49" spans="5:10">
-      <c r="E49" s="376"/>
-      <c r="F49" s="376"/>
-      <c r="G49" s="376"/>
-      <c r="H49" s="376"/>
-      <c r="I49" s="376"/>
-      <c r="J49" s="376"/>
+      <c r="E49" s="348"/>
+      <c r="F49" s="348"/>
+      <c r="G49" s="348"/>
+      <c r="H49" s="348"/>
+      <c r="I49" s="348"/>
+      <c r="J49" s="348"/>
     </row>
     <row r="50" spans="5:10">
-      <c r="E50" s="376"/>
-      <c r="F50" s="376"/>
-      <c r="G50" s="376"/>
-      <c r="H50" s="376"/>
-      <c r="I50" s="376"/>
-      <c r="J50" s="376"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
+      <c r="G50" s="348"/>
+      <c r="H50" s="348"/>
+      <c r="I50" s="348"/>
+      <c r="J50" s="348"/>
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="L22:U32"/>
+    <mergeCell ref="L37:U37"/>
+    <mergeCell ref="L47:U47"/>
+    <mergeCell ref="L38:U38"/>
+    <mergeCell ref="L39:U39"/>
+    <mergeCell ref="L40:U40"/>
+    <mergeCell ref="L41:U41"/>
+    <mergeCell ref="L42:U42"/>
+    <mergeCell ref="L43:U43"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="L45:U45"/>
+    <mergeCell ref="L46:U46"/>
+    <mergeCell ref="L20:U20"/>
+    <mergeCell ref="L21:U21"/>
+    <mergeCell ref="L12:U19"/>
+    <mergeCell ref="L9:U9"/>
+    <mergeCell ref="L10:U10"/>
+    <mergeCell ref="L11:U11"/>
+    <mergeCell ref="L1:U1"/>
+    <mergeCell ref="L5:U5"/>
+    <mergeCell ref="L6:U6"/>
+    <mergeCell ref="L7:U7"/>
+    <mergeCell ref="L8:U8"/>
+    <mergeCell ref="L2:U2"/>
+    <mergeCell ref="L3:U3"/>
+    <mergeCell ref="L4:U4"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B24:J25"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="B19:J19"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B4:J6"/>
     <mergeCell ref="B8:J8"/>
@@ -17440,48 +17575,6 @@
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B10:J11"/>
     <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="B19:J19"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B24:J25"/>
-    <mergeCell ref="L9:U9"/>
-    <mergeCell ref="L10:U10"/>
-    <mergeCell ref="L11:U11"/>
-    <mergeCell ref="L1:U1"/>
-    <mergeCell ref="L5:U5"/>
-    <mergeCell ref="L6:U6"/>
-    <mergeCell ref="L7:U7"/>
-    <mergeCell ref="L8:U8"/>
-    <mergeCell ref="L2:U2"/>
-    <mergeCell ref="L3:U3"/>
-    <mergeCell ref="L4:U4"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="L22:U32"/>
-    <mergeCell ref="L37:U37"/>
-    <mergeCell ref="L47:U47"/>
-    <mergeCell ref="L38:U38"/>
-    <mergeCell ref="L39:U39"/>
-    <mergeCell ref="L40:U40"/>
-    <mergeCell ref="L41:U41"/>
-    <mergeCell ref="L42:U42"/>
-    <mergeCell ref="L43:U43"/>
-    <mergeCell ref="B7:K7"/>
-    <mergeCell ref="L45:U45"/>
-    <mergeCell ref="L46:U46"/>
-    <mergeCell ref="L20:U20"/>
-    <mergeCell ref="L21:U21"/>
-    <mergeCell ref="L12:U19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L41" r:id="rId1"/>
@@ -18011,7 +18104,7 @@
       <c r="J20" s="204"/>
       <c r="K20" s="202"/>
       <c r="L20" s="391"/>
-      <c r="M20" s="343"/>
+      <c r="M20" s="350"/>
       <c r="N20" s="219">
         <v>-0.5</v>
       </c>
@@ -18828,7 +18921,7 @@
       <c r="J20" s="204"/>
       <c r="K20" s="202"/>
       <c r="L20" s="391"/>
-      <c r="M20" s="343"/>
+      <c r="M20" s="350"/>
       <c r="N20" s="235"/>
     </row>
     <row r="21" spans="1:14" ht="16.5">
@@ -19682,7 +19775,7 @@
       <c r="L20" s="204"/>
       <c r="M20" s="202"/>
       <c r="N20" s="391"/>
-      <c r="O20" s="343"/>
+      <c r="O20" s="350"/>
       <c r="P20" s="242"/>
     </row>
     <row r="21" spans="1:16" ht="16.5">
@@ -20873,16 +20966,16 @@
       </c>
     </row>
     <row r="41" spans="1:17">
-      <c r="N41" s="343"/>
-      <c r="O41" s="343"/>
-      <c r="P41" s="343"/>
-      <c r="Q41" s="343"/>
+      <c r="N41" s="350"/>
+      <c r="O41" s="350"/>
+      <c r="P41" s="350"/>
+      <c r="Q41" s="350"/>
     </row>
     <row r="42" spans="1:17">
-      <c r="N42" s="376"/>
-      <c r="O42" s="376"/>
-      <c r="P42" s="376"/>
-      <c r="Q42" s="376"/>
+      <c r="N42" s="348"/>
+      <c r="O42" s="348"/>
+      <c r="P42" s="348"/>
+      <c r="Q42" s="348"/>
     </row>
     <row r="43" spans="1:17">
       <c r="N43" s="76" t="s">
@@ -22449,16 +22542,16 @@
       </c>
     </row>
     <row r="41" spans="1:17">
-      <c r="N41" s="343"/>
-      <c r="O41" s="343"/>
-      <c r="P41" s="343"/>
-      <c r="Q41" s="343"/>
+      <c r="N41" s="350"/>
+      <c r="O41" s="350"/>
+      <c r="P41" s="350"/>
+      <c r="Q41" s="350"/>
     </row>
     <row r="42" spans="1:17">
-      <c r="N42" s="376"/>
-      <c r="O42" s="376"/>
-      <c r="P42" s="376"/>
-      <c r="Q42" s="376"/>
+      <c r="N42" s="348"/>
+      <c r="O42" s="348"/>
+      <c r="P42" s="348"/>
+      <c r="Q42" s="348"/>
     </row>
     <row r="43" spans="1:17">
       <c r="N43" s="266" t="s">
@@ -24793,7 +24886,7 @@
       <c r="I30" s="298"/>
       <c r="J30" s="298"/>
       <c r="K30" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="L30" s="385" t="s">
         <v>258</v>
@@ -25054,7 +25147,7 @@
         <v>216</v>
       </c>
       <c r="K1" s="338" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="L1" s="20" t="s">
         <v>2</v>
@@ -25065,7 +25158,7 @@
       </c>
       <c r="O1" s="335">
         <f>SUM(B3:B30)</f>
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="P1" s="384" t="s">
         <v>218</v>
@@ -25075,27 +25168,27 @@
     <row r="2" spans="1:17" ht="16.5">
       <c r="B2" s="298">
         <f>SUM(B3:B33)</f>
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C2" s="298">
         <f t="shared" ref="C2" si="0">SUM(C3:C33)</f>
-        <v>5.75</v>
+        <v>15.5</v>
       </c>
       <c r="D2" s="298">
         <f>SUM(D3:D33)</f>
-        <v>2.5</v>
+        <v>6.25</v>
       </c>
       <c r="E2" s="298">
         <f t="shared" ref="E2:H2" si="1">SUM(E3:E33)</f>
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="F2" s="298">
         <f>SUM(F3:F33)</f>
-        <v>16</v>
+        <v>23.75</v>
       </c>
       <c r="G2" s="298">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>25.5</v>
       </c>
       <c r="H2" s="298">
         <f t="shared" si="1"/>
@@ -25103,12 +25196,12 @@
       </c>
       <c r="I2" s="298">
         <f>SUM(I3:I30)/60</f>
-        <v>1.4166666666666667</v>
+        <v>3.4833333333333334</v>
       </c>
       <c r="J2" s="298"/>
       <c r="K2" s="287">
         <f>SUM(E2:G2)</f>
-        <v>18</v>
+        <v>56.05</v>
       </c>
       <c r="L2" s="337"/>
       <c r="M2" s="335" t="s">
@@ -25119,7 +25212,7 @@
       </c>
       <c r="O2" s="303">
         <f>SUM(C3:E30)</f>
-        <v>8.25</v>
+        <v>28.55</v>
       </c>
       <c r="P2" s="384"/>
       <c r="Q2" s="384"/>
@@ -25151,14 +25244,14 @@
       </c>
       <c r="M3" s="311">
         <f>SUM(M4:M28)</f>
-        <v>18</v>
+        <v>56.3</v>
       </c>
       <c r="N3" s="302" t="s">
         <v>16</v>
       </c>
       <c r="O3" s="302">
         <f>SUM(F3:H30)</f>
-        <v>3</v>
+        <v>34.25</v>
       </c>
       <c r="P3" s="335">
         <f>SUM(P4:P32)</f>
@@ -25182,7 +25275,9 @@
       <c r="L4" s="340" t="s">
         <v>219</v>
       </c>
-      <c r="M4" s="312"/>
+      <c r="M4" s="312">
+        <v>4.5</v>
+      </c>
       <c r="P4" s="335">
         <v>1.5</v>
       </c>
@@ -25212,7 +25307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="16.5">
+    <row r="6" spans="1:17" ht="30">
       <c r="A6" s="10">
         <v>46116</v>
       </c>
@@ -25233,11 +25328,11 @@
         <v>18</v>
       </c>
       <c r="J6" s="298" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="K6" s="337"/>
       <c r="L6" s="339" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="M6" s="313"/>
       <c r="N6" s="18" t="s">
@@ -25268,15 +25363,17 @@
         <v>30</v>
       </c>
       <c r="J7" s="337" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="K7" s="337" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L7" s="340" t="s">
-        <v>230</v>
-      </c>
-      <c r="M7" s="326"/>
+        <v>360</v>
+      </c>
+      <c r="M7" s="326">
+        <v>1.8</v>
+      </c>
       <c r="N7" s="305" t="s">
         <v>186</v>
       </c>
@@ -25305,12 +25402,14 @@
         <v>7</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="L8" s="340" t="s">
         <v>263</v>
       </c>
-      <c r="M8" s="327"/>
+      <c r="M8" s="327">
+        <v>0.5</v>
+      </c>
       <c r="N8" s="306" t="s">
         <v>189</v>
       </c>
@@ -25349,14 +25448,20 @@
       </c>
       <c r="B10" s="304"/>
       <c r="C10" s="300"/>
-      <c r="D10" s="300"/>
+      <c r="D10" s="300">
+        <v>1</v>
+      </c>
       <c r="E10" s="300"/>
       <c r="F10" s="300"/>
-      <c r="G10" s="298"/>
+      <c r="G10" s="298">
+        <v>5</v>
+      </c>
       <c r="H10" s="298"/>
       <c r="I10" s="317"/>
       <c r="J10" s="298"/>
-      <c r="K10" s="321"/>
+      <c r="K10" s="321" t="s">
+        <v>348</v>
+      </c>
       <c r="L10" s="340"/>
       <c r="M10" s="313"/>
       <c r="N10" s="307" t="s">
@@ -25375,11 +25480,15 @@
       <c r="D11" s="300"/>
       <c r="E11" s="300"/>
       <c r="F11" s="300"/>
-      <c r="G11" s="298"/>
+      <c r="G11" s="298">
+        <v>0.5</v>
+      </c>
       <c r="H11" s="298"/>
       <c r="I11" s="316"/>
       <c r="J11" s="298"/>
-      <c r="K11" s="322"/>
+      <c r="K11" s="322" t="s">
+        <v>349</v>
+      </c>
       <c r="L11" s="340"/>
       <c r="M11" s="313"/>
       <c r="N11" s="306" t="s">
@@ -25398,16 +25507,20 @@
       <c r="D12" s="269"/>
       <c r="E12" s="269"/>
       <c r="F12" s="269"/>
-      <c r="G12" s="269"/>
+      <c r="G12" s="269">
+        <v>4</v>
+      </c>
       <c r="H12" s="269"/>
       <c r="I12" s="269"/>
       <c r="J12" s="269"/>
-      <c r="K12" s="323"/>
+      <c r="K12" s="323" t="s">
+        <v>347</v>
+      </c>
       <c r="L12" s="340" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="M12" s="313">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="N12" s="335" t="s">
         <v>194</v>
@@ -25420,21 +25533,31 @@
       <c r="A13" s="10">
         <v>46123</v>
       </c>
-      <c r="B13" s="304"/>
-      <c r="C13" s="300"/>
+      <c r="B13" s="304">
+        <v>2</v>
+      </c>
+      <c r="C13" s="300">
+        <v>5</v>
+      </c>
       <c r="D13" s="300"/>
       <c r="E13" s="300"/>
       <c r="F13" s="300"/>
-      <c r="G13" s="298"/>
+      <c r="G13" s="298">
+        <v>5.5</v>
+      </c>
       <c r="H13" s="298"/>
       <c r="I13" s="298"/>
-      <c r="J13" s="298"/>
-      <c r="K13" s="322"/>
+      <c r="J13" s="298" t="s">
+        <v>345</v>
+      </c>
+      <c r="K13" s="322" t="s">
+        <v>346</v>
+      </c>
       <c r="L13" s="340" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="M13" s="313">
-        <v>1</v>
+        <v>3.25</v>
       </c>
       <c r="N13" s="306" t="s">
         <v>198</v>
@@ -25450,20 +25573,40 @@
       <c r="A14" s="10">
         <v>46124</v>
       </c>
-      <c r="B14" s="304"/>
-      <c r="C14" s="300"/>
-      <c r="D14" s="300"/>
-      <c r="E14" s="300"/>
-      <c r="F14" s="300"/>
-      <c r="G14" s="298"/>
+      <c r="B14" s="304">
+        <v>4</v>
+      </c>
+      <c r="C14" s="300">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="300">
+        <v>1</v>
+      </c>
+      <c r="E14" s="300">
+        <v>0.3</v>
+      </c>
+      <c r="F14" s="300">
+        <v>2.5</v>
+      </c>
+      <c r="G14" s="298">
+        <v>1</v>
+      </c>
       <c r="H14" s="298"/>
-      <c r="I14" s="298"/>
-      <c r="J14" s="298"/>
-      <c r="K14" s="324"/>
+      <c r="I14" s="298">
+        <v>30</v>
+      </c>
+      <c r="J14" s="298" t="s">
+        <v>354</v>
+      </c>
+      <c r="K14" s="324" t="s">
+        <v>356</v>
+      </c>
       <c r="L14" s="340" t="s">
-        <v>335</v>
-      </c>
-      <c r="M14" s="314"/>
+        <v>334</v>
+      </c>
+      <c r="M14" s="314">
+        <v>6</v>
+      </c>
       <c r="N14" s="59" t="s">
         <v>195</v>
       </c>
@@ -25475,15 +25618,27 @@
       <c r="A15" s="10">
         <v>46125</v>
       </c>
-      <c r="B15" s="304"/>
-      <c r="C15" s="300"/>
-      <c r="D15" s="300"/>
+      <c r="B15" s="304">
+        <v>3.5</v>
+      </c>
+      <c r="C15" s="300">
+        <v>0.25</v>
+      </c>
+      <c r="D15" s="300">
+        <v>0.25</v>
+      </c>
       <c r="E15" s="300"/>
-      <c r="F15" s="300"/>
-      <c r="G15" s="298"/>
+      <c r="F15" s="300">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="298">
+        <v>1</v>
+      </c>
       <c r="H15" s="298"/>
       <c r="I15" s="298"/>
-      <c r="J15" s="298"/>
+      <c r="J15" s="298" t="s">
+        <v>352</v>
+      </c>
       <c r="K15" s="324"/>
       <c r="L15" s="340" t="s">
         <v>259</v>
@@ -25500,18 +25655,32 @@
       <c r="A16" s="10">
         <v>46126</v>
       </c>
-      <c r="B16" s="304"/>
-      <c r="C16" s="300"/>
-      <c r="D16" s="300"/>
+      <c r="B16" s="304">
+        <v>2</v>
+      </c>
+      <c r="C16" s="300">
+        <v>0.25</v>
+      </c>
+      <c r="D16" s="300">
+        <v>1</v>
+      </c>
       <c r="E16" s="300"/>
-      <c r="F16" s="300"/>
+      <c r="F16" s="300">
+        <v>1.25</v>
+      </c>
       <c r="G16" s="298"/>
       <c r="H16" s="298"/>
-      <c r="I16" s="298"/>
-      <c r="J16" s="298"/>
-      <c r="K16" s="324"/>
+      <c r="I16" s="298">
+        <v>27</v>
+      </c>
+      <c r="J16" s="298" t="s">
+        <v>350</v>
+      </c>
+      <c r="K16" s="324" t="s">
+        <v>351</v>
+      </c>
       <c r="L16" s="340" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="M16" s="313">
         <v>0.5</v>
@@ -25540,7 +25709,9 @@
       <c r="L17" s="340" t="s">
         <v>269</v>
       </c>
-      <c r="M17" s="313"/>
+      <c r="M17" s="313">
+        <v>1.5</v>
+      </c>
       <c r="N17" s="308" t="s">
         <v>200</v>
       </c>
@@ -25562,8 +25733,12 @@
       <c r="I18" s="298"/>
       <c r="J18" s="298"/>
       <c r="K18" s="324"/>
-      <c r="L18" s="340"/>
-      <c r="M18" s="313"/>
+      <c r="L18" s="340" t="s">
+        <v>344</v>
+      </c>
+      <c r="M18" s="313">
+        <v>5.5</v>
+      </c>
       <c r="N18" s="335" t="s">
         <v>130</v>
       </c>
@@ -25582,29 +25757,49 @@
       <c r="I19" s="298"/>
       <c r="J19" s="298"/>
       <c r="K19" s="325"/>
-      <c r="L19" s="340"/>
-      <c r="M19" s="326"/>
+      <c r="L19" s="340" t="s">
+        <v>353</v>
+      </c>
+      <c r="M19" s="326">
+        <v>8.5</v>
+      </c>
       <c r="N19" s="309"/>
       <c r="P19" s="336"/>
     </row>
-    <row r="20" spans="1:16" ht="16.5">
+    <row r="20" spans="1:16" ht="30.75">
       <c r="A20" s="10">
         <v>46130</v>
       </c>
-      <c r="B20" s="304"/>
-      <c r="C20" s="300"/>
+      <c r="B20" s="304">
+        <v>2</v>
+      </c>
+      <c r="C20" s="300">
+        <v>2.5</v>
+      </c>
       <c r="D20" s="300"/>
-      <c r="E20" s="300"/>
-      <c r="F20" s="298"/>
+      <c r="E20" s="300">
+        <v>5</v>
+      </c>
+      <c r="F20" s="298">
+        <v>2.5</v>
+      </c>
       <c r="G20" s="298"/>
       <c r="H20" s="298"/>
-      <c r="I20" s="298"/>
-      <c r="J20" s="298"/>
-      <c r="K20" s="319"/>
+      <c r="I20" s="298">
+        <v>10</v>
+      </c>
+      <c r="J20" s="298" t="s">
+        <v>361</v>
+      </c>
+      <c r="K20" s="319" t="s">
+        <v>359</v>
+      </c>
       <c r="L20" s="340" t="s">
         <v>301</v>
       </c>
-      <c r="M20" s="328"/>
+      <c r="M20" s="328">
+        <v>0.75</v>
+      </c>
       <c r="N20" s="310" t="s">
         <v>65</v>
       </c>
@@ -25617,18 +25812,40 @@
       <c r="A21" s="10">
         <v>46131</v>
       </c>
-      <c r="B21" s="304"/>
-      <c r="C21" s="300"/>
-      <c r="D21" s="300"/>
-      <c r="E21" s="300"/>
-      <c r="F21" s="298"/>
-      <c r="G21" s="298"/>
+      <c r="B21" s="304">
+        <v>2</v>
+      </c>
+      <c r="C21" s="300">
+        <v>0.25</v>
+      </c>
+      <c r="D21" s="300">
+        <v>0.5</v>
+      </c>
+      <c r="E21" s="300">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="298">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="298">
+        <v>3.75</v>
+      </c>
       <c r="H21" s="298"/>
-      <c r="I21" s="298"/>
-      <c r="J21" s="298"/>
-      <c r="K21" s="333"/>
-      <c r="L21" s="340"/>
-      <c r="M21" s="315"/>
+      <c r="I21" s="298">
+        <v>8</v>
+      </c>
+      <c r="J21" s="298" t="s">
+        <v>357</v>
+      </c>
+      <c r="K21" s="333" t="s">
+        <v>362</v>
+      </c>
+      <c r="L21" s="340" t="s">
+        <v>355</v>
+      </c>
+      <c r="M21" s="315">
+        <v>1</v>
+      </c>
       <c r="N21" s="310" t="s">
         <v>66</v>
       </c>
@@ -25641,18 +25858,38 @@
       <c r="A22" s="10">
         <v>46132</v>
       </c>
-      <c r="B22" s="304"/>
-      <c r="C22" s="300"/>
+      <c r="B22" s="304">
+        <v>3</v>
+      </c>
+      <c r="C22" s="300">
+        <v>1</v>
+      </c>
       <c r="D22" s="300"/>
-      <c r="E22" s="300"/>
-      <c r="F22" s="298"/>
-      <c r="G22" s="298"/>
+      <c r="E22" s="300">
+        <v>1</v>
+      </c>
+      <c r="F22" s="298">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="298">
+        <v>0.5</v>
+      </c>
       <c r="H22" s="298"/>
-      <c r="I22" s="298"/>
-      <c r="J22" s="298"/>
-      <c r="K22" s="296"/>
-      <c r="L22" s="341"/>
-      <c r="M22" s="334"/>
+      <c r="I22" s="298">
+        <v>31</v>
+      </c>
+      <c r="J22" s="298" t="s">
+        <v>364</v>
+      </c>
+      <c r="K22" s="296" t="s">
+        <v>365</v>
+      </c>
+      <c r="L22" s="341" t="s">
+        <v>363</v>
+      </c>
+      <c r="M22" s="334">
+        <v>3</v>
+      </c>
       <c r="N22" s="310" t="s">
         <v>96</v>
       </c>
@@ -25670,11 +25907,15 @@
       <c r="D23" s="300"/>
       <c r="E23" s="300"/>
       <c r="F23" s="298"/>
-      <c r="G23" s="298"/>
+      <c r="G23" s="298">
+        <v>2</v>
+      </c>
       <c r="H23" s="298"/>
       <c r="I23" s="298"/>
       <c r="J23" s="298"/>
-      <c r="K23" s="297"/>
+      <c r="K23" s="297" t="s">
+        <v>367</v>
+      </c>
       <c r="L23" s="340"/>
       <c r="M23" s="12"/>
       <c r="N23" s="212" t="s">
@@ -25689,15 +25930,23 @@
       <c r="A24" s="10">
         <v>46134</v>
       </c>
-      <c r="B24" s="304"/>
+      <c r="B24" s="304">
+        <v>4.5</v>
+      </c>
       <c r="C24" s="300"/>
       <c r="D24" s="300"/>
       <c r="E24" s="300"/>
       <c r="F24" s="298"/>
-      <c r="G24" s="298"/>
+      <c r="G24" s="298">
+        <v>0.25</v>
+      </c>
       <c r="H24" s="298"/>
-      <c r="I24" s="298"/>
-      <c r="J24" s="298"/>
+      <c r="I24" s="298">
+        <v>18</v>
+      </c>
+      <c r="J24" s="298" t="s">
+        <v>368</v>
+      </c>
       <c r="K24" s="5"/>
       <c r="L24" s="340" t="s">
         <v>214</v>

--- a/3.Study status-2026.xlsx
+++ b/3.Study status-2026.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="383">
   <si>
     <t>hours studied</t>
   </si>
@@ -1203,9 +1203,6 @@
     <t>sreact 16-21</t>
   </si>
   <si>
-    <t>kitchen , house work-, bathroom cleaning 0.5,water 1</t>
-  </si>
-  <si>
     <t>movies  - kerala stories 2, trance</t>
   </si>
   <si>
@@ -1215,13 +1212,31 @@
     <t>hospital-semn androgen, apollo blood test,kims tvs scan , claims -1</t>
   </si>
   <si>
-    <t>movie- trance,1- claims</t>
-  </si>
-  <si>
     <t>pure time waste like surfing</t>
   </si>
   <si>
     <t>1-movie , trance</t>
+  </si>
+  <si>
+    <t>preg book</t>
+  </si>
+  <si>
+    <t>movie- trance,1- claims,1-bathroom, house ,over youtube</t>
+  </si>
+  <si>
+    <t>react 10,11, aws145,146</t>
+  </si>
+  <si>
+    <t>aws 147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surfing </t>
+  </si>
+  <si>
+    <t>BCB-1.5</t>
+  </si>
+  <si>
+    <t>kitchen , house work-, bathroom cleaning 0.5,hc-0.5,water 0.25</t>
   </si>
 </sst>
 </file>
@@ -2989,49 +3004,41 @@
     <xf numFmtId="0" fontId="7" fillId="36" borderId="0" xfId="28">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="11" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="27" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="9" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" xfId="26" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="3" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3075,38 +3082,46 @@
     <xf numFmtId="0" fontId="27" fillId="11" borderId="16" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="27" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="9" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="11" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" xfId="26" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3165,7 +3180,19 @@
     <cellStyle name="Total" xfId="22" builtinId="25"/>
     <cellStyle name="yel-org" xfId="27"/>
   </cellStyles>
-  <dxfs count="83">
+  <dxfs count="84">
+    <dxf>
+      <fill>
+        <gradientFill type="path" left="0.5" right="0.5" top="0.5" bottom="0.5">
+          <stop position="0">
+            <color theme="0"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFFCC00"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4360,7 +4387,7 @@
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
     <tableStyle name="Table Style 1" pivot="0" count="0"/>
     <tableStyle name="Table Style 2" pivot="0" count="1">
-      <tableStyleElement type="secondRowStripe" dxfId="82"/>
+      <tableStyleElement type="secondRowStripe" dxfId="83"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -4690,11 +4717,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="598075392"/>
-        <c:axId val="598069408"/>
+        <c:axId val="-229040448"/>
+        <c:axId val="-229026848"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="598075392"/>
+        <c:axId val="-229040448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4734,14 +4761,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598069408"/>
+        <c:crossAx val="-229026848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="598069408"/>
+        <c:axId val="-229026848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4789,7 +4816,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598075392"/>
+        <c:crossAx val="-229040448"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5080,11 +5107,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="636460720"/>
-        <c:axId val="636459088"/>
+        <c:axId val="-100370224"/>
+        <c:axId val="-100372400"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="636460720"/>
+        <c:axId val="-100370224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5124,14 +5151,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="636459088"/>
+        <c:crossAx val="-100372400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="636459088"/>
+        <c:axId val="-100372400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5179,7 +5206,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="636460720"/>
+        <c:crossAx val="-100370224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5476,11 +5503,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="636468880"/>
-        <c:axId val="636462896"/>
+        <c:axId val="-100368048"/>
+        <c:axId val="-100367504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="636468880"/>
+        <c:axId val="-100368048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5520,14 +5547,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="636462896"/>
+        <c:crossAx val="-100367504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="636462896"/>
+        <c:axId val="-100367504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5575,7 +5602,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="636468880"/>
+        <c:crossAx val="-100368048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5905,11 +5932,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="598083008"/>
-        <c:axId val="598071040"/>
+        <c:axId val="-229038816"/>
+        <c:axId val="-229038272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="598083008"/>
+        <c:axId val="-229038816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5949,14 +5976,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598071040"/>
+        <c:crossAx val="-229038272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="598071040"/>
+        <c:axId val="-229038272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6004,7 +6031,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598083008"/>
+        <c:crossAx val="-229038816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6352,11 +6379,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="598075936"/>
-        <c:axId val="598077024"/>
+        <c:axId val="-229029568"/>
+        <c:axId val="-229037728"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="598075936"/>
+        <c:axId val="-229029568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6396,14 +6423,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598077024"/>
+        <c:crossAx val="-229037728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="598077024"/>
+        <c:axId val="-229037728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6451,7 +6478,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598075936"/>
+        <c:crossAx val="-229029568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6501,6 +6528,444 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="31750" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="35000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'4.apr'!$A$3:$A$30</c:f>
+              <c:numCache>
+                <c:formatCode>d\-mmm</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46116</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46117</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46118</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46119</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46121</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46123</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46124</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46128</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46130</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46131</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46132</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46134</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46137</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46138</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46140</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'4.apr'!$B$3:$B$30</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="-229037184"/>
+        <c:axId val="-229035008"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="-229037184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="d\-mmm" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-229035008"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="-229035008"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="-229037184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6626,156 +7091,111 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'4.apr'!$A$3:$A$30</c:f>
+              <c:f>'5.may'!$A$3:$A$30</c:f>
               <c:numCache>
                 <c:formatCode>d\-mmm</c:formatCode>
                 <c:ptCount val="28"/>
                 <c:pt idx="0">
-                  <c:v>46113</c:v>
+                  <c:v>46143</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46114</c:v>
+                  <c:v>46144</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46115</c:v>
+                  <c:v>46145</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46116</c:v>
+                  <c:v>46146</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46117</c:v>
+                  <c:v>46147</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46118</c:v>
+                  <c:v>46148</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46119</c:v>
+                  <c:v>46149</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46120</c:v>
+                  <c:v>46150</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46121</c:v>
+                  <c:v>46151</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46122</c:v>
+                  <c:v>46152</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>46123</c:v>
+                  <c:v>46153</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>46124</c:v>
+                  <c:v>46154</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>46125</c:v>
+                  <c:v>46155</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46126</c:v>
+                  <c:v>46156</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>46127</c:v>
+                  <c:v>46157</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>46128</c:v>
+                  <c:v>46158</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>46129</c:v>
+                  <c:v>46159</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>46130</c:v>
+                  <c:v>46160</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46131</c:v>
+                  <c:v>46161</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>46132</c:v>
+                  <c:v>46162</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>46133</c:v>
+                  <c:v>46163</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46134</c:v>
+                  <c:v>46164</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>46135</c:v>
+                  <c:v>46165</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>46136</c:v>
+                  <c:v>46166</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>46137</c:v>
+                  <c:v>46167</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>46138</c:v>
+                  <c:v>46168</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>46139</c:v>
+                  <c:v>46169</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>46140</c:v>
+                  <c:v>46170</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'4.apr'!$B$3:$B$30</c:f>
+              <c:f>'5.may'!$B$3:$B$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="28"/>
                 <c:pt idx="0">
-                  <c:v>4.5</c:v>
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>3.5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="20">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2.25</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>3.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6792,11 +7212,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="598077568"/>
-        <c:axId val="598072672"/>
+        <c:axId val="-229033376"/>
+        <c:axId val="-229030656"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="598077568"/>
+        <c:axId val="-229033376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6836,14 +7256,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598072672"/>
+        <c:crossAx val="-229030656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="598072672"/>
+        <c:axId val="-229030656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6891,394 +7311,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598077568"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx2">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx2"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="31750" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="35000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx2"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="tx2">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>'5.may'!$A$3:$A$30</c:f>
-              <c:numCache>
-                <c:formatCode>d\-mmm</c:formatCode>
-                <c:ptCount val="28"/>
-                <c:pt idx="0">
-                  <c:v>46113</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>46114</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>46115</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>46116</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>46117</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>46118</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>46119</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>46120</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>46121</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>46122</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>46123</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>46124</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>46125</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>46126</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>46127</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>46128</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>46129</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>46130</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>46131</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>46132</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>46133</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>46134</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>46135</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>46136</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>46137</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>46138</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>46139</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>46140</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'5.may'!$B$3:$B$30</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
-                <c:pt idx="0">
-                  <c:v>3.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="ctr"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="598079200"/>
-        <c:axId val="598082464"/>
-      </c:lineChart>
-      <c:dateAx>
-        <c:axId val="598079200"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="d\-mmm" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx2">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx2"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="598082464"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="days"/>
-      </c:dateAx>
-      <c:valAx>
-        <c:axId val="598082464"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx2">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx2"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="598079200"/>
+        <c:crossAx val="-229033376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7572,11 +7605,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="598080832"/>
-        <c:axId val="598081376"/>
+        <c:axId val="-100375120"/>
+        <c:axId val="-100371856"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="598080832"/>
+        <c:axId val="-100375120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7616,14 +7649,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598081376"/>
+        <c:crossAx val="-100371856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="598081376"/>
+        <c:axId val="-100371856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7671,7 +7704,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="598080832"/>
+        <c:crossAx val="-100375120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7965,11 +7998,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="636465616"/>
-        <c:axId val="636461808"/>
+        <c:axId val="-100380560"/>
+        <c:axId val="-100377840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="636465616"/>
+        <c:axId val="-100380560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8009,14 +8042,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="636461808"/>
+        <c:crossAx val="-100377840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="636461808"/>
+        <c:axId val="-100377840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8064,7 +8097,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="636465616"/>
+        <c:crossAx val="-100380560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8355,11 +8388,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="636466160"/>
-        <c:axId val="636466704"/>
+        <c:axId val="-100380016"/>
+        <c:axId val="-100374032"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="636466160"/>
+        <c:axId val="-100380016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8399,14 +8432,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="636466704"/>
+        <c:crossAx val="-100374032"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="636466704"/>
+        <c:axId val="-100374032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8454,7 +8487,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="636466160"/>
+        <c:crossAx val="-100380016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8748,11 +8781,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="636467792"/>
-        <c:axId val="636469968"/>
+        <c:axId val="-100368592"/>
+        <c:axId val="-100376208"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="636467792"/>
+        <c:axId val="-100368592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8792,14 +8825,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="636469968"/>
+        <c:crossAx val="-100376208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="636469968"/>
+        <c:axId val="-100376208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8847,7 +8880,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="636467792"/>
+        <c:crossAx val="-100368592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14890,7 +14923,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="L3:L23" totalsRowShown="0" headerRowDxfId="74" tableBorderDxfId="73" dataCellStyle="Style 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="L3:L23" totalsRowShown="0" headerRowDxfId="75" tableBorderDxfId="74" dataCellStyle="Style 2">
   <autoFilter ref="L3:L23"/>
   <tableColumns count="1">
     <tableColumn id="1" name="Total wastage" dataCellStyle="Style 2"/>
@@ -14900,18 +14933,18 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table32356" displayName="Table32356" ref="L3:M25" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3" tableBorderDxfId="2" dataCellStyle="40% - Accent4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table32356" displayName="Table32356" ref="L3:M25" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4" tableBorderDxfId="3" dataCellStyle="40% - Accent4">
   <autoFilter ref="L3:M25"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Column1" dataDxfId="1" dataCellStyle="40% - Accent4"/>
-    <tableColumn id="2" name="Column2" dataDxfId="0" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="1" name="Column1" dataDxfId="2" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="2" name="Column2" dataDxfId="1" dataCellStyle="40% - Accent4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table32" displayName="Table32" ref="L3:L23" totalsRowShown="0" headerRowDxfId="69" tableBorderDxfId="68" dataCellStyle="Style 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table32" displayName="Table32" ref="L3:L23" totalsRowShown="0" headerRowDxfId="70" tableBorderDxfId="69" dataCellStyle="Style 2">
   <autoFilter ref="L3:L23"/>
   <tableColumns count="1">
     <tableColumn id="1" name="Total wastage" dataCellStyle="Style 2"/>
@@ -14921,75 +14954,75 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table323" displayName="Table323" ref="L3:L23" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" tableBorderDxfId="62" dataCellStyle="yel-org">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table323" displayName="Table323" ref="L3:L23" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64" tableBorderDxfId="63" dataCellStyle="yel-org">
   <autoFilter ref="L3:L23"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="Total wastage" dataDxfId="61" dataCellStyle="yel-org"/>
+    <tableColumn id="1" name="Total wastage" dataDxfId="62" dataCellStyle="yel-org"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium28" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table32313" displayName="Table32313" ref="L3:L23" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56" tableBorderDxfId="55" dataCellStyle="yel-org">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table32313" displayName="Table32313" ref="L3:L23" totalsRowShown="0" headerRowDxfId="58" dataDxfId="57" tableBorderDxfId="56" dataCellStyle="yel-org">
   <autoFilter ref="L3:L23"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="Total wastage" dataDxfId="54" dataCellStyle="yel-org"/>
+    <tableColumn id="1" name="Total wastage" dataDxfId="55" dataCellStyle="yel-org"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium28" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table323568" displayName="Table323568" ref="J3:K25" totalsRowShown="0" headerRowDxfId="49" dataDxfId="48" tableBorderDxfId="47" dataCellStyle="40% - Accent4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table323568" displayName="Table323568" ref="J3:K25" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49" tableBorderDxfId="48" dataCellStyle="40% - Accent4">
   <autoFilter ref="J3:K25"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Column1" dataDxfId="46" dataCellStyle="40% - Accent4"/>
-    <tableColumn id="2" name="Column2" dataDxfId="45" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="1" name="Column1" dataDxfId="47" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="2" name="Column2" dataDxfId="46" dataCellStyle="40% - Accent4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table323569" displayName="Table323569" ref="J3:K25" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" tableBorderDxfId="38" dataCellStyle="40% - Accent4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table323569" displayName="Table323569" ref="J3:K25" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40" tableBorderDxfId="39" dataCellStyle="40% - Accent4">
   <autoFilter ref="J3:K25"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Column1" dataDxfId="37" dataCellStyle="40% - Accent4"/>
-    <tableColumn id="2" name="Column2" dataDxfId="36" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="1" name="Column1" dataDxfId="38" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="2" name="Column2" dataDxfId="37" dataCellStyle="40% - Accent4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table3235610" displayName="Table3235610" ref="J3:K25" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" tableBorderDxfId="29" dataCellStyle="40% - Accent4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table3235610" displayName="Table3235610" ref="J3:K25" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30" dataCellStyle="40% - Accent4">
   <autoFilter ref="J3:K25"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Column1" dataDxfId="28" dataCellStyle="40% - Accent4"/>
-    <tableColumn id="2" name="Column2" dataDxfId="27" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="1" name="Column1" dataDxfId="29" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="2" name="Column2" dataDxfId="28" dataCellStyle="40% - Accent4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table3235611" displayName="Table3235611" ref="J3:K25" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" tableBorderDxfId="20" dataCellStyle="40% - Accent4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table3235611" displayName="Table3235611" ref="J3:K25" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21" dataCellStyle="40% - Accent4">
   <autoFilter ref="J3:K25"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Column1" dataDxfId="19" dataCellStyle="40% - Accent4"/>
-    <tableColumn id="2" name="Column2" dataDxfId="18" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="1" name="Column1" dataDxfId="20" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="2" name="Column2" dataDxfId="19" dataCellStyle="40% - Accent4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table3235612" displayName="Table3235612" ref="L3:M25" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" tableBorderDxfId="11" dataCellStyle="40% - Accent4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table3235612" displayName="Table3235612" ref="L3:M25" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12" dataCellStyle="40% - Accent4">
   <autoFilter ref="L3:M25"/>
   <tableColumns count="2">
-    <tableColumn id="1" name="Column1" dataDxfId="10" dataCellStyle="40% - Accent4"/>
-    <tableColumn id="2" name="Column2" dataDxfId="9" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="1" name="Column1" dataDxfId="11" dataCellStyle="40% - Accent4"/>
+    <tableColumn id="2" name="Column2" dataDxfId="10" dataCellStyle="40% - Accent4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15294,988 +15327,1030 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:21" ht="16.5">
-      <c r="B1" s="308" t="s">
+      <c r="B1" s="301" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="308"/>
-      <c r="D1" s="308"/>
-      <c r="E1" s="308"/>
-      <c r="F1" s="308"/>
-      <c r="G1" s="308"/>
-      <c r="H1" s="308"/>
-      <c r="I1" s="308"/>
-      <c r="J1" s="308"/>
-      <c r="L1" s="331" t="s">
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="301"/>
+      <c r="F1" s="301"/>
+      <c r="G1" s="301"/>
+      <c r="H1" s="301"/>
+      <c r="I1" s="301"/>
+      <c r="J1" s="301"/>
+      <c r="L1" s="306" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="331"/>
-      <c r="N1" s="331"/>
-      <c r="O1" s="331"/>
-      <c r="P1" s="331"/>
-      <c r="Q1" s="331"/>
-      <c r="R1" s="331"/>
-      <c r="S1" s="331"/>
-      <c r="T1" s="331"/>
-      <c r="U1" s="331"/>
+      <c r="M1" s="306"/>
+      <c r="N1" s="306"/>
+      <c r="O1" s="306"/>
+      <c r="P1" s="306"/>
+      <c r="Q1" s="306"/>
+      <c r="R1" s="306"/>
+      <c r="S1" s="306"/>
+      <c r="T1" s="306"/>
+      <c r="U1" s="306"/>
     </row>
     <row r="2" spans="2:21" ht="16.5">
-      <c r="B2" s="301" t="s">
+      <c r="B2" s="331" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="301"/>
-      <c r="D2" s="301"/>
-      <c r="E2" s="301"/>
-      <c r="F2" s="301"/>
-      <c r="G2" s="301"/>
-      <c r="H2" s="301"/>
-      <c r="I2" s="301"/>
-      <c r="J2" s="301"/>
-      <c r="L2" s="335" t="s">
+      <c r="C2" s="331"/>
+      <c r="D2" s="331"/>
+      <c r="E2" s="331"/>
+      <c r="F2" s="331"/>
+      <c r="G2" s="331"/>
+      <c r="H2" s="331"/>
+      <c r="I2" s="331"/>
+      <c r="J2" s="331"/>
+      <c r="L2" s="310" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="336"/>
-      <c r="N2" s="336"/>
-      <c r="O2" s="336"/>
-      <c r="P2" s="336"/>
-      <c r="Q2" s="336"/>
-      <c r="R2" s="336"/>
-      <c r="S2" s="336"/>
-      <c r="T2" s="336"/>
-      <c r="U2" s="336"/>
+      <c r="M2" s="311"/>
+      <c r="N2" s="311"/>
+      <c r="O2" s="311"/>
+      <c r="P2" s="311"/>
+      <c r="Q2" s="311"/>
+      <c r="R2" s="311"/>
+      <c r="S2" s="311"/>
+      <c r="T2" s="311"/>
+      <c r="U2" s="311"/>
     </row>
     <row r="3" spans="2:21">
-      <c r="B3" s="310" t="s">
+      <c r="B3" s="338" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="310"/>
-      <c r="D3" s="310"/>
-      <c r="E3" s="310"/>
-      <c r="F3" s="310"/>
-      <c r="G3" s="310"/>
-      <c r="H3" s="310"/>
-      <c r="I3" s="310"/>
-      <c r="J3" s="310"/>
+      <c r="C3" s="338"/>
+      <c r="D3" s="338"/>
+      <c r="E3" s="338"/>
+      <c r="F3" s="338"/>
+      <c r="G3" s="338"/>
+      <c r="H3" s="338"/>
+      <c r="I3" s="338"/>
+      <c r="J3" s="338"/>
       <c r="K3" s="45"/>
-      <c r="L3" s="337" t="s">
+      <c r="L3" s="312" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="337"/>
-      <c r="N3" s="337"/>
-      <c r="O3" s="337"/>
-      <c r="P3" s="337"/>
-      <c r="Q3" s="337"/>
-      <c r="R3" s="337"/>
-      <c r="S3" s="337"/>
-      <c r="T3" s="337"/>
-      <c r="U3" s="337"/>
+      <c r="M3" s="312"/>
+      <c r="N3" s="312"/>
+      <c r="O3" s="312"/>
+      <c r="P3" s="312"/>
+      <c r="Q3" s="312"/>
+      <c r="R3" s="312"/>
+      <c r="S3" s="312"/>
+      <c r="T3" s="312"/>
+      <c r="U3" s="312"/>
     </row>
     <row r="4" spans="2:21" ht="15" customHeight="1">
-      <c r="B4" s="302" t="s">
+      <c r="B4" s="332" t="s">
         <v>355</v>
       </c>
-      <c r="C4" s="302"/>
-      <c r="D4" s="302"/>
-      <c r="E4" s="302"/>
-      <c r="F4" s="302"/>
-      <c r="G4" s="302"/>
-      <c r="H4" s="302"/>
-      <c r="I4" s="302"/>
-      <c r="J4" s="302"/>
+      <c r="C4" s="332"/>
+      <c r="D4" s="332"/>
+      <c r="E4" s="332"/>
+      <c r="F4" s="332"/>
+      <c r="G4" s="332"/>
+      <c r="H4" s="332"/>
+      <c r="I4" s="332"/>
+      <c r="J4" s="332"/>
       <c r="K4" s="45"/>
-      <c r="L4" s="337"/>
-      <c r="M4" s="337"/>
-      <c r="N4" s="337"/>
-      <c r="O4" s="337"/>
-      <c r="P4" s="337"/>
-      <c r="Q4" s="337"/>
-      <c r="R4" s="337"/>
-      <c r="S4" s="337"/>
-      <c r="T4" s="337"/>
-      <c r="U4" s="337"/>
+      <c r="L4" s="312"/>
+      <c r="M4" s="312"/>
+      <c r="N4" s="312"/>
+      <c r="O4" s="312"/>
+      <c r="P4" s="312"/>
+      <c r="Q4" s="312"/>
+      <c r="R4" s="312"/>
+      <c r="S4" s="312"/>
+      <c r="T4" s="312"/>
+      <c r="U4" s="312"/>
     </row>
     <row r="5" spans="2:21" ht="15" customHeight="1">
-      <c r="B5" s="302"/>
-      <c r="C5" s="302"/>
-      <c r="D5" s="302"/>
-      <c r="E5" s="302"/>
-      <c r="F5" s="302"/>
-      <c r="G5" s="302"/>
-      <c r="H5" s="302"/>
-      <c r="I5" s="302"/>
-      <c r="J5" s="302"/>
+      <c r="B5" s="332"/>
+      <c r="C5" s="332"/>
+      <c r="D5" s="332"/>
+      <c r="E5" s="332"/>
+      <c r="F5" s="332"/>
+      <c r="G5" s="332"/>
+      <c r="H5" s="332"/>
+      <c r="I5" s="332"/>
+      <c r="J5" s="332"/>
       <c r="K5" s="45"/>
-      <c r="L5" s="308" t="s">
+      <c r="L5" s="301" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="308"/>
-      <c r="N5" s="308"/>
-      <c r="O5" s="308"/>
-      <c r="P5" s="308"/>
-      <c r="Q5" s="308"/>
-      <c r="R5" s="308"/>
-      <c r="S5" s="308"/>
-      <c r="T5" s="308"/>
-      <c r="U5" s="308"/>
+      <c r="M5" s="301"/>
+      <c r="N5" s="301"/>
+      <c r="O5" s="301"/>
+      <c r="P5" s="301"/>
+      <c r="Q5" s="301"/>
+      <c r="R5" s="301"/>
+      <c r="S5" s="301"/>
+      <c r="T5" s="301"/>
+      <c r="U5" s="301"/>
     </row>
     <row r="6" spans="2:21" ht="35.25" customHeight="1">
-      <c r="B6" s="302"/>
-      <c r="C6" s="302"/>
-      <c r="D6" s="302"/>
-      <c r="E6" s="302"/>
-      <c r="F6" s="302"/>
-      <c r="G6" s="302"/>
-      <c r="H6" s="302"/>
-      <c r="I6" s="302"/>
-      <c r="J6" s="302"/>
+      <c r="B6" s="332"/>
+      <c r="C6" s="332"/>
+      <c r="D6" s="332"/>
+      <c r="E6" s="332"/>
+      <c r="F6" s="332"/>
+      <c r="G6" s="332"/>
+      <c r="H6" s="332"/>
+      <c r="I6" s="332"/>
+      <c r="J6" s="332"/>
       <c r="K6" s="45"/>
-      <c r="L6" s="332" t="s">
+      <c r="L6" s="307" t="s">
         <v>147</v>
       </c>
-      <c r="M6" s="332"/>
-      <c r="N6" s="332"/>
-      <c r="O6" s="332"/>
-      <c r="P6" s="332"/>
-      <c r="Q6" s="332"/>
-      <c r="R6" s="332"/>
-      <c r="S6" s="332"/>
-      <c r="T6" s="332"/>
-      <c r="U6" s="332"/>
+      <c r="M6" s="307"/>
+      <c r="N6" s="307"/>
+      <c r="O6" s="307"/>
+      <c r="P6" s="307"/>
+      <c r="Q6" s="307"/>
+      <c r="R6" s="307"/>
+      <c r="S6" s="307"/>
+      <c r="T6" s="307"/>
+      <c r="U6" s="307"/>
     </row>
     <row r="7" spans="2:21" ht="15.75" thickBot="1">
-      <c r="B7" s="340" t="s">
+      <c r="B7" s="304" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="340"/>
-      <c r="D7" s="340"/>
-      <c r="E7" s="340"/>
-      <c r="F7" s="340"/>
-      <c r="G7" s="340"/>
-      <c r="H7" s="340"/>
-      <c r="I7" s="340"/>
-      <c r="J7" s="340"/>
-      <c r="K7" s="340"/>
-      <c r="L7" s="333" t="s">
+      <c r="C7" s="304"/>
+      <c r="D7" s="304"/>
+      <c r="E7" s="304"/>
+      <c r="F7" s="304"/>
+      <c r="G7" s="304"/>
+      <c r="H7" s="304"/>
+      <c r="I7" s="304"/>
+      <c r="J7" s="304"/>
+      <c r="K7" s="304"/>
+      <c r="L7" s="308" t="s">
         <v>362</v>
       </c>
-      <c r="M7" s="333"/>
-      <c r="N7" s="333"/>
-      <c r="O7" s="333"/>
-      <c r="P7" s="333"/>
-      <c r="Q7" s="333"/>
-      <c r="R7" s="333"/>
-      <c r="S7" s="333"/>
-      <c r="T7" s="333"/>
-      <c r="U7" s="333"/>
+      <c r="M7" s="308"/>
+      <c r="N7" s="308"/>
+      <c r="O7" s="308"/>
+      <c r="P7" s="308"/>
+      <c r="Q7" s="308"/>
+      <c r="R7" s="308"/>
+      <c r="S7" s="308"/>
+      <c r="T7" s="308"/>
+      <c r="U7" s="308"/>
     </row>
     <row r="8" spans="2:21" ht="88.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B8" s="303" t="s">
+      <c r="B8" s="333" t="s">
         <v>287</v>
       </c>
-      <c r="C8" s="303"/>
-      <c r="D8" s="303"/>
-      <c r="E8" s="303"/>
-      <c r="F8" s="303"/>
-      <c r="G8" s="303"/>
-      <c r="H8" s="303"/>
-      <c r="I8" s="303"/>
-      <c r="J8" s="303"/>
-      <c r="L8" s="334" t="s">
+      <c r="C8" s="333"/>
+      <c r="D8" s="333"/>
+      <c r="E8" s="333"/>
+      <c r="F8" s="333"/>
+      <c r="G8" s="333"/>
+      <c r="H8" s="333"/>
+      <c r="I8" s="333"/>
+      <c r="J8" s="333"/>
+      <c r="L8" s="309" t="s">
         <v>126</v>
       </c>
-      <c r="M8" s="334"/>
-      <c r="N8" s="334"/>
-      <c r="O8" s="334"/>
-      <c r="P8" s="334"/>
-      <c r="Q8" s="334"/>
-      <c r="R8" s="334"/>
-      <c r="S8" s="334"/>
-      <c r="T8" s="334"/>
-      <c r="U8" s="334"/>
+      <c r="M8" s="309"/>
+      <c r="N8" s="309"/>
+      <c r="O8" s="309"/>
+      <c r="P8" s="309"/>
+      <c r="Q8" s="309"/>
+      <c r="R8" s="309"/>
+      <c r="S8" s="309"/>
+      <c r="T8" s="309"/>
+      <c r="U8" s="309"/>
     </row>
     <row r="9" spans="2:21" ht="15.75" thickTop="1">
-      <c r="B9" s="304" t="s">
+      <c r="B9" s="334" t="s">
         <v>183</v>
       </c>
-      <c r="C9" s="304"/>
-      <c r="D9" s="304"/>
-      <c r="E9" s="304"/>
-      <c r="F9" s="304"/>
-      <c r="G9" s="304"/>
-      <c r="H9" s="304"/>
-      <c r="I9" s="304"/>
-      <c r="J9" s="304"/>
-      <c r="L9" s="308"/>
-      <c r="M9" s="308"/>
-      <c r="N9" s="308"/>
-      <c r="O9" s="308"/>
-      <c r="P9" s="308"/>
-      <c r="Q9" s="308"/>
-      <c r="R9" s="308"/>
-      <c r="S9" s="308"/>
-      <c r="T9" s="308"/>
-      <c r="U9" s="308"/>
+      <c r="C9" s="334"/>
+      <c r="D9" s="334"/>
+      <c r="E9" s="334"/>
+      <c r="F9" s="334"/>
+      <c r="G9" s="334"/>
+      <c r="H9" s="334"/>
+      <c r="I9" s="334"/>
+      <c r="J9" s="334"/>
+      <c r="L9" s="301"/>
+      <c r="M9" s="301"/>
+      <c r="N9" s="301"/>
+      <c r="O9" s="301"/>
+      <c r="P9" s="301"/>
+      <c r="Q9" s="301"/>
+      <c r="R9" s="301"/>
+      <c r="S9" s="301"/>
+      <c r="T9" s="301"/>
+      <c r="U9" s="301"/>
     </row>
     <row r="10" spans="2:21">
-      <c r="B10" s="311" t="s">
+      <c r="B10" s="339" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="312"/>
-      <c r="D10" s="312"/>
-      <c r="E10" s="312"/>
-      <c r="F10" s="312"/>
-      <c r="G10" s="312"/>
-      <c r="H10" s="312"/>
-      <c r="I10" s="312"/>
-      <c r="J10" s="312"/>
-      <c r="L10" s="308" t="s">
+      <c r="C10" s="340"/>
+      <c r="D10" s="340"/>
+      <c r="E10" s="340"/>
+      <c r="F10" s="340"/>
+      <c r="G10" s="340"/>
+      <c r="H10" s="340"/>
+      <c r="I10" s="340"/>
+      <c r="J10" s="340"/>
+      <c r="L10" s="301" t="s">
         <v>6</v>
       </c>
-      <c r="M10" s="308"/>
-      <c r="N10" s="308"/>
-      <c r="O10" s="308"/>
-      <c r="P10" s="308"/>
-      <c r="Q10" s="308"/>
-      <c r="R10" s="308"/>
-      <c r="S10" s="308"/>
-      <c r="T10" s="308"/>
-      <c r="U10" s="308"/>
+      <c r="M10" s="301"/>
+      <c r="N10" s="301"/>
+      <c r="O10" s="301"/>
+      <c r="P10" s="301"/>
+      <c r="Q10" s="301"/>
+      <c r="R10" s="301"/>
+      <c r="S10" s="301"/>
+      <c r="T10" s="301"/>
+      <c r="U10" s="301"/>
     </row>
     <row r="11" spans="2:21">
-      <c r="B11" s="312"/>
-      <c r="C11" s="312"/>
-      <c r="D11" s="312"/>
-      <c r="E11" s="312"/>
-      <c r="F11" s="312"/>
-      <c r="G11" s="312"/>
-      <c r="H11" s="312"/>
-      <c r="I11" s="312"/>
-      <c r="J11" s="312"/>
-      <c r="L11" s="308"/>
-      <c r="M11" s="308"/>
-      <c r="N11" s="308"/>
-      <c r="O11" s="308"/>
-      <c r="P11" s="308"/>
-      <c r="Q11" s="308"/>
-      <c r="R11" s="308"/>
-      <c r="S11" s="308"/>
-      <c r="T11" s="308"/>
-      <c r="U11" s="308"/>
+      <c r="B11" s="340"/>
+      <c r="C11" s="340"/>
+      <c r="D11" s="340"/>
+      <c r="E11" s="340"/>
+      <c r="F11" s="340"/>
+      <c r="G11" s="340"/>
+      <c r="H11" s="340"/>
+      <c r="I11" s="340"/>
+      <c r="J11" s="340"/>
+      <c r="L11" s="301"/>
+      <c r="M11" s="301"/>
+      <c r="N11" s="301"/>
+      <c r="O11" s="301"/>
+      <c r="P11" s="301"/>
+      <c r="Q11" s="301"/>
+      <c r="R11" s="301"/>
+      <c r="S11" s="301"/>
+      <c r="T11" s="301"/>
+      <c r="U11" s="301"/>
     </row>
     <row r="12" spans="2:21" ht="15" customHeight="1">
-      <c r="B12" s="313" t="s">
+      <c r="B12" s="341" t="s">
         <v>313</v>
       </c>
-      <c r="C12" s="313"/>
-      <c r="D12" s="313"/>
-      <c r="E12" s="313"/>
-      <c r="F12" s="313"/>
-      <c r="G12" s="313"/>
-      <c r="H12" s="313"/>
-      <c r="I12" s="313"/>
-      <c r="J12" s="313"/>
-      <c r="L12" s="341" t="s">
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
+      <c r="G12" s="341"/>
+      <c r="H12" s="341"/>
+      <c r="I12" s="341"/>
+      <c r="J12" s="341"/>
+      <c r="L12" s="305" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="341"/>
-      <c r="N12" s="341"/>
-      <c r="O12" s="341"/>
-      <c r="P12" s="341"/>
-      <c r="Q12" s="341"/>
-      <c r="R12" s="341"/>
-      <c r="S12" s="341"/>
-      <c r="T12" s="341"/>
-      <c r="U12" s="341"/>
+      <c r="M12" s="305"/>
+      <c r="N12" s="305"/>
+      <c r="O12" s="305"/>
+      <c r="P12" s="305"/>
+      <c r="Q12" s="305"/>
+      <c r="R12" s="305"/>
+      <c r="S12" s="305"/>
+      <c r="T12" s="305"/>
+      <c r="U12" s="305"/>
     </row>
     <row r="13" spans="2:21" ht="16.5">
-      <c r="B13" s="314"/>
-      <c r="C13" s="314"/>
-      <c r="D13" s="314"/>
-      <c r="E13" s="314"/>
-      <c r="F13" s="314"/>
-      <c r="G13" s="314"/>
-      <c r="H13" s="314"/>
-      <c r="I13" s="314"/>
-      <c r="J13" s="314"/>
-      <c r="L13" s="341"/>
-      <c r="M13" s="341"/>
-      <c r="N13" s="341"/>
-      <c r="O13" s="341"/>
-      <c r="P13" s="341"/>
-      <c r="Q13" s="341"/>
-      <c r="R13" s="341"/>
-      <c r="S13" s="341"/>
-      <c r="T13" s="341"/>
-      <c r="U13" s="341"/>
+      <c r="B13" s="327"/>
+      <c r="C13" s="327"/>
+      <c r="D13" s="327"/>
+      <c r="E13" s="327"/>
+      <c r="F13" s="327"/>
+      <c r="G13" s="327"/>
+      <c r="H13" s="327"/>
+      <c r="I13" s="327"/>
+      <c r="J13" s="327"/>
+      <c r="L13" s="305"/>
+      <c r="M13" s="305"/>
+      <c r="N13" s="305"/>
+      <c r="O13" s="305"/>
+      <c r="P13" s="305"/>
+      <c r="Q13" s="305"/>
+      <c r="R13" s="305"/>
+      <c r="S13" s="305"/>
+      <c r="T13" s="305"/>
+      <c r="U13" s="305"/>
     </row>
     <row r="14" spans="2:21" ht="16.5">
-      <c r="B14" s="315" t="s">
+      <c r="B14" s="328" t="s">
         <v>356</v>
       </c>
-      <c r="C14" s="315"/>
-      <c r="D14" s="315"/>
-      <c r="E14" s="315"/>
-      <c r="F14" s="315"/>
-      <c r="G14" s="315"/>
-      <c r="H14" s="315"/>
-      <c r="I14" s="315"/>
-      <c r="J14" s="315"/>
-      <c r="L14" s="341"/>
-      <c r="M14" s="341"/>
-      <c r="N14" s="341"/>
-      <c r="O14" s="341"/>
-      <c r="P14" s="341"/>
-      <c r="Q14" s="341"/>
-      <c r="R14" s="341"/>
-      <c r="S14" s="341"/>
-      <c r="T14" s="341"/>
-      <c r="U14" s="341"/>
+      <c r="C14" s="328"/>
+      <c r="D14" s="328"/>
+      <c r="E14" s="328"/>
+      <c r="F14" s="328"/>
+      <c r="G14" s="328"/>
+      <c r="H14" s="328"/>
+      <c r="I14" s="328"/>
+      <c r="J14" s="328"/>
+      <c r="L14" s="305"/>
+      <c r="M14" s="305"/>
+      <c r="N14" s="305"/>
+      <c r="O14" s="305"/>
+      <c r="P14" s="305"/>
+      <c r="Q14" s="305"/>
+      <c r="R14" s="305"/>
+      <c r="S14" s="305"/>
+      <c r="T14" s="305"/>
+      <c r="U14" s="305"/>
     </row>
     <row r="15" spans="2:21" ht="18">
-      <c r="B15" s="316" t="s">
+      <c r="B15" s="329" t="s">
         <v>140</v>
       </c>
-      <c r="C15" s="316"/>
-      <c r="D15" s="316"/>
-      <c r="E15" s="316"/>
-      <c r="F15" s="316"/>
-      <c r="G15" s="316"/>
-      <c r="H15" s="316"/>
-      <c r="I15" s="316"/>
-      <c r="J15" s="316"/>
-      <c r="L15" s="341"/>
-      <c r="M15" s="341"/>
-      <c r="N15" s="341"/>
-      <c r="O15" s="341"/>
-      <c r="P15" s="341"/>
-      <c r="Q15" s="341"/>
-      <c r="R15" s="341"/>
-      <c r="S15" s="341"/>
-      <c r="T15" s="341"/>
-      <c r="U15" s="341"/>
+      <c r="C15" s="329"/>
+      <c r="D15" s="329"/>
+      <c r="E15" s="329"/>
+      <c r="F15" s="329"/>
+      <c r="G15" s="329"/>
+      <c r="H15" s="329"/>
+      <c r="I15" s="329"/>
+      <c r="J15" s="329"/>
+      <c r="L15" s="305"/>
+      <c r="M15" s="305"/>
+      <c r="N15" s="305"/>
+      <c r="O15" s="305"/>
+      <c r="P15" s="305"/>
+      <c r="Q15" s="305"/>
+      <c r="R15" s="305"/>
+      <c r="S15" s="305"/>
+      <c r="T15" s="305"/>
+      <c r="U15" s="305"/>
     </row>
     <row r="16" spans="2:21" ht="18">
-      <c r="B16" s="316" t="s">
+      <c r="B16" s="329" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="316"/>
-      <c r="D16" s="316"/>
-      <c r="E16" s="316"/>
-      <c r="F16" s="316"/>
-      <c r="G16" s="316"/>
-      <c r="H16" s="316"/>
-      <c r="I16" s="316"/>
-      <c r="J16" s="316"/>
-      <c r="L16" s="341"/>
-      <c r="M16" s="341"/>
-      <c r="N16" s="341"/>
-      <c r="O16" s="341"/>
-      <c r="P16" s="341"/>
-      <c r="Q16" s="341"/>
-      <c r="R16" s="341"/>
-      <c r="S16" s="341"/>
-      <c r="T16" s="341"/>
-      <c r="U16" s="341"/>
+      <c r="C16" s="329"/>
+      <c r="D16" s="329"/>
+      <c r="E16" s="329"/>
+      <c r="F16" s="329"/>
+      <c r="G16" s="329"/>
+      <c r="H16" s="329"/>
+      <c r="I16" s="329"/>
+      <c r="J16" s="329"/>
+      <c r="L16" s="305"/>
+      <c r="M16" s="305"/>
+      <c r="N16" s="305"/>
+      <c r="O16" s="305"/>
+      <c r="P16" s="305"/>
+      <c r="Q16" s="305"/>
+      <c r="R16" s="305"/>
+      <c r="S16" s="305"/>
+      <c r="T16" s="305"/>
+      <c r="U16" s="305"/>
     </row>
     <row r="17" spans="2:21">
-      <c r="B17" s="308" t="s">
+      <c r="B17" s="301" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="308"/>
-      <c r="D17" s="308"/>
-      <c r="E17" s="308"/>
-      <c r="F17" s="308"/>
-      <c r="G17" s="308"/>
-      <c r="H17" s="308"/>
-      <c r="I17" s="308"/>
-      <c r="J17" s="308"/>
-      <c r="L17" s="341"/>
-      <c r="M17" s="341"/>
-      <c r="N17" s="341"/>
-      <c r="O17" s="341"/>
-      <c r="P17" s="341"/>
-      <c r="Q17" s="341"/>
-      <c r="R17" s="341"/>
-      <c r="S17" s="341"/>
-      <c r="T17" s="341"/>
-      <c r="U17" s="341"/>
+      <c r="C17" s="301"/>
+      <c r="D17" s="301"/>
+      <c r="E17" s="301"/>
+      <c r="F17" s="301"/>
+      <c r="G17" s="301"/>
+      <c r="H17" s="301"/>
+      <c r="I17" s="301"/>
+      <c r="J17" s="301"/>
+      <c r="L17" s="305"/>
+      <c r="M17" s="305"/>
+      <c r="N17" s="305"/>
+      <c r="O17" s="305"/>
+      <c r="P17" s="305"/>
+      <c r="Q17" s="305"/>
+      <c r="R17" s="305"/>
+      <c r="S17" s="305"/>
+      <c r="T17" s="305"/>
+      <c r="U17" s="305"/>
     </row>
     <row r="18" spans="2:21">
-      <c r="B18" s="309" t="s">
+      <c r="B18" s="330" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="309"/>
-      <c r="D18" s="309"/>
-      <c r="E18" s="309"/>
-      <c r="F18" s="309"/>
-      <c r="G18" s="309"/>
-      <c r="H18" s="309"/>
-      <c r="I18" s="309"/>
-      <c r="J18" s="309"/>
-      <c r="L18" s="341"/>
-      <c r="M18" s="341"/>
-      <c r="N18" s="341"/>
-      <c r="O18" s="341"/>
-      <c r="P18" s="341"/>
-      <c r="Q18" s="341"/>
-      <c r="R18" s="341"/>
-      <c r="S18" s="341"/>
-      <c r="T18" s="341"/>
-      <c r="U18" s="341"/>
+      <c r="C18" s="330"/>
+      <c r="D18" s="330"/>
+      <c r="E18" s="330"/>
+      <c r="F18" s="330"/>
+      <c r="G18" s="330"/>
+      <c r="H18" s="330"/>
+      <c r="I18" s="330"/>
+      <c r="J18" s="330"/>
+      <c r="L18" s="305"/>
+      <c r="M18" s="305"/>
+      <c r="N18" s="305"/>
+      <c r="O18" s="305"/>
+      <c r="P18" s="305"/>
+      <c r="Q18" s="305"/>
+      <c r="R18" s="305"/>
+      <c r="S18" s="305"/>
+      <c r="T18" s="305"/>
+      <c r="U18" s="305"/>
     </row>
     <row r="19" spans="2:21">
-      <c r="B19" s="309" t="s">
+      <c r="B19" s="330" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="309"/>
-      <c r="D19" s="309"/>
-      <c r="E19" s="309"/>
-      <c r="F19" s="309"/>
-      <c r="G19" s="309"/>
-      <c r="H19" s="309"/>
-      <c r="I19" s="309"/>
-      <c r="J19" s="309"/>
-      <c r="L19" s="341"/>
-      <c r="M19" s="341"/>
-      <c r="N19" s="341"/>
-      <c r="O19" s="341"/>
-      <c r="P19" s="341"/>
-      <c r="Q19" s="341"/>
-      <c r="R19" s="341"/>
-      <c r="S19" s="341"/>
-      <c r="T19" s="341"/>
-      <c r="U19" s="341"/>
+      <c r="C19" s="330"/>
+      <c r="D19" s="330"/>
+      <c r="E19" s="330"/>
+      <c r="F19" s="330"/>
+      <c r="G19" s="330"/>
+      <c r="H19" s="330"/>
+      <c r="I19" s="330"/>
+      <c r="J19" s="330"/>
+      <c r="L19" s="305"/>
+      <c r="M19" s="305"/>
+      <c r="N19" s="305"/>
+      <c r="O19" s="305"/>
+      <c r="P19" s="305"/>
+      <c r="Q19" s="305"/>
+      <c r="R19" s="305"/>
+      <c r="S19" s="305"/>
+      <c r="T19" s="305"/>
+      <c r="U19" s="305"/>
     </row>
     <row r="20" spans="2:21" ht="15" customHeight="1">
-      <c r="B20" s="308" t="s">
+      <c r="B20" s="301" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="308"/>
-      <c r="D20" s="308"/>
-      <c r="E20" s="308"/>
-      <c r="F20" s="308"/>
-      <c r="G20" s="308"/>
-      <c r="H20" s="308"/>
-      <c r="I20" s="308"/>
-      <c r="J20" s="308"/>
-      <c r="L20" s="308"/>
-      <c r="M20" s="308"/>
-      <c r="N20" s="308"/>
-      <c r="O20" s="308"/>
-      <c r="P20" s="308"/>
-      <c r="Q20" s="308"/>
-      <c r="R20" s="308"/>
-      <c r="S20" s="308"/>
-      <c r="T20" s="308"/>
-      <c r="U20" s="308"/>
+      <c r="C20" s="301"/>
+      <c r="D20" s="301"/>
+      <c r="E20" s="301"/>
+      <c r="F20" s="301"/>
+      <c r="G20" s="301"/>
+      <c r="H20" s="301"/>
+      <c r="I20" s="301"/>
+      <c r="J20" s="301"/>
+      <c r="L20" s="301"/>
+      <c r="M20" s="301"/>
+      <c r="N20" s="301"/>
+      <c r="O20" s="301"/>
+      <c r="P20" s="301"/>
+      <c r="Q20" s="301"/>
+      <c r="R20" s="301"/>
+      <c r="S20" s="301"/>
+      <c r="T20" s="301"/>
+      <c r="U20" s="301"/>
     </row>
     <row r="21" spans="2:21">
-      <c r="L21" s="308"/>
-      <c r="M21" s="308"/>
-      <c r="N21" s="308"/>
-      <c r="O21" s="308"/>
-      <c r="P21" s="308"/>
-      <c r="Q21" s="308"/>
-      <c r="R21" s="308"/>
-      <c r="S21" s="308"/>
-      <c r="T21" s="308"/>
-      <c r="U21" s="308"/>
+      <c r="L21" s="301"/>
+      <c r="M21" s="301"/>
+      <c r="N21" s="301"/>
+      <c r="O21" s="301"/>
+      <c r="P21" s="301"/>
+      <c r="Q21" s="301"/>
+      <c r="R21" s="301"/>
+      <c r="S21" s="301"/>
+      <c r="T21" s="301"/>
+      <c r="U21" s="301"/>
     </row>
     <row r="22" spans="2:21" ht="15" customHeight="1">
-      <c r="B22" s="308"/>
-      <c r="C22" s="308"/>
-      <c r="D22" s="308"/>
-      <c r="E22" s="308"/>
-      <c r="F22" s="308"/>
-      <c r="G22" s="308"/>
-      <c r="H22" s="308"/>
-      <c r="I22" s="308"/>
-      <c r="J22" s="308"/>
-      <c r="L22" s="338" t="s">
+      <c r="B22" s="301"/>
+      <c r="C22" s="301"/>
+      <c r="D22" s="301"/>
+      <c r="E22" s="301"/>
+      <c r="F22" s="301"/>
+      <c r="G22" s="301"/>
+      <c r="H22" s="301"/>
+      <c r="I22" s="301"/>
+      <c r="J22" s="301"/>
+      <c r="L22" s="302" t="s">
         <v>39</v>
       </c>
-      <c r="M22" s="338"/>
-      <c r="N22" s="338"/>
-      <c r="O22" s="338"/>
-      <c r="P22" s="338"/>
-      <c r="Q22" s="338"/>
-      <c r="R22" s="338"/>
-      <c r="S22" s="338"/>
-      <c r="T22" s="338"/>
-      <c r="U22" s="338"/>
+      <c r="M22" s="302"/>
+      <c r="N22" s="302"/>
+      <c r="O22" s="302"/>
+      <c r="P22" s="302"/>
+      <c r="Q22" s="302"/>
+      <c r="R22" s="302"/>
+      <c r="S22" s="302"/>
+      <c r="T22" s="302"/>
+      <c r="U22" s="302"/>
     </row>
     <row r="23" spans="2:21">
-      <c r="B23" s="308" t="s">
+      <c r="B23" s="301" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="308"/>
-      <c r="D23" s="308"/>
-      <c r="E23" s="308"/>
-      <c r="F23" s="308"/>
-      <c r="G23" s="308"/>
-      <c r="H23" s="308"/>
-      <c r="I23" s="308"/>
-      <c r="J23" s="308"/>
-      <c r="L23" s="338"/>
-      <c r="M23" s="338"/>
-      <c r="N23" s="338"/>
-      <c r="O23" s="338"/>
-      <c r="P23" s="338"/>
-      <c r="Q23" s="338"/>
-      <c r="R23" s="338"/>
-      <c r="S23" s="338"/>
-      <c r="T23" s="338"/>
-      <c r="U23" s="338"/>
+      <c r="C23" s="301"/>
+      <c r="D23" s="301"/>
+      <c r="E23" s="301"/>
+      <c r="F23" s="301"/>
+      <c r="G23" s="301"/>
+      <c r="H23" s="301"/>
+      <c r="I23" s="301"/>
+      <c r="J23" s="301"/>
+      <c r="L23" s="302"/>
+      <c r="M23" s="302"/>
+      <c r="N23" s="302"/>
+      <c r="O23" s="302"/>
+      <c r="P23" s="302"/>
+      <c r="Q23" s="302"/>
+      <c r="R23" s="302"/>
+      <c r="S23" s="302"/>
+      <c r="T23" s="302"/>
+      <c r="U23" s="302"/>
     </row>
     <row r="24" spans="2:21" ht="30" customHeight="1">
-      <c r="B24" s="325" t="s">
+      <c r="B24" s="321" t="s">
         <v>273</v>
       </c>
-      <c r="C24" s="326"/>
-      <c r="D24" s="326"/>
-      <c r="E24" s="326"/>
-      <c r="F24" s="326"/>
-      <c r="G24" s="326"/>
-      <c r="H24" s="326"/>
-      <c r="I24" s="326"/>
-      <c r="J24" s="327"/>
-      <c r="L24" s="338"/>
-      <c r="M24" s="338"/>
-      <c r="N24" s="338"/>
-      <c r="O24" s="338"/>
-      <c r="P24" s="338"/>
-      <c r="Q24" s="338"/>
-      <c r="R24" s="338"/>
-      <c r="S24" s="338"/>
-      <c r="T24" s="338"/>
-      <c r="U24" s="338"/>
+      <c r="C24" s="322"/>
+      <c r="D24" s="322"/>
+      <c r="E24" s="322"/>
+      <c r="F24" s="322"/>
+      <c r="G24" s="322"/>
+      <c r="H24" s="322"/>
+      <c r="I24" s="322"/>
+      <c r="J24" s="323"/>
+      <c r="L24" s="302"/>
+      <c r="M24" s="302"/>
+      <c r="N24" s="302"/>
+      <c r="O24" s="302"/>
+      <c r="P24" s="302"/>
+      <c r="Q24" s="302"/>
+      <c r="R24" s="302"/>
+      <c r="S24" s="302"/>
+      <c r="T24" s="302"/>
+      <c r="U24" s="302"/>
     </row>
     <row r="25" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B25" s="328"/>
-      <c r="C25" s="329"/>
-      <c r="D25" s="329"/>
-      <c r="E25" s="329"/>
-      <c r="F25" s="329"/>
-      <c r="G25" s="329"/>
-      <c r="H25" s="329"/>
-      <c r="I25" s="329"/>
-      <c r="J25" s="330"/>
-      <c r="L25" s="338"/>
-      <c r="M25" s="338"/>
-      <c r="N25" s="338"/>
-      <c r="O25" s="338"/>
-      <c r="P25" s="338"/>
-      <c r="Q25" s="338"/>
-      <c r="R25" s="338"/>
-      <c r="S25" s="338"/>
-      <c r="T25" s="338"/>
-      <c r="U25" s="338"/>
+      <c r="B25" s="324"/>
+      <c r="C25" s="325"/>
+      <c r="D25" s="325"/>
+      <c r="E25" s="325"/>
+      <c r="F25" s="325"/>
+      <c r="G25" s="325"/>
+      <c r="H25" s="325"/>
+      <c r="I25" s="325"/>
+      <c r="J25" s="326"/>
+      <c r="L25" s="302"/>
+      <c r="M25" s="302"/>
+      <c r="N25" s="302"/>
+      <c r="O25" s="302"/>
+      <c r="P25" s="302"/>
+      <c r="Q25" s="302"/>
+      <c r="R25" s="302"/>
+      <c r="S25" s="302"/>
+      <c r="T25" s="302"/>
+      <c r="U25" s="302"/>
     </row>
     <row r="26" spans="2:21" ht="15.75">
-      <c r="B26" s="317" t="s">
+      <c r="B26" s="313" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="318"/>
-      <c r="D26" s="318"/>
-      <c r="E26" s="318"/>
-      <c r="F26" s="318"/>
-      <c r="G26" s="318"/>
-      <c r="H26" s="318"/>
-      <c r="I26" s="318"/>
-      <c r="J26" s="319"/>
-      <c r="L26" s="338"/>
-      <c r="M26" s="338"/>
-      <c r="N26" s="338"/>
-      <c r="O26" s="338"/>
-      <c r="P26" s="338"/>
-      <c r="Q26" s="338"/>
-      <c r="R26" s="338"/>
-      <c r="S26" s="338"/>
-      <c r="T26" s="338"/>
-      <c r="U26" s="338"/>
+      <c r="C26" s="314"/>
+      <c r="D26" s="314"/>
+      <c r="E26" s="314"/>
+      <c r="F26" s="314"/>
+      <c r="G26" s="314"/>
+      <c r="H26" s="314"/>
+      <c r="I26" s="314"/>
+      <c r="J26" s="315"/>
+      <c r="L26" s="302"/>
+      <c r="M26" s="302"/>
+      <c r="N26" s="302"/>
+      <c r="O26" s="302"/>
+      <c r="P26" s="302"/>
+      <c r="Q26" s="302"/>
+      <c r="R26" s="302"/>
+      <c r="S26" s="302"/>
+      <c r="T26" s="302"/>
+      <c r="U26" s="302"/>
     </row>
     <row r="27" spans="2:21">
-      <c r="B27" s="320" t="s">
+      <c r="B27" s="316" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="321"/>
-      <c r="D27" s="321"/>
-      <c r="E27" s="321"/>
-      <c r="F27" s="321"/>
-      <c r="G27" s="321"/>
-      <c r="H27" s="321"/>
-      <c r="I27" s="321"/>
-      <c r="J27" s="322"/>
-      <c r="L27" s="338"/>
-      <c r="M27" s="338"/>
-      <c r="N27" s="338"/>
-      <c r="O27" s="338"/>
-      <c r="P27" s="338"/>
-      <c r="Q27" s="338"/>
-      <c r="R27" s="338"/>
-      <c r="S27" s="338"/>
-      <c r="T27" s="338"/>
-      <c r="U27" s="338"/>
+      <c r="C27" s="317"/>
+      <c r="D27" s="317"/>
+      <c r="E27" s="317"/>
+      <c r="F27" s="317"/>
+      <c r="G27" s="317"/>
+      <c r="H27" s="317"/>
+      <c r="I27" s="317"/>
+      <c r="J27" s="318"/>
+      <c r="L27" s="302"/>
+      <c r="M27" s="302"/>
+      <c r="N27" s="302"/>
+      <c r="O27" s="302"/>
+      <c r="P27" s="302"/>
+      <c r="Q27" s="302"/>
+      <c r="R27" s="302"/>
+      <c r="S27" s="302"/>
+      <c r="T27" s="302"/>
+      <c r="U27" s="302"/>
     </row>
     <row r="28" spans="2:21">
-      <c r="B28" s="323" t="s">
+      <c r="B28" s="319" t="s">
         <v>229</v>
       </c>
-      <c r="C28" s="323"/>
-      <c r="D28" s="323"/>
-      <c r="E28" s="323"/>
-      <c r="F28" s="323"/>
-      <c r="G28" s="323"/>
-      <c r="H28" s="323"/>
-      <c r="I28" s="323"/>
-      <c r="J28" s="323"/>
-      <c r="L28" s="338"/>
-      <c r="M28" s="338"/>
-      <c r="N28" s="338"/>
-      <c r="O28" s="338"/>
-      <c r="P28" s="338"/>
-      <c r="Q28" s="338"/>
-      <c r="R28" s="338"/>
-      <c r="S28" s="338"/>
-      <c r="T28" s="338"/>
-      <c r="U28" s="338"/>
+      <c r="C28" s="319"/>
+      <c r="D28" s="319"/>
+      <c r="E28" s="319"/>
+      <c r="F28" s="319"/>
+      <c r="G28" s="319"/>
+      <c r="H28" s="319"/>
+      <c r="I28" s="319"/>
+      <c r="J28" s="319"/>
+      <c r="L28" s="302"/>
+      <c r="M28" s="302"/>
+      <c r="N28" s="302"/>
+      <c r="O28" s="302"/>
+      <c r="P28" s="302"/>
+      <c r="Q28" s="302"/>
+      <c r="R28" s="302"/>
+      <c r="S28" s="302"/>
+      <c r="T28" s="302"/>
+      <c r="U28" s="302"/>
     </row>
     <row r="29" spans="2:21" ht="16.5">
-      <c r="B29" s="324" t="s">
+      <c r="B29" s="320" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="324"/>
-      <c r="D29" s="324"/>
-      <c r="E29" s="324"/>
-      <c r="F29" s="324"/>
-      <c r="G29" s="324"/>
-      <c r="H29" s="324"/>
-      <c r="I29" s="324"/>
-      <c r="J29" s="324"/>
-      <c r="L29" s="338"/>
-      <c r="M29" s="338"/>
-      <c r="N29" s="338"/>
-      <c r="O29" s="338"/>
-      <c r="P29" s="338"/>
-      <c r="Q29" s="338"/>
-      <c r="R29" s="338"/>
-      <c r="S29" s="338"/>
-      <c r="T29" s="338"/>
-      <c r="U29" s="338"/>
+      <c r="C29" s="320"/>
+      <c r="D29" s="320"/>
+      <c r="E29" s="320"/>
+      <c r="F29" s="320"/>
+      <c r="G29" s="320"/>
+      <c r="H29" s="320"/>
+      <c r="I29" s="320"/>
+      <c r="J29" s="320"/>
+      <c r="L29" s="302"/>
+      <c r="M29" s="302"/>
+      <c r="N29" s="302"/>
+      <c r="O29" s="302"/>
+      <c r="P29" s="302"/>
+      <c r="Q29" s="302"/>
+      <c r="R29" s="302"/>
+      <c r="S29" s="302"/>
+      <c r="T29" s="302"/>
+      <c r="U29" s="302"/>
     </row>
     <row r="30" spans="2:21">
-      <c r="B30" s="308" t="s">
+      <c r="B30" s="301" t="s">
         <v>366</v>
       </c>
-      <c r="C30" s="308"/>
-      <c r="D30" s="308"/>
-      <c r="E30" s="308"/>
-      <c r="F30" s="308"/>
-      <c r="G30" s="308"/>
-      <c r="H30" s="308"/>
-      <c r="I30" s="308"/>
-      <c r="J30" s="308"/>
-      <c r="L30" s="338"/>
-      <c r="M30" s="338"/>
-      <c r="N30" s="338"/>
-      <c r="O30" s="338"/>
-      <c r="P30" s="338"/>
-      <c r="Q30" s="338"/>
-      <c r="R30" s="338"/>
-      <c r="S30" s="338"/>
-      <c r="T30" s="338"/>
-      <c r="U30" s="338"/>
+      <c r="C30" s="301"/>
+      <c r="D30" s="301"/>
+      <c r="E30" s="301"/>
+      <c r="F30" s="301"/>
+      <c r="G30" s="301"/>
+      <c r="H30" s="301"/>
+      <c r="I30" s="301"/>
+      <c r="J30" s="301"/>
+      <c r="L30" s="302"/>
+      <c r="M30" s="302"/>
+      <c r="N30" s="302"/>
+      <c r="O30" s="302"/>
+      <c r="P30" s="302"/>
+      <c r="Q30" s="302"/>
+      <c r="R30" s="302"/>
+      <c r="S30" s="302"/>
+      <c r="T30" s="302"/>
+      <c r="U30" s="302"/>
     </row>
     <row r="31" spans="2:21">
-      <c r="B31" s="308" t="s">
+      <c r="B31" s="301" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="308"/>
-      <c r="D31" s="308"/>
-      <c r="E31" s="308"/>
-      <c r="F31" s="308"/>
-      <c r="G31" s="308"/>
-      <c r="H31" s="308"/>
-      <c r="I31" s="308"/>
-      <c r="J31" s="308"/>
-      <c r="L31" s="338"/>
-      <c r="M31" s="338"/>
-      <c r="N31" s="338"/>
-      <c r="O31" s="338"/>
-      <c r="P31" s="338"/>
-      <c r="Q31" s="338"/>
-      <c r="R31" s="338"/>
-      <c r="S31" s="338"/>
-      <c r="T31" s="338"/>
-      <c r="U31" s="338"/>
+      <c r="C31" s="301"/>
+      <c r="D31" s="301"/>
+      <c r="E31" s="301"/>
+      <c r="F31" s="301"/>
+      <c r="G31" s="301"/>
+      <c r="H31" s="301"/>
+      <c r="I31" s="301"/>
+      <c r="J31" s="301"/>
+      <c r="L31" s="302"/>
+      <c r="M31" s="302"/>
+      <c r="N31" s="302"/>
+      <c r="O31" s="302"/>
+      <c r="P31" s="302"/>
+      <c r="Q31" s="302"/>
+      <c r="R31" s="302"/>
+      <c r="S31" s="302"/>
+      <c r="T31" s="302"/>
+      <c r="U31" s="302"/>
     </row>
     <row r="32" spans="2:21">
-      <c r="B32" s="308" t="s">
+      <c r="B32" s="301" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="308"/>
-      <c r="D32" s="308"/>
-      <c r="E32" s="308"/>
-      <c r="F32" s="308"/>
-      <c r="G32" s="308"/>
-      <c r="H32" s="308"/>
-      <c r="I32" s="308"/>
-      <c r="J32" s="308"/>
-      <c r="L32" s="338"/>
-      <c r="M32" s="338"/>
-      <c r="N32" s="338"/>
-      <c r="O32" s="338"/>
-      <c r="P32" s="338"/>
-      <c r="Q32" s="338"/>
-      <c r="R32" s="338"/>
-      <c r="S32" s="338"/>
-      <c r="T32" s="338"/>
-      <c r="U32" s="338"/>
+      <c r="C32" s="301"/>
+      <c r="D32" s="301"/>
+      <c r="E32" s="301"/>
+      <c r="F32" s="301"/>
+      <c r="G32" s="301"/>
+      <c r="H32" s="301"/>
+      <c r="I32" s="301"/>
+      <c r="J32" s="301"/>
+      <c r="L32" s="302"/>
+      <c r="M32" s="302"/>
+      <c r="N32" s="302"/>
+      <c r="O32" s="302"/>
+      <c r="P32" s="302"/>
+      <c r="Q32" s="302"/>
+      <c r="R32" s="302"/>
+      <c r="S32" s="302"/>
+      <c r="T32" s="302"/>
+      <c r="U32" s="302"/>
     </row>
     <row r="34" spans="3:21">
-      <c r="C34" s="307" t="s">
+      <c r="C34" s="337" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="307"/>
+      <c r="D34" s="337"/>
       <c r="E34" s="27"/>
       <c r="G34" s="191" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="35" spans="3:21">
-      <c r="C35" s="307" t="s">
+      <c r="C35" s="337" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="307"/>
+      <c r="D35" s="337"/>
       <c r="E35" s="27"/>
       <c r="G35" s="191" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="36" spans="3:21">
-      <c r="C36" s="307" t="s">
+      <c r="C36" s="337" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="307"/>
+      <c r="D36" s="337"/>
       <c r="E36" s="27"/>
       <c r="G36" s="191" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="37" spans="3:21">
-      <c r="C37" s="307" t="s">
+      <c r="C37" s="337" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="307"/>
+      <c r="D37" s="337"/>
       <c r="E37" s="27"/>
       <c r="G37" s="191" t="s">
         <v>102</v>
       </c>
-      <c r="L37" s="308" t="s">
+      <c r="L37" s="301" t="s">
         <v>7</v>
       </c>
-      <c r="M37" s="308"/>
-      <c r="N37" s="308"/>
-      <c r="O37" s="308"/>
-      <c r="P37" s="308"/>
-      <c r="Q37" s="308"/>
-      <c r="R37" s="308"/>
-      <c r="S37" s="308"/>
-      <c r="T37" s="308"/>
-      <c r="U37" s="308"/>
+      <c r="M37" s="301"/>
+      <c r="N37" s="301"/>
+      <c r="O37" s="301"/>
+      <c r="P37" s="301"/>
+      <c r="Q37" s="301"/>
+      <c r="R37" s="301"/>
+      <c r="S37" s="301"/>
+      <c r="T37" s="301"/>
+      <c r="U37" s="301"/>
     </row>
     <row r="38" spans="3:21">
-      <c r="C38" s="307" t="s">
+      <c r="C38" s="337" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="307"/>
+      <c r="D38" s="337"/>
       <c r="E38" s="27"/>
-      <c r="L38" s="308" t="s">
+      <c r="L38" s="301" t="s">
         <v>8</v>
       </c>
-      <c r="M38" s="308"/>
-      <c r="N38" s="308"/>
-      <c r="O38" s="308"/>
-      <c r="P38" s="308"/>
-      <c r="Q38" s="308"/>
-      <c r="R38" s="308"/>
-      <c r="S38" s="308"/>
-      <c r="T38" s="308"/>
-      <c r="U38" s="308"/>
+      <c r="M38" s="301"/>
+      <c r="N38" s="301"/>
+      <c r="O38" s="301"/>
+      <c r="P38" s="301"/>
+      <c r="Q38" s="301"/>
+      <c r="R38" s="301"/>
+      <c r="S38" s="301"/>
+      <c r="T38" s="301"/>
+      <c r="U38" s="301"/>
     </row>
     <row r="39" spans="3:21">
-      <c r="L39" s="308" t="s">
+      <c r="L39" s="301" t="s">
         <v>9</v>
       </c>
-      <c r="M39" s="308"/>
-      <c r="N39" s="308"/>
-      <c r="O39" s="308"/>
-      <c r="P39" s="308"/>
-      <c r="Q39" s="308"/>
-      <c r="R39" s="308"/>
-      <c r="S39" s="308"/>
-      <c r="T39" s="308"/>
-      <c r="U39" s="308"/>
+      <c r="M39" s="301"/>
+      <c r="N39" s="301"/>
+      <c r="O39" s="301"/>
+      <c r="P39" s="301"/>
+      <c r="Q39" s="301"/>
+      <c r="R39" s="301"/>
+      <c r="S39" s="301"/>
+      <c r="T39" s="301"/>
+      <c r="U39" s="301"/>
     </row>
     <row r="40" spans="3:21">
-      <c r="L40" s="308" t="s">
+      <c r="L40" s="301" t="s">
         <v>11</v>
       </c>
-      <c r="M40" s="308"/>
-      <c r="N40" s="308"/>
-      <c r="O40" s="308"/>
-      <c r="P40" s="308"/>
-      <c r="Q40" s="308"/>
-      <c r="R40" s="308"/>
-      <c r="S40" s="308"/>
-      <c r="T40" s="308"/>
-      <c r="U40" s="308"/>
+      <c r="M40" s="301"/>
+      <c r="N40" s="301"/>
+      <c r="O40" s="301"/>
+      <c r="P40" s="301"/>
+      <c r="Q40" s="301"/>
+      <c r="R40" s="301"/>
+      <c r="S40" s="301"/>
+      <c r="T40" s="301"/>
+      <c r="U40" s="301"/>
     </row>
     <row r="41" spans="3:21">
-      <c r="E41" s="305" t="s">
+      <c r="E41" s="335" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="306"/>
-      <c r="G41" s="306"/>
-      <c r="H41" s="306"/>
-      <c r="I41" s="306"/>
-      <c r="J41" s="306"/>
-      <c r="L41" s="339" t="s">
+      <c r="F41" s="336"/>
+      <c r="G41" s="336"/>
+      <c r="H41" s="336"/>
+      <c r="I41" s="336"/>
+      <c r="J41" s="336"/>
+      <c r="L41" s="303" t="s">
         <v>18</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="308"/>
-      <c r="R41" s="308"/>
-      <c r="S41" s="308"/>
-      <c r="T41" s="308"/>
-      <c r="U41" s="308"/>
+      <c r="M41" s="301"/>
+      <c r="N41" s="301"/>
+      <c r="O41" s="301"/>
+      <c r="P41" s="301"/>
+      <c r="Q41" s="301"/>
+      <c r="R41" s="301"/>
+      <c r="S41" s="301"/>
+      <c r="T41" s="301"/>
+      <c r="U41" s="301"/>
     </row>
     <row r="42" spans="3:21">
-      <c r="E42" s="306"/>
-      <c r="F42" s="306"/>
-      <c r="G42" s="306"/>
-      <c r="H42" s="306"/>
-      <c r="I42" s="306"/>
-      <c r="J42" s="306"/>
-      <c r="L42" s="308"/>
-      <c r="M42" s="308"/>
-      <c r="N42" s="308"/>
-      <c r="O42" s="308"/>
-      <c r="P42" s="308"/>
-      <c r="Q42" s="308"/>
-      <c r="R42" s="308"/>
-      <c r="S42" s="308"/>
-      <c r="T42" s="308"/>
-      <c r="U42" s="308"/>
+      <c r="E42" s="336"/>
+      <c r="F42" s="336"/>
+      <c r="G42" s="336"/>
+      <c r="H42" s="336"/>
+      <c r="I42" s="336"/>
+      <c r="J42" s="336"/>
+      <c r="L42" s="301"/>
+      <c r="M42" s="301"/>
+      <c r="N42" s="301"/>
+      <c r="O42" s="301"/>
+      <c r="P42" s="301"/>
+      <c r="Q42" s="301"/>
+      <c r="R42" s="301"/>
+      <c r="S42" s="301"/>
+      <c r="T42" s="301"/>
+      <c r="U42" s="301"/>
     </row>
     <row r="43" spans="3:21">
-      <c r="E43" s="306"/>
-      <c r="F43" s="306"/>
-      <c r="G43" s="306"/>
-      <c r="H43" s="306"/>
-      <c r="I43" s="306"/>
-      <c r="J43" s="306"/>
-      <c r="L43" s="308"/>
-      <c r="M43" s="308"/>
-      <c r="N43" s="308"/>
-      <c r="O43" s="308"/>
-      <c r="P43" s="308"/>
-      <c r="Q43" s="308"/>
-      <c r="R43" s="308"/>
-      <c r="S43" s="308"/>
-      <c r="T43" s="308"/>
-      <c r="U43" s="308"/>
+      <c r="E43" s="336"/>
+      <c r="F43" s="336"/>
+      <c r="G43" s="336"/>
+      <c r="H43" s="336"/>
+      <c r="I43" s="336"/>
+      <c r="J43" s="336"/>
+      <c r="L43" s="301"/>
+      <c r="M43" s="301"/>
+      <c r="N43" s="301"/>
+      <c r="O43" s="301"/>
+      <c r="P43" s="301"/>
+      <c r="Q43" s="301"/>
+      <c r="R43" s="301"/>
+      <c r="S43" s="301"/>
+      <c r="T43" s="301"/>
+      <c r="U43" s="301"/>
     </row>
     <row r="44" spans="3:21">
-      <c r="E44" s="306"/>
-      <c r="F44" s="306"/>
-      <c r="G44" s="306"/>
-      <c r="H44" s="306"/>
-      <c r="I44" s="306"/>
-      <c r="J44" s="306"/>
+      <c r="E44" s="336"/>
+      <c r="F44" s="336"/>
+      <c r="G44" s="336"/>
+      <c r="H44" s="336"/>
+      <c r="I44" s="336"/>
+      <c r="J44" s="336"/>
     </row>
     <row r="45" spans="3:21">
-      <c r="E45" s="306"/>
-      <c r="F45" s="306"/>
-      <c r="G45" s="306"/>
-      <c r="H45" s="306"/>
-      <c r="I45" s="306"/>
-      <c r="J45" s="306"/>
-      <c r="L45" s="308"/>
-      <c r="M45" s="308"/>
-      <c r="N45" s="308"/>
-      <c r="O45" s="308"/>
-      <c r="P45" s="308"/>
-      <c r="Q45" s="308"/>
-      <c r="R45" s="308"/>
-      <c r="S45" s="308"/>
-      <c r="T45" s="308"/>
-      <c r="U45" s="308"/>
+      <c r="E45" s="336"/>
+      <c r="F45" s="336"/>
+      <c r="G45" s="336"/>
+      <c r="H45" s="336"/>
+      <c r="I45" s="336"/>
+      <c r="J45" s="336"/>
+      <c r="L45" s="301"/>
+      <c r="M45" s="301"/>
+      <c r="N45" s="301"/>
+      <c r="O45" s="301"/>
+      <c r="P45" s="301"/>
+      <c r="Q45" s="301"/>
+      <c r="R45" s="301"/>
+      <c r="S45" s="301"/>
+      <c r="T45" s="301"/>
+      <c r="U45" s="301"/>
     </row>
     <row r="46" spans="3:21">
-      <c r="E46" s="306"/>
-      <c r="F46" s="306"/>
-      <c r="G46" s="306"/>
-      <c r="H46" s="306"/>
-      <c r="I46" s="306"/>
-      <c r="J46" s="306"/>
-      <c r="L46" s="308"/>
-      <c r="M46" s="308"/>
-      <c r="N46" s="308"/>
-      <c r="O46" s="308"/>
-      <c r="P46" s="308"/>
-      <c r="Q46" s="308"/>
-      <c r="R46" s="308"/>
-      <c r="S46" s="308"/>
-      <c r="T46" s="308"/>
-      <c r="U46" s="308"/>
+      <c r="E46" s="336"/>
+      <c r="F46" s="336"/>
+      <c r="G46" s="336"/>
+      <c r="H46" s="336"/>
+      <c r="I46" s="336"/>
+      <c r="J46" s="336"/>
+      <c r="L46" s="301"/>
+      <c r="M46" s="301"/>
+      <c r="N46" s="301"/>
+      <c r="O46" s="301"/>
+      <c r="P46" s="301"/>
+      <c r="Q46" s="301"/>
+      <c r="R46" s="301"/>
+      <c r="S46" s="301"/>
+      <c r="T46" s="301"/>
+      <c r="U46" s="301"/>
     </row>
     <row r="47" spans="3:21">
-      <c r="E47" s="306"/>
-      <c r="F47" s="306"/>
-      <c r="G47" s="306"/>
-      <c r="H47" s="306"/>
-      <c r="I47" s="306"/>
-      <c r="J47" s="306"/>
-      <c r="L47" s="308"/>
-      <c r="M47" s="308"/>
-      <c r="N47" s="308"/>
-      <c r="O47" s="308"/>
-      <c r="P47" s="308"/>
-      <c r="Q47" s="308"/>
-      <c r="R47" s="308"/>
-      <c r="S47" s="308"/>
-      <c r="T47" s="308"/>
-      <c r="U47" s="308"/>
+      <c r="E47" s="336"/>
+      <c r="F47" s="336"/>
+      <c r="G47" s="336"/>
+      <c r="H47" s="336"/>
+      <c r="I47" s="336"/>
+      <c r="J47" s="336"/>
+      <c r="L47" s="301"/>
+      <c r="M47" s="301"/>
+      <c r="N47" s="301"/>
+      <c r="O47" s="301"/>
+      <c r="P47" s="301"/>
+      <c r="Q47" s="301"/>
+      <c r="R47" s="301"/>
+      <c r="S47" s="301"/>
+      <c r="T47" s="301"/>
+      <c r="U47" s="301"/>
     </row>
     <row r="48" spans="3:21">
-      <c r="E48" s="306"/>
-      <c r="F48" s="306"/>
-      <c r="G48" s="306"/>
-      <c r="H48" s="306"/>
-      <c r="I48" s="306"/>
-      <c r="J48" s="306"/>
+      <c r="E48" s="336"/>
+      <c r="F48" s="336"/>
+      <c r="G48" s="336"/>
+      <c r="H48" s="336"/>
+      <c r="I48" s="336"/>
+      <c r="J48" s="336"/>
     </row>
     <row r="49" spans="5:10">
-      <c r="E49" s="306"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
-      <c r="J49" s="306"/>
+      <c r="E49" s="336"/>
+      <c r="F49" s="336"/>
+      <c r="G49" s="336"/>
+      <c r="H49" s="336"/>
+      <c r="I49" s="336"/>
+      <c r="J49" s="336"/>
     </row>
     <row r="50" spans="5:10">
-      <c r="E50" s="306"/>
-      <c r="F50" s="306"/>
-      <c r="G50" s="306"/>
-      <c r="H50" s="306"/>
-      <c r="I50" s="306"/>
-      <c r="J50" s="306"/>
+      <c r="E50" s="336"/>
+      <c r="F50" s="336"/>
+      <c r="G50" s="336"/>
+      <c r="H50" s="336"/>
+      <c r="I50" s="336"/>
+      <c r="J50" s="336"/>
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B4:J6"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="E41:J50"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="B20:J20"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B10:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B24:J25"/>
+    <mergeCell ref="L9:U9"/>
+    <mergeCell ref="L10:U10"/>
+    <mergeCell ref="L11:U11"/>
+    <mergeCell ref="L1:U1"/>
+    <mergeCell ref="L5:U5"/>
+    <mergeCell ref="L6:U6"/>
+    <mergeCell ref="L7:U7"/>
+    <mergeCell ref="L8:U8"/>
+    <mergeCell ref="L2:U2"/>
+    <mergeCell ref="L3:U3"/>
+    <mergeCell ref="L4:U4"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="L22:U32"/>
     <mergeCell ref="L37:U37"/>
@@ -16292,48 +16367,6 @@
     <mergeCell ref="L20:U20"/>
     <mergeCell ref="L21:U21"/>
     <mergeCell ref="L12:U19"/>
-    <mergeCell ref="L9:U9"/>
-    <mergeCell ref="L10:U10"/>
-    <mergeCell ref="L11:U11"/>
-    <mergeCell ref="L1:U1"/>
-    <mergeCell ref="L5:U5"/>
-    <mergeCell ref="L6:U6"/>
-    <mergeCell ref="L7:U7"/>
-    <mergeCell ref="L8:U8"/>
-    <mergeCell ref="L2:U2"/>
-    <mergeCell ref="L3:U3"/>
-    <mergeCell ref="L4:U4"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B24:J25"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="B19:J19"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B4:J6"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="E41:J50"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="B20:J20"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B10:J11"/>
-    <mergeCell ref="B12:J12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L41" r:id="rId1"/>
@@ -16871,7 +16904,7 @@
       <c r="J20" s="157"/>
       <c r="K20" s="155"/>
       <c r="L20" s="349"/>
-      <c r="M20" s="308"/>
+      <c r="M20" s="301"/>
       <c r="N20" s="188"/>
     </row>
     <row r="21" spans="1:14" ht="16.5">
@@ -17128,19 +17161,19 @@
     <mergeCell ref="J28:N29"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:B4 B6:B33">
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="lessThan">
       <formula>$B$35</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="between">
       <formula>$B$35</formula>
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="greaterThan">
       <formula>$B$35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A34">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17725,7 +17758,7 @@
       <c r="L20" s="157"/>
       <c r="M20" s="155"/>
       <c r="N20" s="349"/>
-      <c r="O20" s="308"/>
+      <c r="O20" s="301"/>
       <c r="P20" s="195"/>
     </row>
     <row r="21" spans="1:16" ht="16.5">
@@ -18010,19 +18043,19 @@
     <mergeCell ref="L28:P29"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:B4 B6:B33">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="lessThan">
       <formula>$B$35</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="between">
       <formula>$B$35</formula>
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="greaterThan">
       <formula>$B$35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A34">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18916,16 +18949,16 @@
       </c>
     </row>
     <row r="41" spans="1:17">
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="308"/>
+      <c r="N41" s="301"/>
+      <c r="O41" s="301"/>
+      <c r="P41" s="301"/>
+      <c r="Q41" s="301"/>
     </row>
     <row r="42" spans="1:17">
-      <c r="N42" s="306"/>
-      <c r="O42" s="306"/>
-      <c r="P42" s="306"/>
-      <c r="Q42" s="306"/>
+      <c r="N42" s="336"/>
+      <c r="O42" s="336"/>
+      <c r="P42" s="336"/>
+      <c r="Q42" s="336"/>
     </row>
     <row r="43" spans="1:17">
       <c r="N43" s="46" t="s">
@@ -18971,19 +19004,19 @@
     <mergeCell ref="N42:Q42"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:B4 B6:B33">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="lessThan">
       <formula>$B$35</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="between">
       <formula>$B$35</formula>
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="greaterThan">
       <formula>$B$35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A34">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20492,16 +20525,16 @@
       </c>
     </row>
     <row r="41" spans="1:17">
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="308"/>
+      <c r="N41" s="301"/>
+      <c r="O41" s="301"/>
+      <c r="P41" s="301"/>
+      <c r="Q41" s="301"/>
     </row>
     <row r="42" spans="1:17">
-      <c r="N42" s="306"/>
-      <c r="O42" s="306"/>
-      <c r="P42" s="306"/>
-      <c r="Q42" s="306"/>
+      <c r="N42" s="336"/>
+      <c r="O42" s="336"/>
+      <c r="P42" s="336"/>
+      <c r="Q42" s="336"/>
     </row>
     <row r="43" spans="1:17">
       <c r="N43" s="219" t="s">
@@ -20547,19 +20580,19 @@
     <mergeCell ref="N42:Q42"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:B4 B6:B33">
-    <cfRule type="cellIs" dxfId="81" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="2" operator="lessThan">
       <formula>$B$35</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="81" priority="3" operator="between">
       <formula>$B$35</formula>
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="4" operator="greaterThan">
       <formula>$B$35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A34">
-    <cfRule type="expression" dxfId="78" priority="1">
+    <cfRule type="expression" dxfId="79" priority="1">
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21696,15 +21729,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B30">
-    <cfRule type="cellIs" dxfId="77" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="78" priority="3" operator="lessThan">
       <formula>$B$32</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="77" priority="4" operator="greaterThan">
       <formula>$B$32</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A30">
-    <cfRule type="expression" dxfId="75" priority="2">
+    <cfRule type="expression" dxfId="76" priority="2">
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23011,15 +23044,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B32">
-    <cfRule type="cellIs" dxfId="72" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="73" priority="3" operator="lessThan">
       <formula>$B$34</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="4" operator="greaterThan">
       <formula>$B$34</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A33">
-    <cfRule type="expression" dxfId="70" priority="2">
+    <cfRule type="expression" dxfId="71" priority="2">
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24298,15 +24331,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B32">
-    <cfRule type="cellIs" dxfId="67" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="3" operator="lessThan">
       <formula>$B$34</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="4" operator="greaterThan">
       <formula>$B$34</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A33">
-    <cfRule type="expression" dxfId="65" priority="2">
+    <cfRule type="expression" dxfId="66" priority="2">
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24343,7 +24376,7 @@
     <col min="7" max="7" width="9.140625" style="296"/>
     <col min="8" max="8" width="6.5703125" style="296" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" style="296" customWidth="1"/>
-    <col min="10" max="10" width="20.5703125" style="296" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" style="296" customWidth="1"/>
     <col min="11" max="11" width="47" style="296" customWidth="1"/>
     <col min="12" max="12" width="61.42578125" style="296" customWidth="1"/>
     <col min="13" max="13" width="12.5703125" style="296" customWidth="1"/>
@@ -24395,7 +24428,7 @@
       </c>
       <c r="O1" s="296">
         <f>SUM(B3:B30)</f>
-        <v>3.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="P1" s="344" t="s">
         <v>198</v>
@@ -24405,11 +24438,11 @@
     <row r="2" spans="1:17" ht="16.5">
       <c r="B2" s="251">
         <f>SUM(B3:B33)</f>
-        <v>3.5</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="C2" s="251">
         <f t="shared" ref="C2" si="0">SUM(C3:C33)</f>
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="D2" s="251">
         <f>SUM(D3:D33)</f>
@@ -24417,15 +24450,15 @@
       </c>
       <c r="E2" s="251">
         <f t="shared" ref="E2:H2" si="1">SUM(E3:E33)</f>
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F2" s="251">
         <f>SUM(F3:F33)</f>
-        <v>15.5</v>
+        <v>16.25</v>
       </c>
       <c r="G2" s="251">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H2" s="251">
         <f t="shared" si="1"/>
@@ -24433,12 +24466,12 @@
       </c>
       <c r="I2" s="251">
         <f>SUM(I3:I30)/60</f>
-        <v>0.43333333333333335</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="J2" s="251"/>
       <c r="K2" s="240">
         <f>SUM(E2:G2)</f>
-        <v>17</v>
+        <v>20.75</v>
       </c>
       <c r="L2" s="299"/>
       <c r="M2" s="296" t="s">
@@ -24449,14 +24482,14 @@
       </c>
       <c r="O2" s="256">
         <f>SUM(C3:E30)</f>
-        <v>6.75</v>
+        <v>9.5</v>
       </c>
       <c r="P2" s="344"/>
       <c r="Q2" s="344"/>
     </row>
     <row r="3" spans="1:17" ht="16.5">
       <c r="A3" s="9">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="298">
         <v>3.5</v>
@@ -24478,21 +24511,21 @@
         <v>370</v>
       </c>
       <c r="K3" s="299" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L3" s="20" t="s">
         <v>25</v>
       </c>
       <c r="M3" s="264">
         <f>SUM(M4:M28)</f>
-        <v>17</v>
+        <v>20.75</v>
       </c>
       <c r="N3" s="255" t="s">
         <v>16</v>
       </c>
       <c r="O3" s="255">
         <f>SUM(F3:H30)</f>
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="P3" s="296">
         <f>SUM(P4:P32)</f>
@@ -24501,7 +24534,7 @@
     </row>
     <row r="4" spans="1:17" ht="16.5">
       <c r="A4" s="9">
-        <v>46114</v>
+        <v>46144</v>
       </c>
       <c r="B4" s="300"/>
       <c r="C4" s="253">
@@ -24517,23 +24550,27 @@
       <c r="I4" s="251"/>
       <c r="J4" s="251"/>
       <c r="K4" s="299" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L4" s="300" t="s">
         <v>199</v>
       </c>
-      <c r="M4" s="265"/>
+      <c r="M4" s="265">
+        <v>1.5</v>
+      </c>
       <c r="P4" s="296">
         <v>1.5</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="16.5">
       <c r="A5" s="9">
-        <v>46115</v>
-      </c>
-      <c r="B5" s="300"/>
+        <v>46145</v>
+      </c>
+      <c r="B5" s="300">
+        <v>4.3</v>
+      </c>
       <c r="C5" s="253">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="D5" s="253">
         <v>0.25</v>
@@ -24542,21 +24579,25 @@
         <v>0.25</v>
       </c>
       <c r="F5" s="253">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G5" s="251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="251">
         <v>1</v>
       </c>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
+      <c r="I5" s="251">
+        <v>51</v>
+      </c>
+      <c r="J5" s="251" t="s">
+        <v>378</v>
+      </c>
       <c r="K5" s="299" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L5" s="300" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M5" s="266">
         <v>0.5</v>
@@ -24570,13 +24611,35 @@
     </row>
     <row r="6" spans="1:17" ht="16.5">
       <c r="A6" s="9">
-        <v>46116</v>
-      </c>
-      <c r="B6" s="300"/>
-      <c r="C6" s="253"/>
+        <v>46146</v>
+      </c>
+      <c r="B6" s="300">
+        <v>1</v>
+      </c>
+      <c r="C6" s="253">
+        <v>0.5</v>
+      </c>
       <c r="D6" s="253"/>
+      <c r="E6" s="296">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="296">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="296">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="296">
+        <v>3</v>
+      </c>
+      <c r="J6" s="251" t="s">
+        <v>379</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>381</v>
+      </c>
       <c r="L6" s="300" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M6" s="266"/>
       <c r="N6" s="17" t="s">
@@ -24588,7 +24651,7 @@
     </row>
     <row r="7" spans="1:17" ht="16.5">
       <c r="A7" s="9">
-        <v>46117</v>
+        <v>46147</v>
       </c>
       <c r="B7" s="300"/>
       <c r="C7" s="253"/>
@@ -24606,15 +24669,17 @@
     </row>
     <row r="8" spans="1:17" ht="16.5">
       <c r="A8" s="9">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="B8" s="300"/>
       <c r="C8" s="253"/>
       <c r="D8" s="253"/>
       <c r="L8" s="300" t="s">
-        <v>243</v>
-      </c>
-      <c r="M8" s="280"/>
+        <v>380</v>
+      </c>
+      <c r="M8" s="280">
+        <v>0.5</v>
+      </c>
       <c r="N8" s="259" t="s">
         <v>169</v>
       </c>
@@ -24624,7 +24689,7 @@
     </row>
     <row r="9" spans="1:17" ht="16.5">
       <c r="A9" s="9">
-        <v>46119</v>
+        <v>46149</v>
       </c>
       <c r="B9" s="300"/>
       <c r="C9" s="253"/>
@@ -24642,15 +24707,17 @@
     </row>
     <row r="10" spans="1:17" ht="16.5">
       <c r="A10" s="9">
-        <v>46120</v>
+        <v>46150</v>
       </c>
       <c r="B10" s="300"/>
       <c r="C10" s="253"/>
       <c r="D10" s="253"/>
       <c r="L10" s="300" t="s">
-        <v>345</v>
-      </c>
-      <c r="M10" s="266"/>
+        <v>376</v>
+      </c>
+      <c r="M10" s="266">
+        <v>1</v>
+      </c>
       <c r="N10" s="260" t="s">
         <v>171</v>
       </c>
@@ -24660,7 +24727,7 @@
     </row>
     <row r="11" spans="1:17" ht="16.5">
       <c r="A11" s="9">
-        <v>46121</v>
+        <v>46151</v>
       </c>
       <c r="B11" s="300"/>
       <c r="C11" s="253"/>
@@ -24676,14 +24743,12 @@
     </row>
     <row r="12" spans="1:17" ht="16.5">
       <c r="A12" s="9">
-        <v>46122</v>
+        <v>46152</v>
       </c>
       <c r="B12" s="300"/>
       <c r="C12" s="253"/>
       <c r="D12" s="222"/>
-      <c r="L12" s="300" t="s">
-        <v>340</v>
-      </c>
+      <c r="L12" s="300"/>
       <c r="M12" s="266"/>
       <c r="N12" s="296" t="s">
         <v>174</v>
@@ -24694,7 +24759,7 @@
     </row>
     <row r="13" spans="1:17" ht="16.5">
       <c r="A13" s="9">
-        <v>46123</v>
+        <v>46153</v>
       </c>
       <c r="B13" s="300"/>
       <c r="C13" s="253"/>
@@ -24715,16 +24780,16 @@
     </row>
     <row r="14" spans="1:17" ht="34.5" customHeight="1">
       <c r="A14" s="9">
-        <v>46124</v>
+        <v>46154</v>
       </c>
       <c r="B14" s="300"/>
       <c r="C14" s="253"/>
       <c r="D14" s="253"/>
       <c r="L14" s="300" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="M14" s="267">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="N14" s="39" t="s">
         <v>175</v>
@@ -24735,7 +24800,7 @@
     </row>
     <row r="15" spans="1:17" ht="16.5">
       <c r="A15" s="9">
-        <v>46125</v>
+        <v>46155</v>
       </c>
       <c r="B15" s="300"/>
       <c r="C15" s="253"/>
@@ -24753,7 +24818,7 @@
     </row>
     <row r="16" spans="1:17" ht="16.5">
       <c r="A16" s="9">
-        <v>46126</v>
+        <v>46156</v>
       </c>
       <c r="B16" s="300"/>
       <c r="C16" s="253"/>
@@ -24771,7 +24836,7 @@
     </row>
     <row r="17" spans="1:16" ht="16.5">
       <c r="A17" s="9">
-        <v>46127</v>
+        <v>46157</v>
       </c>
       <c r="B17" s="300"/>
       <c r="C17" s="253"/>
@@ -24789,7 +24854,7 @@
     </row>
     <row r="18" spans="1:16" ht="16.5">
       <c r="A18" s="9">
-        <v>46128</v>
+        <v>46158</v>
       </c>
       <c r="B18" s="300"/>
       <c r="C18" s="253"/>
@@ -24804,7 +24869,7 @@
     </row>
     <row r="19" spans="1:16" ht="16.5">
       <c r="A19" s="9">
-        <v>46129</v>
+        <v>46159</v>
       </c>
       <c r="B19" s="300"/>
       <c r="C19" s="253"/>
@@ -24818,13 +24883,13 @@
     </row>
     <row r="20" spans="1:16" ht="33">
       <c r="A20" s="9">
-        <v>46130</v>
+        <v>46160</v>
       </c>
       <c r="B20" s="300"/>
       <c r="C20" s="253"/>
       <c r="D20" s="253"/>
       <c r="L20" s="300" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M20" s="281">
         <v>1</v>
@@ -24839,7 +24904,7 @@
     </row>
     <row r="21" spans="1:16" ht="16.5">
       <c r="A21" s="9">
-        <v>46131</v>
+        <v>46161</v>
       </c>
       <c r="B21" s="300"/>
       <c r="C21" s="253"/>
@@ -24858,7 +24923,7 @@
     </row>
     <row r="22" spans="1:16" ht="16.5">
       <c r="A22" s="9">
-        <v>46132</v>
+        <v>46162</v>
       </c>
       <c r="B22" s="300"/>
       <c r="C22" s="253"/>
@@ -24877,7 +24942,7 @@
     </row>
     <row r="23" spans="1:16" ht="16.5">
       <c r="A23" s="9">
-        <v>46133</v>
+        <v>46163</v>
       </c>
       <c r="B23" s="300"/>
       <c r="C23" s="253"/>
@@ -24894,7 +24959,7 @@
     </row>
     <row r="24" spans="1:16" ht="16.5">
       <c r="A24" s="9">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="B24" s="300"/>
       <c r="C24" s="253"/>
@@ -24921,7 +24986,7 @@
     </row>
     <row r="25" spans="1:16" ht="16.5">
       <c r="A25" s="9">
-        <v>46135</v>
+        <v>46165</v>
       </c>
       <c r="B25" s="300"/>
       <c r="C25" s="253"/>
@@ -24944,7 +25009,7 @@
     </row>
     <row r="26" spans="1:16" ht="16.5">
       <c r="A26" s="9">
-        <v>46136</v>
+        <v>46166</v>
       </c>
       <c r="B26" s="300"/>
       <c r="C26" s="253"/>
@@ -24963,7 +25028,7 @@
     </row>
     <row r="27" spans="1:16" ht="16.5">
       <c r="A27" s="9">
-        <v>46137</v>
+        <v>46167</v>
       </c>
       <c r="B27" s="300"/>
       <c r="C27" s="253"/>
@@ -24988,7 +25053,7 @@
     </row>
     <row r="28" spans="1:16" ht="16.5">
       <c r="A28" s="9">
-        <v>46138</v>
+        <v>46168</v>
       </c>
       <c r="B28" s="300"/>
       <c r="C28" s="253"/>
@@ -25004,7 +25069,7 @@
     </row>
     <row r="29" spans="1:16" ht="16.5">
       <c r="A29" s="9">
-        <v>46139</v>
+        <v>46169</v>
       </c>
       <c r="B29" s="300"/>
       <c r="C29" s="253"/>
@@ -25019,7 +25084,7 @@
     </row>
     <row r="30" spans="1:16" ht="16.5">
       <c r="A30" s="9">
-        <v>46140</v>
+        <v>46170</v>
       </c>
       <c r="B30" s="300"/>
       <c r="C30" s="253"/>
@@ -25038,7 +25103,7 @@
     </row>
     <row r="31" spans="1:16" ht="16.5">
       <c r="A31" s="9">
-        <v>46141</v>
+        <v>46171</v>
       </c>
       <c r="B31" s="300"/>
       <c r="C31" s="253"/>
@@ -25057,7 +25122,7 @@
     </row>
     <row r="32" spans="1:16" ht="16.5">
       <c r="A32" s="9">
-        <v>46142</v>
+        <v>46172</v>
       </c>
       <c r="B32" s="298"/>
       <c r="C32" s="253"/>
@@ -25076,7 +25141,7 @@
     </row>
     <row r="33" spans="1:15" ht="16.5">
       <c r="A33" s="9">
-        <v>46112</v>
+        <v>46173</v>
       </c>
       <c r="B33" s="299"/>
       <c r="C33" s="299"/>
@@ -25183,15 +25248,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B32">
-    <cfRule type="cellIs" dxfId="60" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="61" priority="3" operator="lessThan">
       <formula>$B$34</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="4" operator="greaterThan">
       <formula>$B$34</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A33">
-    <cfRule type="expression" dxfId="58" priority="2">
+    <cfRule type="expression" dxfId="59" priority="2">
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25952,19 +26017,19 @@
     <mergeCell ref="J28:N29"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:B4 B6:B33">
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="54" priority="2" operator="lessThan">
       <formula>$B$35</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="53" priority="3" operator="between">
       <formula>$B$35</formula>
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="4" operator="greaterThan">
       <formula>$B$35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A34">
-    <cfRule type="expression" dxfId="50" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26743,19 +26808,19 @@
     <mergeCell ref="J28:N29"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:B4 B6:B33">
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="2" operator="lessThan">
       <formula>$B$35</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="44" priority="3" operator="between">
       <formula>$B$35</formula>
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="4" operator="greaterThan">
       <formula>$B$35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A34">
-    <cfRule type="expression" dxfId="41" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27288,7 +27353,7 @@
       <c r="J20" s="157"/>
       <c r="K20" s="155"/>
       <c r="L20" s="349"/>
-      <c r="M20" s="308"/>
+      <c r="M20" s="301"/>
       <c r="N20" s="172">
         <v>-0.5</v>
       </c>
@@ -27552,19 +27617,19 @@
     <mergeCell ref="J28:N29"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:B4 B6:B33">
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="lessThan">
       <formula>$B$35</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="between">
       <formula>$B$35</formula>
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="4" operator="greaterThan">
       <formula>$B$35</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:A34">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>

--- a/3.Study status-2026.xlsx
+++ b/3.Study status-2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7650"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7650" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Rules" sheetId="21" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="492">
   <si>
     <t>hours studied</t>
   </si>
@@ -786,9 +786,6 @@
     <t>0.5- time pass, 0.5- head ache</t>
   </si>
   <si>
-    <t>sollu calls</t>
-  </si>
-  <si>
     <t>lwc 57-60</t>
   </si>
   <si>
@@ -1118,9 +1115,6 @@
   </si>
   <si>
     <t>BCB rules- BCB must be done before 9:30 PM else other may rest</t>
-  </si>
-  <si>
-    <t>Food related -keep always 15 mins timer during tiffin,lunch , dinner and eat,rem 10 mins dish wash</t>
   </si>
   <si>
     <t>akka 16</t>
@@ -1343,9 +1337,6 @@
     <t>kitchen-1 , house work-0.25, bathroom cleaning 1.5,hc-0.75,water 1.25, weekend -1, veg help -1</t>
   </si>
   <si>
-    <t>pure time waste like surfing, car search 0.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">financial- silver sell, nps 0.5,bank loan </t>
   </si>
   <si>
@@ -1376,30 +1367,51 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">movies   </t>
-  </si>
-  <si>
-    <t>house related shopping- veg buy, millet shop buy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kitchen , house work-, bathroom cleaning ,hc-,water , weekend -, veg help </t>
-  </si>
-  <si>
-    <t xml:space="preserve">financial- </t>
-  </si>
-  <si>
-    <t xml:space="preserve">hospital </t>
-  </si>
-  <si>
     <t>target- aws (complete daily 30 mins syllabus ),  react (daily 30mins 22 may-22 july),monthly complete 15 hours of any syllabus</t>
   </si>
   <si>
     <t>aws 179-181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) plan the day and keep watch - if u dont plan day will wasted, stop mobile &amp;stop all works@ 9:00AM &amp;keep cell away from 9:00-12:30 &amp;  don’t talk lontalk talk long any call from 930-12 
+2)  once reading starts then No deviation for  2 hours -means we should not use mobile,youtube, no google search of  topics other than subject 
+(if u get bored see amazon/ only 1 song in jio savn- dont open  youtube)
+ </t>
+  </si>
+  <si>
+    <t>youtube- audio release , trailers, gamechanger</t>
+  </si>
+  <si>
+    <t>react -28, spr ai</t>
+  </si>
+  <si>
+    <t>timing 9AM-12PM  keep cell phone away don’t open youtube or any long calls more than 15 mins, if bored listen 1 audio song , 9-12 only study  don’t even search other topics also</t>
+  </si>
+  <si>
+    <t>react- 29,30</t>
+  </si>
+  <si>
+    <t>1- tcs work interviews</t>
+  </si>
+  <si>
+    <t>spr 5,6,7,9, react prac</t>
+  </si>
+  <si>
+    <t>tcs work interviews -1,ampf prod deploy 6</t>
+  </si>
+  <si>
+    <t>6-prod deployment,0.5- my pant search,0.75- santu teach aws</t>
+  </si>
+  <si>
+    <t>aws 182- 188</t>
+  </si>
+  <si>
+    <t>Food related -keep always 20 mins timer during tiffin,lunch , dinner and eat,rem 10 mins dish wash</t>
   </si>
   <si>
     <r>
       <t xml:space="preserve">1) Open TV/youtube only twice  in a day - don’t open in lunch  time as it is consuming more time (dinner -max15 mins)
- 2) per day max youtube/TV is 20 minutes even on weekends-1st keep alarm and then see, 2 movies a month max
+ 2) per day max youtube/TV is 30 minutes even on weekends-1st keep alarm and then see, 2 movies a month max
 3) </t>
     </r>
     <r>
@@ -1427,10 +1439,145 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">1) plan the day and keep watch - if u dont plan day will wasted, stop mobile &amp;stop all works@ 9:00AM &amp;keep cell away from 9:30-12:30 &amp;  don’t talk lontalk talk long any call from 930-12 
-2)  once reading starts then No deviation for  2 hours -means we should not use mobile,youtube, no google search of  topics other than subject 
-(if u get bored see amazon/ only 1 song in jio savn- dont open  youtube)
- </t>
+    <t>my shopping slippers</t>
+  </si>
+  <si>
+    <t>pure time waste like surfing, car search 0.3, bcb items -2 mynt</t>
+  </si>
+  <si>
+    <t>0.75-BCB,3- slippers dmart shoping, 2- myn BCB</t>
+  </si>
+  <si>
+    <t>react 32</t>
+  </si>
+  <si>
+    <t>1-sleep due to back pain</t>
+  </si>
+  <si>
+    <t>react 33-35</t>
+  </si>
+  <si>
+    <t>bike svc</t>
+  </si>
+  <si>
+    <t>react 36</t>
+  </si>
+  <si>
+    <t>2.5- bday calls</t>
+  </si>
+  <si>
+    <t>react 37</t>
+  </si>
+  <si>
+    <t>real estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75- real estate cal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">my job search , in linked in </t>
+  </si>
+  <si>
+    <t>react 37, aws 189-193</t>
+  </si>
+  <si>
+    <t>3.5- 2 BCB, 0.5- movie booking,1.5- train book</t>
+  </si>
+  <si>
+    <t>train book</t>
+  </si>
+  <si>
+    <t>2.5-bike svc, pick up</t>
+  </si>
+  <si>
+    <t>1- hosp back pain, 3- sleep due to night back pain</t>
+  </si>
+  <si>
+    <t>spr ai 11-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mangoes pickup </t>
+  </si>
+  <si>
+    <t xml:space="preserve">pure time waste -5.3 like surfing, car search 0.3 ,rent house </t>
+  </si>
+  <si>
+    <t>extra ofc work</t>
+  </si>
+  <si>
+    <t>2- sailu calls before flight</t>
+  </si>
+  <si>
+    <t>aws 128-132</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> over sleep due to extra water </t>
+  </si>
+  <si>
+    <t>3- charan inst help</t>
+  </si>
+  <si>
+    <t>roopa visit to ongole-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">went to ogl to see sai daughter </t>
+  </si>
+  <si>
+    <t>react without prac</t>
+  </si>
+  <si>
+    <t>maternity insurance enq</t>
+  </si>
+  <si>
+    <t>1- santu accenture apply,5.5- rainbow genetic rep coll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">house related shopping- veg buy 0.5, millet shop buy, HELMET SHOP </t>
+  </si>
+  <si>
+    <t>fnds resumehelp 0.3, charan help 0.25, sailu resum tcs</t>
+  </si>
+  <si>
+    <t>full back pain went to pvg hosp</t>
+  </si>
+  <si>
+    <t>kitchen , house work-, bathroom cleaning ,hc-,water0.5 , weekend -2.5, veg help , khash 0.5, house clean 0.5</t>
+  </si>
+  <si>
+    <t>misc- sys clean -1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5-songs,1- sys clean </t>
+  </si>
+  <si>
+    <t>react 41,42.5</t>
+  </si>
+  <si>
+    <t>bcb sleep -3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resume , santu resume -2, my resume, santu teach 1 aws, int help </t>
+  </si>
+  <si>
+    <t>2.5-BCB, 7- santu infosys inte help</t>
+  </si>
+  <si>
+    <t>movies   -peddi, op valentine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">santu pickup -1, resort search </t>
+  </si>
+  <si>
+    <t>react 38,39,40, spr ai -15</t>
+  </si>
+  <si>
+    <t>4- santu resume naukrai prof updae</t>
+  </si>
+  <si>
+    <t>4-went to oasis hosp</t>
+  </si>
+  <si>
+    <t>hosp -back pain 4.5 ,rohit final enq 5.5, oasis hosp</t>
   </si>
 </sst>
 </file>
@@ -1534,12 +1681,6 @@
       <sz val="12"/>
       <color rgb="FF9C0006"/>
       <name val="Candara"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
@@ -1771,7 +1912,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="9"/>
+      <color theme="8" tint="0.79998168889431442"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -2541,7 +2689,7 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2550,9 +2698,9 @@
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="27" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="43" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="42" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="3" applyFont="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="center"/>
     </xf>
@@ -2573,7 +2721,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="372">
+  <cellXfs count="378">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2605,9 +2753,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="10" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="10" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2630,22 +2778,22 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="2" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="2" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="2" xfId="14" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="13" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="2" xfId="14" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" xfId="13" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="2" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="2" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="2" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="2" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2654,7 +2802,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2662,7 +2810,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="10" xfId="14" applyBorder="1"/>
-    <xf numFmtId="16" fontId="24" fillId="11" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="23" fillId="11" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2682,61 +2830,73 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="33" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="32" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="34" fillId="22" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="33" fillId="22" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="35" fillId="23" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="34" fillId="23" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="35" fillId="22" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="36" fillId="22" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="25" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2745,11 +2905,11 @@
     <xf numFmtId="0" fontId="37" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="24" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="38" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2757,16 +2917,26 @@
     <xf numFmtId="0" fontId="38" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="40" fillId="26" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2775,76 +2945,54 @@
     <xf numFmtId="0" fontId="40" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="41" fillId="26" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="26" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="41" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="40" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="27" borderId="7" xfId="19" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="27" borderId="7" xfId="19" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="27" borderId="7" xfId="19" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="27" borderId="7" xfId="19" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="9" applyBorder="1" applyAlignment="1">
@@ -2877,10 +3025,10 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="28" borderId="9" xfId="20" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="28" borderId="9" xfId="20" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="29" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2978,10 +3126,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="28" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="42" fillId="17" borderId="2" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="2" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="17" borderId="2" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="2" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3014,7 +3162,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="44" fillId="10" borderId="30" xfId="22" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="30" xfId="22" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3031,7 +3179,7 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="11" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3048,7 +3196,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3074,7 +3222,7 @@
     <xf numFmtId="0" fontId="0" fillId="31" borderId="2" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="31" borderId="2" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="2" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="3" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3089,7 +3237,7 @@
     <xf numFmtId="0" fontId="0" fillId="31" borderId="12" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="31" borderId="0" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
@@ -3098,7 +3246,7 @@
     <xf numFmtId="0" fontId="7" fillId="31" borderId="0" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="33" borderId="0" xfId="25">
@@ -3126,13 +3274,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -3141,8 +3289,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="24" fillId="11" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="5" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="23" fillId="11" borderId="5" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="5" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="5" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="14" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="5" xfId="21" applyBorder="1" applyAlignment="1">
@@ -3167,7 +3315,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="38" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3196,7 +3344,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="31" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="30" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -3234,10 +3382,9 @@
     <xf numFmtId="0" fontId="7" fillId="36" borderId="0" xfId="28">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="49" fillId="36" borderId="0" xfId="28" applyFont="1">
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="0" xfId="28" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="34" borderId="0" xfId="26">
@@ -3251,10 +3398,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" xfId="29">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="37" borderId="0" xfId="29" applyFont="1">
+    <xf numFmtId="0" fontId="50" fillId="37" borderId="0" xfId="29" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="31" borderId="32" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3284,29 +3428,48 @@
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="34" borderId="0" xfId="26" applyFont="1">
+    <xf numFmtId="0" fontId="51" fillId="37" borderId="0" xfId="29" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="36" borderId="0" xfId="28" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" xfId="28" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" xfId="26" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="37" borderId="0" xfId="29" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="35" borderId="0" xfId="27" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="7" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="32" borderId="0" xfId="24" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3322,25 +3485,30 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="9" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" xfId="26" applyFont="1">
+    <xf numFmtId="0" fontId="47" fillId="34" borderId="0" xfId="26" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="35" borderId="0" xfId="27" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="3" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="3" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="4" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="5" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="16" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3358,25 +3526,25 @@
     <xf numFmtId="0" fontId="7" fillId="34" borderId="0" xfId="26">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="11" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="11" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="6" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="6" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="14" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="14" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="15" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="15" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="8" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="8" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="16" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="16" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3385,13 +3553,13 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="27" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="4" applyAlignment="1">
@@ -3400,7 +3568,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="11" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="11" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4429,7 +4597,7 @@
             <color theme="0"/>
           </stop>
           <stop position="1">
-            <color rgb="FF00FF99"/>
+            <color rgb="FFFFCC00"/>
           </stop>
         </gradientFill>
       </fill>
@@ -4808,6 +4976,7 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFFFCC00"/>
       <color rgb="FFCC3399"/>
       <color rgb="FFFF3399"/>
       <color rgb="FFFF7C80"/>
@@ -4817,7 +4986,6 @@
       <color rgb="FFCC0099"/>
       <color rgb="FF99FFCC"/>
       <color rgb="FF66FF99"/>
-      <color rgb="FFFF9933"/>
     </mruColors>
   </colors>
   <extLst>
@@ -5133,11 +5301,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="70037696"/>
-        <c:axId val="70039872"/>
+        <c:axId val="-166890048"/>
+        <c:axId val="-166881888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="70037696"/>
+        <c:axId val="-166890048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5177,14 +5345,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70039872"/>
+        <c:crossAx val="-166881888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="70039872"/>
+        <c:axId val="-166881888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5232,7 +5400,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70037696"/>
+        <c:crossAx val="-166890048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5526,11 +5694,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="141804976"/>
-        <c:axId val="141793552"/>
+        <c:axId val="-128673392"/>
+        <c:axId val="-128683184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="141804976"/>
+        <c:axId val="-128673392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5570,14 +5738,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141793552"/>
+        <c:crossAx val="-128683184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="141793552"/>
+        <c:axId val="-128683184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5625,7 +5793,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141804976"/>
+        <c:crossAx val="-128673392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5916,11 +6084,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="141800080"/>
-        <c:axId val="141806064"/>
+        <c:axId val="-128672848"/>
+        <c:axId val="-128685360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="141800080"/>
+        <c:axId val="-128672848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5960,14 +6128,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141806064"/>
+        <c:crossAx val="-128685360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="141806064"/>
+        <c:axId val="-128685360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6015,7 +6183,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141800080"/>
+        <c:crossAx val="-128672848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6312,11 +6480,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="141791920"/>
-        <c:axId val="141801712"/>
+        <c:axId val="-128671216"/>
+        <c:axId val="-128684816"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="141791920"/>
+        <c:axId val="-128671216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6356,14 +6524,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141801712"/>
+        <c:crossAx val="-128684816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="141801712"/>
+        <c:axId val="-128684816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6411,7 +6579,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141791920"/>
+        <c:crossAx val="-128671216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6741,11 +6909,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="70038784"/>
-        <c:axId val="70040960"/>
+        <c:axId val="-166882976"/>
+        <c:axId val="-166892224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="70038784"/>
+        <c:axId val="-166882976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6785,14 +6953,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70040960"/>
+        <c:crossAx val="-166892224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="70040960"/>
+        <c:axId val="-166892224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6840,7 +7008,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70038784"/>
+        <c:crossAx val="-166882976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7188,11 +7356,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="70039328"/>
-        <c:axId val="70038240"/>
+        <c:axId val="-166882432"/>
+        <c:axId val="-166895488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="70039328"/>
+        <c:axId val="-166882432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7232,14 +7400,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70038240"/>
+        <c:crossAx val="-166895488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="70038240"/>
+        <c:axId val="-166895488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7287,7 +7455,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70039328"/>
+        <c:crossAx val="-166882432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7581,6 +7749,12 @@
                 <c:pt idx="13">
                   <c:v>2</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2</c:v>
+                </c:pt>
                 <c:pt idx="17">
                   <c:v>2</c:v>
                 </c:pt>
@@ -7626,11 +7800,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="70045312"/>
-        <c:axId val="70048576"/>
+        <c:axId val="-166893856"/>
+        <c:axId val="-166890592"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="70045312"/>
+        <c:axId val="-166893856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7670,14 +7844,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70048576"/>
+        <c:crossAx val="-166890592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="70048576"/>
+        <c:axId val="-166890592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7725,7 +7899,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70045312"/>
+        <c:crossAx val="-166893856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7789,7 +7963,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7880,7 +8053,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -8072,11 +8244,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="70037152"/>
-        <c:axId val="70050208"/>
+        <c:axId val="-166884608"/>
+        <c:axId val="-166893312"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="70037152"/>
+        <c:axId val="-166884608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8116,14 +8288,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70050208"/>
+        <c:crossAx val="-166893312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="70050208"/>
+        <c:axId val="-166893312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8171,7 +8343,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70037152"/>
+        <c:crossAx val="-166884608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8444,6 +8616,60 @@
                 <c:pt idx="0">
                   <c:v>1.75</c:v>
                 </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.75</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.25</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8459,11 +8685,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="141797360"/>
-        <c:axId val="141792464"/>
+        <c:axId val="-166889504"/>
+        <c:axId val="-166883520"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="141797360"/>
+        <c:axId val="-166889504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8503,14 +8729,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141792464"/>
+        <c:crossAx val="-166883520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="141792464"/>
+        <c:axId val="-166883520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8558,7 +8784,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141797360"/>
+        <c:crossAx val="-166889504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8852,11 +9078,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="141798448"/>
-        <c:axId val="141805520"/>
+        <c:axId val="-166888416"/>
+        <c:axId val="-166886784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="141798448"/>
+        <c:axId val="-166888416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8896,14 +9122,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141805520"/>
+        <c:crossAx val="-166886784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="141805520"/>
+        <c:axId val="-166886784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8951,7 +9177,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141798448"/>
+        <c:crossAx val="-166888416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9245,11 +9471,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="141791376"/>
-        <c:axId val="141797904"/>
+        <c:axId val="-128675568"/>
+        <c:axId val="-128686448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="141791376"/>
+        <c:axId val="-128675568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9289,14 +9515,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141797904"/>
+        <c:crossAx val="-128686448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="141797904"/>
+        <c:axId val="-128686448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9344,7 +9570,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141791376"/>
+        <c:crossAx val="-128675568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9635,11 +9861,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="141800624"/>
-        <c:axId val="141803888"/>
+        <c:axId val="-128672304"/>
+        <c:axId val="-128681008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="141800624"/>
+        <c:axId val="-128672304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9679,14 +9905,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141803888"/>
+        <c:crossAx val="-128681008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="141803888"/>
+        <c:axId val="-128681008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9734,7 +9960,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="141800624"/>
+        <c:crossAx val="-128672304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16384,8 +16610,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table32313" displayName="Table32313" ref="L3:L24" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56" tableBorderDxfId="55" dataCellStyle="pink">
-  <autoFilter ref="L3:L24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table32313" displayName="Table32313" ref="L3:L25" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56" tableBorderDxfId="55" dataCellStyle="pink">
+  <autoFilter ref="L3:L25"/>
   <tableColumns count="1">
     <tableColumn id="1" name="Total wastage" dataDxfId="54" dataCellStyle="pink"/>
   </tableColumns>
@@ -16729,992 +16955,994 @@
   <cols>
     <col min="7" max="7" width="25.140625" customWidth="1"/>
     <col min="10" max="10" width="85.28515625" customWidth="1"/>
-    <col min="19" max="19" width="5" customWidth="1"/>
+    <col min="19" max="19" width="4.85546875" customWidth="1"/>
     <col min="20" max="20" width="8.28515625" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="9.140625" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="4.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:21" ht="16.5">
-      <c r="B1" s="329" t="s">
+      <c r="B1" s="332" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="329"/>
-      <c r="D1" s="329"/>
-      <c r="E1" s="329"/>
-      <c r="F1" s="329"/>
-      <c r="G1" s="329"/>
-      <c r="H1" s="329"/>
-      <c r="I1" s="329"/>
-      <c r="J1" s="329"/>
-      <c r="L1" s="352" t="s">
+      <c r="C1" s="332"/>
+      <c r="D1" s="332"/>
+      <c r="E1" s="332"/>
+      <c r="F1" s="332"/>
+      <c r="G1" s="332"/>
+      <c r="H1" s="332"/>
+      <c r="I1" s="332"/>
+      <c r="J1" s="332"/>
+      <c r="L1" s="358" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="352"/>
-      <c r="N1" s="352"/>
-      <c r="O1" s="352"/>
-      <c r="P1" s="352"/>
-      <c r="Q1" s="352"/>
-      <c r="R1" s="352"/>
-      <c r="S1" s="352"/>
-      <c r="T1" s="352"/>
-      <c r="U1" s="352"/>
+      <c r="M1" s="358"/>
+      <c r="N1" s="358"/>
+      <c r="O1" s="358"/>
+      <c r="P1" s="358"/>
+      <c r="Q1" s="358"/>
+      <c r="R1" s="358"/>
+      <c r="S1" s="358"/>
+      <c r="T1" s="358"/>
+      <c r="U1" s="358"/>
     </row>
     <row r="2" spans="2:21" ht="16.5">
-      <c r="B2" s="322" t="s">
+      <c r="B2" s="327" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="327"/>
+      <c r="D2" s="327"/>
+      <c r="E2" s="327"/>
+      <c r="F2" s="327"/>
+      <c r="G2" s="327"/>
+      <c r="H2" s="327"/>
+      <c r="I2" s="327"/>
+      <c r="J2" s="327"/>
+      <c r="L2" s="362" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" s="363"/>
+      <c r="N2" s="363"/>
+      <c r="O2" s="363"/>
+      <c r="P2" s="363"/>
+      <c r="Q2" s="363"/>
+      <c r="R2" s="363"/>
+      <c r="S2" s="363"/>
+      <c r="T2" s="363"/>
+      <c r="U2" s="363"/>
+    </row>
+    <row r="3" spans="2:21">
+      <c r="B3" s="334" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="334"/>
+      <c r="D3" s="334"/>
+      <c r="E3" s="334"/>
+      <c r="F3" s="334"/>
+      <c r="G3" s="334"/>
+      <c r="H3" s="334"/>
+      <c r="I3" s="334"/>
+      <c r="J3" s="334"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="364" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="364"/>
+      <c r="N3" s="364"/>
+      <c r="O3" s="364"/>
+      <c r="P3" s="364"/>
+      <c r="Q3" s="364"/>
+      <c r="R3" s="364"/>
+      <c r="S3" s="364"/>
+      <c r="T3" s="364"/>
+      <c r="U3" s="364"/>
+    </row>
+    <row r="4" spans="2:21" ht="15" customHeight="1">
+      <c r="B4" s="329" t="s">
+        <v>433</v>
+      </c>
+      <c r="C4" s="329"/>
+      <c r="D4" s="329"/>
+      <c r="E4" s="329"/>
+      <c r="F4" s="329"/>
+      <c r="G4" s="329"/>
+      <c r="H4" s="329"/>
+      <c r="I4" s="329"/>
+      <c r="J4" s="329"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="364"/>
+      <c r="M4" s="364"/>
+      <c r="N4" s="364"/>
+      <c r="O4" s="364"/>
+      <c r="P4" s="364"/>
+      <c r="Q4" s="364"/>
+      <c r="R4" s="364"/>
+      <c r="S4" s="364"/>
+      <c r="T4" s="364"/>
+      <c r="U4" s="364"/>
+    </row>
+    <row r="5" spans="2:21" ht="15" customHeight="1">
+      <c r="B5" s="329"/>
+      <c r="C5" s="329"/>
+      <c r="D5" s="329"/>
+      <c r="E5" s="329"/>
+      <c r="F5" s="329"/>
+      <c r="G5" s="329"/>
+      <c r="H5" s="329"/>
+      <c r="I5" s="329"/>
+      <c r="J5" s="329"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="332" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="332"/>
+      <c r="N5" s="332"/>
+      <c r="O5" s="332"/>
+      <c r="P5" s="332"/>
+      <c r="Q5" s="332"/>
+      <c r="R5" s="332"/>
+      <c r="S5" s="332"/>
+      <c r="T5" s="332"/>
+      <c r="U5" s="332"/>
+    </row>
+    <row r="6" spans="2:21" ht="35.25" customHeight="1">
+      <c r="B6" s="329"/>
+      <c r="C6" s="329"/>
+      <c r="D6" s="329"/>
+      <c r="E6" s="329"/>
+      <c r="F6" s="329"/>
+      <c r="G6" s="329"/>
+      <c r="H6" s="329"/>
+      <c r="I6" s="329"/>
+      <c r="J6" s="329"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="359" t="s">
+        <v>147</v>
+      </c>
+      <c r="M6" s="359"/>
+      <c r="N6" s="359"/>
+      <c r="O6" s="359"/>
+      <c r="P6" s="359"/>
+      <c r="Q6" s="359"/>
+      <c r="R6" s="359"/>
+      <c r="S6" s="359"/>
+      <c r="T6" s="359"/>
+      <c r="U6" s="359"/>
+    </row>
+    <row r="7" spans="2:21" ht="15.75" thickBot="1">
+      <c r="B7" s="367" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="367"/>
+      <c r="D7" s="367"/>
+      <c r="E7" s="367"/>
+      <c r="F7" s="367"/>
+      <c r="G7" s="367"/>
+      <c r="H7" s="367"/>
+      <c r="I7" s="367"/>
+      <c r="J7" s="367"/>
+      <c r="K7" s="367"/>
+      <c r="L7" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="M7" s="360"/>
+      <c r="N7" s="360"/>
+      <c r="O7" s="360"/>
+      <c r="P7" s="360"/>
+      <c r="Q7" s="360"/>
+      <c r="R7" s="360"/>
+      <c r="S7" s="360"/>
+      <c r="T7" s="360"/>
+      <c r="U7" s="360"/>
+    </row>
+    <row r="8" spans="2:21" ht="88.5" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B8" s="330" t="s">
+        <v>444</v>
+      </c>
+      <c r="C8" s="330"/>
+      <c r="D8" s="330"/>
+      <c r="E8" s="330"/>
+      <c r="F8" s="330"/>
+      <c r="G8" s="330"/>
+      <c r="H8" s="330"/>
+      <c r="I8" s="330"/>
+      <c r="J8" s="330"/>
+      <c r="L8" s="361" t="s">
+        <v>126</v>
+      </c>
+      <c r="M8" s="361"/>
+      <c r="N8" s="361"/>
+      <c r="O8" s="361"/>
+      <c r="P8" s="361"/>
+      <c r="Q8" s="361"/>
+      <c r="R8" s="361"/>
+      <c r="S8" s="361"/>
+      <c r="T8" s="361"/>
+      <c r="U8" s="361"/>
+    </row>
+    <row r="9" spans="2:21" ht="15.75" thickTop="1">
+      <c r="B9" s="331" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="331"/>
+      <c r="D9" s="331"/>
+      <c r="E9" s="331"/>
+      <c r="F9" s="331"/>
+      <c r="G9" s="331"/>
+      <c r="H9" s="331"/>
+      <c r="I9" s="331"/>
+      <c r="J9" s="331"/>
+      <c r="L9" s="332"/>
+      <c r="M9" s="332"/>
+      <c r="N9" s="332"/>
+      <c r="O9" s="332"/>
+      <c r="P9" s="332"/>
+      <c r="Q9" s="332"/>
+      <c r="R9" s="332"/>
+      <c r="S9" s="332"/>
+      <c r="T9" s="332"/>
+      <c r="U9" s="332"/>
+    </row>
+    <row r="10" spans="2:21">
+      <c r="B10" s="335" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="336"/>
+      <c r="D10" s="336"/>
+      <c r="E10" s="336"/>
+      <c r="F10" s="336"/>
+      <c r="G10" s="336"/>
+      <c r="H10" s="336"/>
+      <c r="I10" s="336"/>
+      <c r="J10" s="336"/>
+      <c r="L10" s="332" t="s">
+        <v>6</v>
+      </c>
+      <c r="M10" s="332"/>
+      <c r="N10" s="332"/>
+      <c r="O10" s="332"/>
+      <c r="P10" s="332"/>
+      <c r="Q10" s="332"/>
+      <c r="R10" s="332"/>
+      <c r="S10" s="332"/>
+      <c r="T10" s="332"/>
+      <c r="U10" s="332"/>
+    </row>
+    <row r="11" spans="2:21">
+      <c r="B11" s="336"/>
+      <c r="C11" s="336"/>
+      <c r="D11" s="336"/>
+      <c r="E11" s="336"/>
+      <c r="F11" s="336"/>
+      <c r="G11" s="336"/>
+      <c r="H11" s="336"/>
+      <c r="I11" s="336"/>
+      <c r="J11" s="336"/>
+      <c r="L11" s="332"/>
+      <c r="M11" s="332"/>
+      <c r="N11" s="332"/>
+      <c r="O11" s="332"/>
+      <c r="P11" s="332"/>
+      <c r="Q11" s="332"/>
+      <c r="R11" s="332"/>
+      <c r="S11" s="332"/>
+      <c r="T11" s="332"/>
+      <c r="U11" s="332"/>
+    </row>
+    <row r="12" spans="2:21" ht="15" customHeight="1">
+      <c r="B12" s="337" t="s">
+        <v>310</v>
+      </c>
+      <c r="C12" s="337"/>
+      <c r="D12" s="337"/>
+      <c r="E12" s="337"/>
+      <c r="F12" s="337"/>
+      <c r="G12" s="337"/>
+      <c r="H12" s="337"/>
+      <c r="I12" s="337"/>
+      <c r="J12" s="337"/>
+      <c r="L12" s="368" t="s">
+        <v>36</v>
+      </c>
+      <c r="M12" s="368"/>
+      <c r="N12" s="368"/>
+      <c r="O12" s="368"/>
+      <c r="P12" s="368"/>
+      <c r="Q12" s="368"/>
+      <c r="R12" s="368"/>
+      <c r="S12" s="368"/>
+      <c r="T12" s="368"/>
+      <c r="U12" s="368"/>
+    </row>
+    <row r="13" spans="2:21" ht="16.5">
+      <c r="B13" s="338"/>
+      <c r="C13" s="338"/>
+      <c r="D13" s="338"/>
+      <c r="E13" s="338"/>
+      <c r="F13" s="338"/>
+      <c r="G13" s="338"/>
+      <c r="H13" s="338"/>
+      <c r="I13" s="338"/>
+      <c r="J13" s="338"/>
+      <c r="L13" s="368"/>
+      <c r="M13" s="368"/>
+      <c r="N13" s="368"/>
+      <c r="O13" s="368"/>
+      <c r="P13" s="368"/>
+      <c r="Q13" s="368"/>
+      <c r="R13" s="368"/>
+      <c r="S13" s="368"/>
+      <c r="T13" s="368"/>
+      <c r="U13" s="368"/>
+    </row>
+    <row r="14" spans="2:21" ht="16.5">
+      <c r="B14" s="339" t="s">
+        <v>443</v>
+      </c>
+      <c r="C14" s="339"/>
+      <c r="D14" s="339"/>
+      <c r="E14" s="339"/>
+      <c r="F14" s="339"/>
+      <c r="G14" s="339"/>
+      <c r="H14" s="339"/>
+      <c r="I14" s="339"/>
+      <c r="J14" s="339"/>
+      <c r="L14" s="368"/>
+      <c r="M14" s="368"/>
+      <c r="N14" s="368"/>
+      <c r="O14" s="368"/>
+      <c r="P14" s="368"/>
+      <c r="Q14" s="368"/>
+      <c r="R14" s="368"/>
+      <c r="S14" s="368"/>
+      <c r="T14" s="368"/>
+      <c r="U14" s="368"/>
+    </row>
+    <row r="15" spans="2:21" ht="18">
+      <c r="B15" s="340" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="340"/>
+      <c r="D15" s="340"/>
+      <c r="E15" s="340"/>
+      <c r="F15" s="340"/>
+      <c r="G15" s="340"/>
+      <c r="H15" s="340"/>
+      <c r="I15" s="340"/>
+      <c r="J15" s="340"/>
+      <c r="L15" s="368"/>
+      <c r="M15" s="368"/>
+      <c r="N15" s="368"/>
+      <c r="O15" s="368"/>
+      <c r="P15" s="368"/>
+      <c r="Q15" s="368"/>
+      <c r="R15" s="368"/>
+      <c r="S15" s="368"/>
+      <c r="T15" s="368"/>
+      <c r="U15" s="368"/>
+    </row>
+    <row r="16" spans="2:21" ht="18">
+      <c r="B16" s="340" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="340"/>
+      <c r="D16" s="340"/>
+      <c r="E16" s="340"/>
+      <c r="F16" s="340"/>
+      <c r="G16" s="340"/>
+      <c r="H16" s="340"/>
+      <c r="I16" s="340"/>
+      <c r="J16" s="340"/>
+      <c r="L16" s="368"/>
+      <c r="M16" s="368"/>
+      <c r="N16" s="368"/>
+      <c r="O16" s="368"/>
+      <c r="P16" s="368"/>
+      <c r="Q16" s="368"/>
+      <c r="R16" s="368"/>
+      <c r="S16" s="368"/>
+      <c r="T16" s="368"/>
+      <c r="U16" s="368"/>
+    </row>
+    <row r="17" spans="2:21">
+      <c r="B17" s="332" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="332"/>
+      <c r="D17" s="332"/>
+      <c r="E17" s="332"/>
+      <c r="F17" s="332"/>
+      <c r="G17" s="332"/>
+      <c r="H17" s="332"/>
+      <c r="I17" s="332"/>
+      <c r="J17" s="332"/>
+      <c r="L17" s="368"/>
+      <c r="M17" s="368"/>
+      <c r="N17" s="368"/>
+      <c r="O17" s="368"/>
+      <c r="P17" s="368"/>
+      <c r="Q17" s="368"/>
+      <c r="R17" s="368"/>
+      <c r="S17" s="368"/>
+      <c r="T17" s="368"/>
+      <c r="U17" s="368"/>
+    </row>
+    <row r="18" spans="2:21">
+      <c r="B18" s="333" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="333"/>
+      <c r="D18" s="333"/>
+      <c r="E18" s="333"/>
+      <c r="F18" s="333"/>
+      <c r="G18" s="333"/>
+      <c r="H18" s="333"/>
+      <c r="I18" s="333"/>
+      <c r="J18" s="333"/>
+      <c r="L18" s="368"/>
+      <c r="M18" s="368"/>
+      <c r="N18" s="368"/>
+      <c r="O18" s="368"/>
+      <c r="P18" s="368"/>
+      <c r="Q18" s="368"/>
+      <c r="R18" s="368"/>
+      <c r="S18" s="368"/>
+      <c r="T18" s="368"/>
+      <c r="U18" s="368"/>
+    </row>
+    <row r="19" spans="2:21">
+      <c r="B19" s="333" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="333"/>
+      <c r="D19" s="333"/>
+      <c r="E19" s="333"/>
+      <c r="F19" s="333"/>
+      <c r="G19" s="333"/>
+      <c r="H19" s="333"/>
+      <c r="I19" s="333"/>
+      <c r="J19" s="333"/>
+      <c r="L19" s="368"/>
+      <c r="M19" s="368"/>
+      <c r="N19" s="368"/>
+      <c r="O19" s="368"/>
+      <c r="P19" s="368"/>
+      <c r="Q19" s="368"/>
+      <c r="R19" s="368"/>
+      <c r="S19" s="368"/>
+      <c r="T19" s="368"/>
+      <c r="U19" s="368"/>
+    </row>
+    <row r="20" spans="2:21" ht="15" customHeight="1">
+      <c r="B20" s="332" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="332"/>
+      <c r="D20" s="332"/>
+      <c r="E20" s="332"/>
+      <c r="F20" s="332"/>
+      <c r="G20" s="332"/>
+      <c r="H20" s="332"/>
+      <c r="I20" s="332"/>
+      <c r="J20" s="332"/>
+      <c r="L20" s="332"/>
+      <c r="M20" s="332"/>
+      <c r="N20" s="332"/>
+      <c r="O20" s="332"/>
+      <c r="P20" s="332"/>
+      <c r="Q20" s="332"/>
+      <c r="R20" s="332"/>
+      <c r="S20" s="332"/>
+      <c r="T20" s="332"/>
+      <c r="U20" s="332"/>
+    </row>
+    <row r="21" spans="2:21">
+      <c r="L21" s="332"/>
+      <c r="M21" s="332"/>
+      <c r="N21" s="332"/>
+      <c r="O21" s="332"/>
+      <c r="P21" s="332"/>
+      <c r="Q21" s="332"/>
+      <c r="R21" s="332"/>
+      <c r="S21" s="332"/>
+      <c r="T21" s="332"/>
+      <c r="U21" s="332"/>
+    </row>
+    <row r="22" spans="2:21" ht="15" customHeight="1">
+      <c r="B22" s="328" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="322"/>
-      <c r="D2" s="322"/>
-      <c r="E2" s="322"/>
-      <c r="F2" s="322"/>
-      <c r="G2" s="322"/>
-      <c r="H2" s="322"/>
-      <c r="I2" s="322"/>
-      <c r="J2" s="322"/>
-      <c r="L2" s="356" t="s">
-        <v>37</v>
-      </c>
-      <c r="M2" s="357"/>
-      <c r="N2" s="357"/>
-      <c r="O2" s="357"/>
-      <c r="P2" s="357"/>
-      <c r="Q2" s="357"/>
-      <c r="R2" s="357"/>
-      <c r="S2" s="357"/>
-      <c r="T2" s="357"/>
-      <c r="U2" s="357"/>
-    </row>
-    <row r="3" spans="2:21">
-      <c r="B3" s="331" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="331"/>
-      <c r="D3" s="331"/>
-      <c r="E3" s="331"/>
-      <c r="F3" s="331"/>
-      <c r="G3" s="331"/>
-      <c r="H3" s="331"/>
-      <c r="I3" s="331"/>
-      <c r="J3" s="331"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="358" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="358"/>
-      <c r="N3" s="358"/>
-      <c r="O3" s="358"/>
-      <c r="P3" s="358"/>
-      <c r="Q3" s="358"/>
-      <c r="R3" s="358"/>
-      <c r="S3" s="358"/>
-      <c r="T3" s="358"/>
-      <c r="U3" s="358"/>
-    </row>
-    <row r="4" spans="2:21" ht="15" customHeight="1">
-      <c r="B4" s="323" t="s">
-        <v>442</v>
-      </c>
-      <c r="C4" s="323"/>
-      <c r="D4" s="323"/>
-      <c r="E4" s="323"/>
-      <c r="F4" s="323"/>
-      <c r="G4" s="323"/>
-      <c r="H4" s="323"/>
-      <c r="I4" s="323"/>
-      <c r="J4" s="323"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="358"/>
-      <c r="M4" s="358"/>
-      <c r="N4" s="358"/>
-      <c r="O4" s="358"/>
-      <c r="P4" s="358"/>
-      <c r="Q4" s="358"/>
-      <c r="R4" s="358"/>
-      <c r="S4" s="358"/>
-      <c r="T4" s="358"/>
-      <c r="U4" s="358"/>
-    </row>
-    <row r="5" spans="2:21" ht="15" customHeight="1">
-      <c r="B5" s="323"/>
-      <c r="C5" s="323"/>
-      <c r="D5" s="323"/>
-      <c r="E5" s="323"/>
-      <c r="F5" s="323"/>
-      <c r="G5" s="323"/>
-      <c r="H5" s="323"/>
-      <c r="I5" s="323"/>
-      <c r="J5" s="323"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="329" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="329"/>
-      <c r="N5" s="329"/>
-      <c r="O5" s="329"/>
-      <c r="P5" s="329"/>
-      <c r="Q5" s="329"/>
-      <c r="R5" s="329"/>
-      <c r="S5" s="329"/>
-      <c r="T5" s="329"/>
-      <c r="U5" s="329"/>
-    </row>
-    <row r="6" spans="2:21" ht="35.25" customHeight="1">
-      <c r="B6" s="323"/>
-      <c r="C6" s="323"/>
-      <c r="D6" s="323"/>
-      <c r="E6" s="323"/>
-      <c r="F6" s="323"/>
-      <c r="G6" s="323"/>
-      <c r="H6" s="323"/>
-      <c r="I6" s="323"/>
-      <c r="J6" s="323"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="353" t="s">
-        <v>147</v>
-      </c>
-      <c r="M6" s="353"/>
-      <c r="N6" s="353"/>
-      <c r="O6" s="353"/>
-      <c r="P6" s="353"/>
-      <c r="Q6" s="353"/>
-      <c r="R6" s="353"/>
-      <c r="S6" s="353"/>
-      <c r="T6" s="353"/>
-      <c r="U6" s="353"/>
-    </row>
-    <row r="7" spans="2:21" ht="15.75" thickBot="1">
-      <c r="B7" s="361" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="361"/>
-      <c r="D7" s="361"/>
-      <c r="E7" s="361"/>
-      <c r="F7" s="361"/>
-      <c r="G7" s="361"/>
-      <c r="H7" s="361"/>
-      <c r="I7" s="361"/>
-      <c r="J7" s="361"/>
-      <c r="K7" s="361"/>
-      <c r="L7" s="354" t="s">
-        <v>359</v>
-      </c>
-      <c r="M7" s="354"/>
-      <c r="N7" s="354"/>
-      <c r="O7" s="354"/>
-      <c r="P7" s="354"/>
-      <c r="Q7" s="354"/>
-      <c r="R7" s="354"/>
-      <c r="S7" s="354"/>
-      <c r="T7" s="354"/>
-      <c r="U7" s="354"/>
-    </row>
-    <row r="8" spans="2:21" ht="88.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B8" s="324" t="s">
-        <v>441</v>
-      </c>
-      <c r="C8" s="324"/>
-      <c r="D8" s="324"/>
-      <c r="E8" s="324"/>
-      <c r="F8" s="324"/>
-      <c r="G8" s="324"/>
-      <c r="H8" s="324"/>
-      <c r="I8" s="324"/>
-      <c r="J8" s="324"/>
-      <c r="L8" s="355" t="s">
-        <v>126</v>
-      </c>
-      <c r="M8" s="355"/>
-      <c r="N8" s="355"/>
-      <c r="O8" s="355"/>
-      <c r="P8" s="355"/>
-      <c r="Q8" s="355"/>
-      <c r="R8" s="355"/>
-      <c r="S8" s="355"/>
-      <c r="T8" s="355"/>
-      <c r="U8" s="355"/>
-    </row>
-    <row r="9" spans="2:21" ht="15.75" thickTop="1">
-      <c r="B9" s="325" t="s">
-        <v>182</v>
-      </c>
-      <c r="C9" s="325"/>
-      <c r="D9" s="325"/>
-      <c r="E9" s="325"/>
-      <c r="F9" s="325"/>
-      <c r="G9" s="325"/>
-      <c r="H9" s="325"/>
-      <c r="I9" s="325"/>
-      <c r="J9" s="325"/>
-      <c r="L9" s="329"/>
-      <c r="M9" s="329"/>
-      <c r="N9" s="329"/>
-      <c r="O9" s="329"/>
-      <c r="P9" s="329"/>
-      <c r="Q9" s="329"/>
-      <c r="R9" s="329"/>
-      <c r="S9" s="329"/>
-      <c r="T9" s="329"/>
-      <c r="U9" s="329"/>
-    </row>
-    <row r="10" spans="2:21">
-      <c r="B10" s="332" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="333"/>
-      <c r="D10" s="333"/>
-      <c r="E10" s="333"/>
-      <c r="F10" s="333"/>
-      <c r="G10" s="333"/>
-      <c r="H10" s="333"/>
-      <c r="I10" s="333"/>
-      <c r="J10" s="333"/>
-      <c r="L10" s="329" t="s">
-        <v>6</v>
-      </c>
-      <c r="M10" s="329"/>
-      <c r="N10" s="329"/>
-      <c r="O10" s="329"/>
-      <c r="P10" s="329"/>
-      <c r="Q10" s="329"/>
-      <c r="R10" s="329"/>
-      <c r="S10" s="329"/>
-      <c r="T10" s="329"/>
-      <c r="U10" s="329"/>
-    </row>
-    <row r="11" spans="2:21">
-      <c r="B11" s="333"/>
-      <c r="C11" s="333"/>
-      <c r="D11" s="333"/>
-      <c r="E11" s="333"/>
-      <c r="F11" s="333"/>
-      <c r="G11" s="333"/>
-      <c r="H11" s="333"/>
-      <c r="I11" s="333"/>
-      <c r="J11" s="333"/>
-      <c r="L11" s="329"/>
-      <c r="M11" s="329"/>
-      <c r="N11" s="329"/>
-      <c r="O11" s="329"/>
-      <c r="P11" s="329"/>
-      <c r="Q11" s="329"/>
-      <c r="R11" s="329"/>
-      <c r="S11" s="329"/>
-      <c r="T11" s="329"/>
-      <c r="U11" s="329"/>
-    </row>
-    <row r="12" spans="2:21" ht="15" customHeight="1">
-      <c r="B12" s="334" t="s">
-        <v>311</v>
-      </c>
-      <c r="C12" s="334"/>
-      <c r="D12" s="334"/>
-      <c r="E12" s="334"/>
-      <c r="F12" s="334"/>
-      <c r="G12" s="334"/>
-      <c r="H12" s="334"/>
-      <c r="I12" s="334"/>
-      <c r="J12" s="334"/>
-      <c r="L12" s="362" t="s">
-        <v>36</v>
-      </c>
-      <c r="M12" s="362"/>
-      <c r="N12" s="362"/>
-      <c r="O12" s="362"/>
-      <c r="P12" s="362"/>
-      <c r="Q12" s="362"/>
-      <c r="R12" s="362"/>
-      <c r="S12" s="362"/>
-      <c r="T12" s="362"/>
-      <c r="U12" s="362"/>
-    </row>
-    <row r="13" spans="2:21" ht="16.5">
-      <c r="B13" s="335"/>
-      <c r="C13" s="335"/>
-      <c r="D13" s="335"/>
-      <c r="E13" s="335"/>
-      <c r="F13" s="335"/>
-      <c r="G13" s="335"/>
-      <c r="H13" s="335"/>
-      <c r="I13" s="335"/>
-      <c r="J13" s="335"/>
-      <c r="L13" s="362"/>
-      <c r="M13" s="362"/>
-      <c r="N13" s="362"/>
-      <c r="O13" s="362"/>
-      <c r="P13" s="362"/>
-      <c r="Q13" s="362"/>
-      <c r="R13" s="362"/>
-      <c r="S13" s="362"/>
-      <c r="T13" s="362"/>
-      <c r="U13" s="362"/>
-    </row>
-    <row r="14" spans="2:21" ht="16.5">
-      <c r="B14" s="336" t="s">
-        <v>353</v>
-      </c>
-      <c r="C14" s="336"/>
-      <c r="D14" s="336"/>
-      <c r="E14" s="336"/>
-      <c r="F14" s="336"/>
-      <c r="G14" s="336"/>
-      <c r="H14" s="336"/>
-      <c r="I14" s="336"/>
-      <c r="J14" s="336"/>
-      <c r="L14" s="362"/>
-      <c r="M14" s="362"/>
-      <c r="N14" s="362"/>
-      <c r="O14" s="362"/>
-      <c r="P14" s="362"/>
-      <c r="Q14" s="362"/>
-      <c r="R14" s="362"/>
-      <c r="S14" s="362"/>
-      <c r="T14" s="362"/>
-      <c r="U14" s="362"/>
-    </row>
-    <row r="15" spans="2:21" ht="18">
-      <c r="B15" s="337" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15" s="337"/>
-      <c r="D15" s="337"/>
-      <c r="E15" s="337"/>
-      <c r="F15" s="337"/>
-      <c r="G15" s="337"/>
-      <c r="H15" s="337"/>
-      <c r="I15" s="337"/>
-      <c r="J15" s="337"/>
-      <c r="L15" s="362"/>
-      <c r="M15" s="362"/>
-      <c r="N15" s="362"/>
-      <c r="O15" s="362"/>
-      <c r="P15" s="362"/>
-      <c r="Q15" s="362"/>
-      <c r="R15" s="362"/>
-      <c r="S15" s="362"/>
-      <c r="T15" s="362"/>
-      <c r="U15" s="362"/>
-    </row>
-    <row r="16" spans="2:21" ht="18">
-      <c r="B16" s="337" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="337"/>
-      <c r="D16" s="337"/>
-      <c r="E16" s="337"/>
-      <c r="F16" s="337"/>
-      <c r="G16" s="337"/>
-      <c r="H16" s="337"/>
-      <c r="I16" s="337"/>
-      <c r="J16" s="337"/>
-      <c r="L16" s="362"/>
-      <c r="M16" s="362"/>
-      <c r="N16" s="362"/>
-      <c r="O16" s="362"/>
-      <c r="P16" s="362"/>
-      <c r="Q16" s="362"/>
-      <c r="R16" s="362"/>
-      <c r="S16" s="362"/>
-      <c r="T16" s="362"/>
-      <c r="U16" s="362"/>
-    </row>
-    <row r="17" spans="2:21">
-      <c r="B17" s="329" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="329"/>
-      <c r="D17" s="329"/>
-      <c r="E17" s="329"/>
-      <c r="F17" s="329"/>
-      <c r="G17" s="329"/>
-      <c r="H17" s="329"/>
-      <c r="I17" s="329"/>
-      <c r="J17" s="329"/>
-      <c r="L17" s="362"/>
-      <c r="M17" s="362"/>
-      <c r="N17" s="362"/>
-      <c r="O17" s="362"/>
-      <c r="P17" s="362"/>
-      <c r="Q17" s="362"/>
-      <c r="R17" s="362"/>
-      <c r="S17" s="362"/>
-      <c r="T17" s="362"/>
-      <c r="U17" s="362"/>
-    </row>
-    <row r="18" spans="2:21">
-      <c r="B18" s="330" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="330"/>
-      <c r="D18" s="330"/>
-      <c r="E18" s="330"/>
-      <c r="F18" s="330"/>
-      <c r="G18" s="330"/>
-      <c r="H18" s="330"/>
-      <c r="I18" s="330"/>
-      <c r="J18" s="330"/>
-      <c r="L18" s="362"/>
-      <c r="M18" s="362"/>
-      <c r="N18" s="362"/>
-      <c r="O18" s="362"/>
-      <c r="P18" s="362"/>
-      <c r="Q18" s="362"/>
-      <c r="R18" s="362"/>
-      <c r="S18" s="362"/>
-      <c r="T18" s="362"/>
-      <c r="U18" s="362"/>
-    </row>
-    <row r="19" spans="2:21">
-      <c r="B19" s="330" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="330"/>
-      <c r="D19" s="330"/>
-      <c r="E19" s="330"/>
-      <c r="F19" s="330"/>
-      <c r="G19" s="330"/>
-      <c r="H19" s="330"/>
-      <c r="I19" s="330"/>
-      <c r="J19" s="330"/>
-      <c r="L19" s="362"/>
-      <c r="M19" s="362"/>
-      <c r="N19" s="362"/>
-      <c r="O19" s="362"/>
-      <c r="P19" s="362"/>
-      <c r="Q19" s="362"/>
-      <c r="R19" s="362"/>
-      <c r="S19" s="362"/>
-      <c r="T19" s="362"/>
-      <c r="U19" s="362"/>
-    </row>
-    <row r="20" spans="2:21" ht="15" customHeight="1">
-      <c r="B20" s="329" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="329"/>
-      <c r="D20" s="329"/>
-      <c r="E20" s="329"/>
-      <c r="F20" s="329"/>
-      <c r="G20" s="329"/>
-      <c r="H20" s="329"/>
-      <c r="I20" s="329"/>
-      <c r="J20" s="329"/>
-      <c r="L20" s="329"/>
-      <c r="M20" s="329"/>
-      <c r="N20" s="329"/>
-      <c r="O20" s="329"/>
-      <c r="P20" s="329"/>
-      <c r="Q20" s="329"/>
-      <c r="R20" s="329"/>
-      <c r="S20" s="329"/>
-      <c r="T20" s="329"/>
-      <c r="U20" s="329"/>
-    </row>
-    <row r="21" spans="2:21">
-      <c r="L21" s="329"/>
-      <c r="M21" s="329"/>
-      <c r="N21" s="329"/>
-      <c r="O21" s="329"/>
-      <c r="P21" s="329"/>
-      <c r="Q21" s="329"/>
-      <c r="R21" s="329"/>
-      <c r="S21" s="329"/>
-      <c r="T21" s="329"/>
-      <c r="U21" s="329"/>
-    </row>
-    <row r="22" spans="2:21" ht="15" customHeight="1">
-      <c r="B22" s="329"/>
-      <c r="C22" s="329"/>
-      <c r="D22" s="329"/>
-      <c r="E22" s="329"/>
-      <c r="F22" s="329"/>
-      <c r="G22" s="329"/>
-      <c r="H22" s="329"/>
-      <c r="I22" s="329"/>
-      <c r="J22" s="329"/>
-      <c r="L22" s="359" t="s">
+      <c r="C22" s="328"/>
+      <c r="D22" s="328"/>
+      <c r="E22" s="328"/>
+      <c r="F22" s="328"/>
+      <c r="G22" s="328"/>
+      <c r="H22" s="328"/>
+      <c r="I22" s="328"/>
+      <c r="J22" s="328"/>
+      <c r="L22" s="365" t="s">
         <v>39</v>
       </c>
-      <c r="M22" s="359"/>
-      <c r="N22" s="359"/>
-      <c r="O22" s="359"/>
-      <c r="P22" s="359"/>
-      <c r="Q22" s="359"/>
-      <c r="R22" s="359"/>
-      <c r="S22" s="359"/>
-      <c r="T22" s="359"/>
-      <c r="U22" s="359"/>
+      <c r="M22" s="365"/>
+      <c r="N22" s="365"/>
+      <c r="O22" s="365"/>
+      <c r="P22" s="365"/>
+      <c r="Q22" s="365"/>
+      <c r="R22" s="365"/>
+      <c r="S22" s="365"/>
+      <c r="T22" s="365"/>
+      <c r="U22" s="365"/>
     </row>
     <row r="23" spans="2:21">
-      <c r="B23" s="329" t="s">
+      <c r="B23" s="332" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="329"/>
-      <c r="D23" s="329"/>
-      <c r="E23" s="329"/>
-      <c r="F23" s="329"/>
-      <c r="G23" s="329"/>
-      <c r="H23" s="329"/>
-      <c r="I23" s="329"/>
-      <c r="J23" s="329"/>
-      <c r="L23" s="359"/>
-      <c r="M23" s="359"/>
-      <c r="N23" s="359"/>
-      <c r="O23" s="359"/>
-      <c r="P23" s="359"/>
-      <c r="Q23" s="359"/>
-      <c r="R23" s="359"/>
-      <c r="S23" s="359"/>
-      <c r="T23" s="359"/>
-      <c r="U23" s="359"/>
+      <c r="C23" s="332"/>
+      <c r="D23" s="332"/>
+      <c r="E23" s="332"/>
+      <c r="F23" s="332"/>
+      <c r="G23" s="332"/>
+      <c r="H23" s="332"/>
+      <c r="I23" s="332"/>
+      <c r="J23" s="332"/>
+      <c r="L23" s="365"/>
+      <c r="M23" s="365"/>
+      <c r="N23" s="365"/>
+      <c r="O23" s="365"/>
+      <c r="P23" s="365"/>
+      <c r="Q23" s="365"/>
+      <c r="R23" s="365"/>
+      <c r="S23" s="365"/>
+      <c r="T23" s="365"/>
+      <c r="U23" s="365"/>
     </row>
     <row r="24" spans="2:21" ht="30" customHeight="1">
-      <c r="B24" s="346" t="s">
-        <v>272</v>
-      </c>
-      <c r="C24" s="347"/>
-      <c r="D24" s="347"/>
-      <c r="E24" s="347"/>
-      <c r="F24" s="347"/>
-      <c r="G24" s="347"/>
-      <c r="H24" s="347"/>
-      <c r="I24" s="347"/>
-      <c r="J24" s="348"/>
-      <c r="L24" s="359"/>
-      <c r="M24" s="359"/>
-      <c r="N24" s="359"/>
-      <c r="O24" s="359"/>
-      <c r="P24" s="359"/>
-      <c r="Q24" s="359"/>
-      <c r="R24" s="359"/>
-      <c r="S24" s="359"/>
-      <c r="T24" s="359"/>
-      <c r="U24" s="359"/>
+      <c r="B24" s="352" t="s">
+        <v>271</v>
+      </c>
+      <c r="C24" s="353"/>
+      <c r="D24" s="353"/>
+      <c r="E24" s="353"/>
+      <c r="F24" s="353"/>
+      <c r="G24" s="353"/>
+      <c r="H24" s="353"/>
+      <c r="I24" s="353"/>
+      <c r="J24" s="354"/>
+      <c r="L24" s="365"/>
+      <c r="M24" s="365"/>
+      <c r="N24" s="365"/>
+      <c r="O24" s="365"/>
+      <c r="P24" s="365"/>
+      <c r="Q24" s="365"/>
+      <c r="R24" s="365"/>
+      <c r="S24" s="365"/>
+      <c r="T24" s="365"/>
+      <c r="U24" s="365"/>
     </row>
     <row r="25" spans="2:21" ht="15.75" customHeight="1">
-      <c r="B25" s="349"/>
-      <c r="C25" s="350"/>
-      <c r="D25" s="350"/>
-      <c r="E25" s="350"/>
-      <c r="F25" s="350"/>
-      <c r="G25" s="350"/>
-      <c r="H25" s="350"/>
-      <c r="I25" s="350"/>
-      <c r="J25" s="351"/>
-      <c r="L25" s="359"/>
-      <c r="M25" s="359"/>
-      <c r="N25" s="359"/>
-      <c r="O25" s="359"/>
-      <c r="P25" s="359"/>
-      <c r="Q25" s="359"/>
-      <c r="R25" s="359"/>
-      <c r="S25" s="359"/>
-      <c r="T25" s="359"/>
-      <c r="U25" s="359"/>
+      <c r="B25" s="355"/>
+      <c r="C25" s="356"/>
+      <c r="D25" s="356"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
+      <c r="G25" s="356"/>
+      <c r="H25" s="356"/>
+      <c r="I25" s="356"/>
+      <c r="J25" s="357"/>
+      <c r="L25" s="365"/>
+      <c r="M25" s="365"/>
+      <c r="N25" s="365"/>
+      <c r="O25" s="365"/>
+      <c r="P25" s="365"/>
+      <c r="Q25" s="365"/>
+      <c r="R25" s="365"/>
+      <c r="S25" s="365"/>
+      <c r="T25" s="365"/>
+      <c r="U25" s="365"/>
     </row>
     <row r="26" spans="2:21" ht="15.75">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="344" t="s">
         <v>86</v>
       </c>
-      <c r="C26" s="339"/>
-      <c r="D26" s="339"/>
-      <c r="E26" s="339"/>
-      <c r="F26" s="339"/>
-      <c r="G26" s="339"/>
-      <c r="H26" s="339"/>
-      <c r="I26" s="339"/>
-      <c r="J26" s="340"/>
-      <c r="L26" s="359"/>
-      <c r="M26" s="359"/>
-      <c r="N26" s="359"/>
-      <c r="O26" s="359"/>
-      <c r="P26" s="359"/>
-      <c r="Q26" s="359"/>
-      <c r="R26" s="359"/>
-      <c r="S26" s="359"/>
-      <c r="T26" s="359"/>
-      <c r="U26" s="359"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
+      <c r="G26" s="345"/>
+      <c r="H26" s="345"/>
+      <c r="I26" s="345"/>
+      <c r="J26" s="346"/>
+      <c r="L26" s="365"/>
+      <c r="M26" s="365"/>
+      <c r="N26" s="365"/>
+      <c r="O26" s="365"/>
+      <c r="P26" s="365"/>
+      <c r="Q26" s="365"/>
+      <c r="R26" s="365"/>
+      <c r="S26" s="365"/>
+      <c r="T26" s="365"/>
+      <c r="U26" s="365"/>
     </row>
     <row r="27" spans="2:21">
-      <c r="B27" s="341" t="s">
+      <c r="B27" s="347" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="342"/>
-      <c r="D27" s="342"/>
-      <c r="E27" s="342"/>
-      <c r="F27" s="342"/>
-      <c r="G27" s="342"/>
-      <c r="H27" s="342"/>
-      <c r="I27" s="342"/>
-      <c r="J27" s="343"/>
-      <c r="L27" s="359"/>
-      <c r="M27" s="359"/>
-      <c r="N27" s="359"/>
-      <c r="O27" s="359"/>
-      <c r="P27" s="359"/>
-      <c r="Q27" s="359"/>
-      <c r="R27" s="359"/>
-      <c r="S27" s="359"/>
-      <c r="T27" s="359"/>
-      <c r="U27" s="359"/>
+      <c r="C27" s="348"/>
+      <c r="D27" s="348"/>
+      <c r="E27" s="348"/>
+      <c r="F27" s="348"/>
+      <c r="G27" s="348"/>
+      <c r="H27" s="348"/>
+      <c r="I27" s="348"/>
+      <c r="J27" s="349"/>
+      <c r="L27" s="365"/>
+      <c r="M27" s="365"/>
+      <c r="N27" s="365"/>
+      <c r="O27" s="365"/>
+      <c r="P27" s="365"/>
+      <c r="Q27" s="365"/>
+      <c r="R27" s="365"/>
+      <c r="S27" s="365"/>
+      <c r="T27" s="365"/>
+      <c r="U27" s="365"/>
     </row>
     <row r="28" spans="2:21">
-      <c r="B28" s="344" t="s">
+      <c r="B28" s="350" t="s">
         <v>228</v>
       </c>
-      <c r="C28" s="344"/>
-      <c r="D28" s="344"/>
-      <c r="E28" s="344"/>
-      <c r="F28" s="344"/>
-      <c r="G28" s="344"/>
-      <c r="H28" s="344"/>
-      <c r="I28" s="344"/>
-      <c r="J28" s="344"/>
-      <c r="L28" s="359"/>
-      <c r="M28" s="359"/>
-      <c r="N28" s="359"/>
-      <c r="O28" s="359"/>
-      <c r="P28" s="359"/>
-      <c r="Q28" s="359"/>
-      <c r="R28" s="359"/>
-      <c r="S28" s="359"/>
-      <c r="T28" s="359"/>
-      <c r="U28" s="359"/>
+      <c r="C28" s="350"/>
+      <c r="D28" s="350"/>
+      <c r="E28" s="350"/>
+      <c r="F28" s="350"/>
+      <c r="G28" s="350"/>
+      <c r="H28" s="350"/>
+      <c r="I28" s="350"/>
+      <c r="J28" s="350"/>
+      <c r="L28" s="365"/>
+      <c r="M28" s="365"/>
+      <c r="N28" s="365"/>
+      <c r="O28" s="365"/>
+      <c r="P28" s="365"/>
+      <c r="Q28" s="365"/>
+      <c r="R28" s="365"/>
+      <c r="S28" s="365"/>
+      <c r="T28" s="365"/>
+      <c r="U28" s="365"/>
     </row>
     <row r="29" spans="2:21" ht="16.5">
-      <c r="B29" s="345" t="s">
-        <v>352</v>
-      </c>
-      <c r="C29" s="345"/>
-      <c r="D29" s="345"/>
-      <c r="E29" s="345"/>
-      <c r="F29" s="345"/>
-      <c r="G29" s="345"/>
-      <c r="H29" s="345"/>
-      <c r="I29" s="345"/>
-      <c r="J29" s="345"/>
-      <c r="L29" s="359"/>
-      <c r="M29" s="359"/>
-      <c r="N29" s="359"/>
-      <c r="O29" s="359"/>
-      <c r="P29" s="359"/>
-      <c r="Q29" s="359"/>
-      <c r="R29" s="359"/>
-      <c r="S29" s="359"/>
-      <c r="T29" s="359"/>
-      <c r="U29" s="359"/>
+      <c r="B29" s="351" t="s">
+        <v>351</v>
+      </c>
+      <c r="C29" s="351"/>
+      <c r="D29" s="351"/>
+      <c r="E29" s="351"/>
+      <c r="F29" s="351"/>
+      <c r="G29" s="351"/>
+      <c r="H29" s="351"/>
+      <c r="I29" s="351"/>
+      <c r="J29" s="351"/>
+      <c r="L29" s="365"/>
+      <c r="M29" s="365"/>
+      <c r="N29" s="365"/>
+      <c r="O29" s="365"/>
+      <c r="P29" s="365"/>
+      <c r="Q29" s="365"/>
+      <c r="R29" s="365"/>
+      <c r="S29" s="365"/>
+      <c r="T29" s="365"/>
+      <c r="U29" s="365"/>
     </row>
     <row r="30" spans="2:21">
-      <c r="B30" s="329" t="s">
-        <v>363</v>
-      </c>
-      <c r="C30" s="329"/>
-      <c r="D30" s="329"/>
-      <c r="E30" s="329"/>
-      <c r="F30" s="329"/>
-      <c r="G30" s="329"/>
-      <c r="H30" s="329"/>
-      <c r="I30" s="329"/>
-      <c r="J30" s="329"/>
-      <c r="L30" s="359"/>
-      <c r="M30" s="359"/>
-      <c r="N30" s="359"/>
-      <c r="O30" s="359"/>
-      <c r="P30" s="359"/>
-      <c r="Q30" s="359"/>
-      <c r="R30" s="359"/>
-      <c r="S30" s="359"/>
-      <c r="T30" s="359"/>
-      <c r="U30" s="359"/>
+      <c r="B30" s="332" t="s">
+        <v>361</v>
+      </c>
+      <c r="C30" s="332"/>
+      <c r="D30" s="332"/>
+      <c r="E30" s="332"/>
+      <c r="F30" s="332"/>
+      <c r="G30" s="332"/>
+      <c r="H30" s="332"/>
+      <c r="I30" s="332"/>
+      <c r="J30" s="332"/>
+      <c r="L30" s="365"/>
+      <c r="M30" s="365"/>
+      <c r="N30" s="365"/>
+      <c r="O30" s="365"/>
+      <c r="P30" s="365"/>
+      <c r="Q30" s="365"/>
+      <c r="R30" s="365"/>
+      <c r="S30" s="365"/>
+      <c r="T30" s="365"/>
+      <c r="U30" s="365"/>
     </row>
     <row r="31" spans="2:21">
-      <c r="B31" s="329" t="s">
+      <c r="B31" s="332" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="329"/>
-      <c r="D31" s="329"/>
-      <c r="E31" s="329"/>
-      <c r="F31" s="329"/>
-      <c r="G31" s="329"/>
-      <c r="H31" s="329"/>
-      <c r="I31" s="329"/>
-      <c r="J31" s="329"/>
-      <c r="L31" s="359"/>
-      <c r="M31" s="359"/>
-      <c r="N31" s="359"/>
-      <c r="O31" s="359"/>
-      <c r="P31" s="359"/>
-      <c r="Q31" s="359"/>
-      <c r="R31" s="359"/>
-      <c r="S31" s="359"/>
-      <c r="T31" s="359"/>
-      <c r="U31" s="359"/>
+      <c r="C31" s="332"/>
+      <c r="D31" s="332"/>
+      <c r="E31" s="332"/>
+      <c r="F31" s="332"/>
+      <c r="G31" s="332"/>
+      <c r="H31" s="332"/>
+      <c r="I31" s="332"/>
+      <c r="J31" s="332"/>
+      <c r="L31" s="365"/>
+      <c r="M31" s="365"/>
+      <c r="N31" s="365"/>
+      <c r="O31" s="365"/>
+      <c r="P31" s="365"/>
+      <c r="Q31" s="365"/>
+      <c r="R31" s="365"/>
+      <c r="S31" s="365"/>
+      <c r="T31" s="365"/>
+      <c r="U31" s="365"/>
     </row>
     <row r="32" spans="2:21">
-      <c r="B32" s="329" t="s">
+      <c r="B32" s="332" t="s">
         <v>111</v>
       </c>
-      <c r="C32" s="329"/>
-      <c r="D32" s="329"/>
-      <c r="E32" s="329"/>
-      <c r="F32" s="329"/>
-      <c r="G32" s="329"/>
-      <c r="H32" s="329"/>
-      <c r="I32" s="329"/>
-      <c r="J32" s="329"/>
-      <c r="L32" s="359"/>
-      <c r="M32" s="359"/>
-      <c r="N32" s="359"/>
-      <c r="O32" s="359"/>
-      <c r="P32" s="359"/>
-      <c r="Q32" s="359"/>
-      <c r="R32" s="359"/>
-      <c r="S32" s="359"/>
-      <c r="T32" s="359"/>
-      <c r="U32" s="359"/>
+      <c r="C32" s="332"/>
+      <c r="D32" s="332"/>
+      <c r="E32" s="332"/>
+      <c r="F32" s="332"/>
+      <c r="G32" s="332"/>
+      <c r="H32" s="332"/>
+      <c r="I32" s="332"/>
+      <c r="J32" s="332"/>
+      <c r="L32" s="365"/>
+      <c r="M32" s="365"/>
+      <c r="N32" s="365"/>
+      <c r="O32" s="365"/>
+      <c r="P32" s="365"/>
+      <c r="Q32" s="365"/>
+      <c r="R32" s="365"/>
+      <c r="S32" s="365"/>
+      <c r="T32" s="365"/>
+      <c r="U32" s="365"/>
     </row>
     <row r="34" spans="3:21">
-      <c r="C34" s="328" t="s">
+      <c r="C34" s="343" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="328"/>
+      <c r="D34" s="343"/>
       <c r="E34" s="27"/>
       <c r="G34" s="191" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="35" spans="3:21">
-      <c r="C35" s="328" t="s">
+      <c r="C35" s="343" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="328"/>
+      <c r="D35" s="343"/>
       <c r="E35" s="27"/>
       <c r="G35" s="191" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="36" spans="3:21">
-      <c r="C36" s="328" t="s">
+      <c r="C36" s="343" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="328"/>
+      <c r="D36" s="343"/>
       <c r="E36" s="27"/>
       <c r="G36" s="191" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="37" spans="3:21">
-      <c r="C37" s="328" t="s">
+      <c r="C37" s="343" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="328"/>
+      <c r="D37" s="343"/>
       <c r="E37" s="27"/>
       <c r="G37" s="191" t="s">
         <v>102</v>
       </c>
-      <c r="L37" s="329" t="s">
+      <c r="L37" s="332" t="s">
         <v>7</v>
       </c>
-      <c r="M37" s="329"/>
-      <c r="N37" s="329"/>
-      <c r="O37" s="329"/>
-      <c r="P37" s="329"/>
-      <c r="Q37" s="329"/>
-      <c r="R37" s="329"/>
-      <c r="S37" s="329"/>
-      <c r="T37" s="329"/>
-      <c r="U37" s="329"/>
+      <c r="M37" s="332"/>
+      <c r="N37" s="332"/>
+      <c r="O37" s="332"/>
+      <c r="P37" s="332"/>
+      <c r="Q37" s="332"/>
+      <c r="R37" s="332"/>
+      <c r="S37" s="332"/>
+      <c r="T37" s="332"/>
+      <c r="U37" s="332"/>
     </row>
     <row r="38" spans="3:21">
-      <c r="C38" s="328" t="s">
+      <c r="C38" s="343" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="328"/>
+      <c r="D38" s="343"/>
       <c r="E38" s="27"/>
-      <c r="L38" s="329" t="s">
+      <c r="L38" s="332" t="s">
         <v>8</v>
       </c>
-      <c r="M38" s="329"/>
-      <c r="N38" s="329"/>
-      <c r="O38" s="329"/>
-      <c r="P38" s="329"/>
-      <c r="Q38" s="329"/>
-      <c r="R38" s="329"/>
-      <c r="S38" s="329"/>
-      <c r="T38" s="329"/>
-      <c r="U38" s="329"/>
+      <c r="M38" s="332"/>
+      <c r="N38" s="332"/>
+      <c r="O38" s="332"/>
+      <c r="P38" s="332"/>
+      <c r="Q38" s="332"/>
+      <c r="R38" s="332"/>
+      <c r="S38" s="332"/>
+      <c r="T38" s="332"/>
+      <c r="U38" s="332"/>
     </row>
     <row r="39" spans="3:21">
-      <c r="L39" s="329" t="s">
+      <c r="L39" s="332" t="s">
         <v>9</v>
       </c>
-      <c r="M39" s="329"/>
-      <c r="N39" s="329"/>
-      <c r="O39" s="329"/>
-      <c r="P39" s="329"/>
-      <c r="Q39" s="329"/>
-      <c r="R39" s="329"/>
-      <c r="S39" s="329"/>
-      <c r="T39" s="329"/>
-      <c r="U39" s="329"/>
+      <c r="M39" s="332"/>
+      <c r="N39" s="332"/>
+      <c r="O39" s="332"/>
+      <c r="P39" s="332"/>
+      <c r="Q39" s="332"/>
+      <c r="R39" s="332"/>
+      <c r="S39" s="332"/>
+      <c r="T39" s="332"/>
+      <c r="U39" s="332"/>
     </row>
     <row r="40" spans="3:21">
-      <c r="L40" s="329" t="s">
+      <c r="L40" s="332" t="s">
         <v>11</v>
       </c>
-      <c r="M40" s="329"/>
-      <c r="N40" s="329"/>
-      <c r="O40" s="329"/>
-      <c r="P40" s="329"/>
-      <c r="Q40" s="329"/>
-      <c r="R40" s="329"/>
-      <c r="S40" s="329"/>
-      <c r="T40" s="329"/>
-      <c r="U40" s="329"/>
+      <c r="M40" s="332"/>
+      <c r="N40" s="332"/>
+      <c r="O40" s="332"/>
+      <c r="P40" s="332"/>
+      <c r="Q40" s="332"/>
+      <c r="R40" s="332"/>
+      <c r="S40" s="332"/>
+      <c r="T40" s="332"/>
+      <c r="U40" s="332"/>
     </row>
     <row r="41" spans="3:21">
-      <c r="E41" s="326" t="s">
+      <c r="E41" s="341" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="327"/>
-      <c r="G41" s="327"/>
-      <c r="H41" s="327"/>
-      <c r="I41" s="327"/>
-      <c r="J41" s="327"/>
-      <c r="L41" s="360" t="s">
+      <c r="F41" s="342"/>
+      <c r="G41" s="342"/>
+      <c r="H41" s="342"/>
+      <c r="I41" s="342"/>
+      <c r="J41" s="342"/>
+      <c r="L41" s="366" t="s">
         <v>18</v>
       </c>
-      <c r="M41" s="329"/>
-      <c r="N41" s="329"/>
-      <c r="O41" s="329"/>
-      <c r="P41" s="329"/>
-      <c r="Q41" s="329"/>
-      <c r="R41" s="329"/>
-      <c r="S41" s="329"/>
-      <c r="T41" s="329"/>
-      <c r="U41" s="329"/>
+      <c r="M41" s="332"/>
+      <c r="N41" s="332"/>
+      <c r="O41" s="332"/>
+      <c r="P41" s="332"/>
+      <c r="Q41" s="332"/>
+      <c r="R41" s="332"/>
+      <c r="S41" s="332"/>
+      <c r="T41" s="332"/>
+      <c r="U41" s="332"/>
     </row>
     <row r="42" spans="3:21">
-      <c r="E42" s="327"/>
-      <c r="F42" s="327"/>
-      <c r="G42" s="327"/>
-      <c r="H42" s="327"/>
-      <c r="I42" s="327"/>
-      <c r="J42" s="327"/>
-      <c r="L42" s="329"/>
-      <c r="M42" s="329"/>
-      <c r="N42" s="329"/>
-      <c r="O42" s="329"/>
-      <c r="P42" s="329"/>
-      <c r="Q42" s="329"/>
-      <c r="R42" s="329"/>
-      <c r="S42" s="329"/>
-      <c r="T42" s="329"/>
-      <c r="U42" s="329"/>
+      <c r="E42" s="342"/>
+      <c r="F42" s="342"/>
+      <c r="G42" s="342"/>
+      <c r="H42" s="342"/>
+      <c r="I42" s="342"/>
+      <c r="J42" s="342"/>
+      <c r="L42" s="332"/>
+      <c r="M42" s="332"/>
+      <c r="N42" s="332"/>
+      <c r="O42" s="332"/>
+      <c r="P42" s="332"/>
+      <c r="Q42" s="332"/>
+      <c r="R42" s="332"/>
+      <c r="S42" s="332"/>
+      <c r="T42" s="332"/>
+      <c r="U42" s="332"/>
     </row>
     <row r="43" spans="3:21">
-      <c r="E43" s="327"/>
-      <c r="F43" s="327"/>
-      <c r="G43" s="327"/>
-      <c r="H43" s="327"/>
-      <c r="I43" s="327"/>
-      <c r="J43" s="327"/>
-      <c r="L43" s="329"/>
-      <c r="M43" s="329"/>
-      <c r="N43" s="329"/>
-      <c r="O43" s="329"/>
-      <c r="P43" s="329"/>
-      <c r="Q43" s="329"/>
-      <c r="R43" s="329"/>
-      <c r="S43" s="329"/>
-      <c r="T43" s="329"/>
-      <c r="U43" s="329"/>
+      <c r="E43" s="342"/>
+      <c r="F43" s="342"/>
+      <c r="G43" s="342"/>
+      <c r="H43" s="342"/>
+      <c r="I43" s="342"/>
+      <c r="J43" s="342"/>
+      <c r="L43" s="332"/>
+      <c r="M43" s="332"/>
+      <c r="N43" s="332"/>
+      <c r="O43" s="332"/>
+      <c r="P43" s="332"/>
+      <c r="Q43" s="332"/>
+      <c r="R43" s="332"/>
+      <c r="S43" s="332"/>
+      <c r="T43" s="332"/>
+      <c r="U43" s="332"/>
     </row>
     <row r="44" spans="3:21">
-      <c r="E44" s="327"/>
-      <c r="F44" s="327"/>
-      <c r="G44" s="327"/>
-      <c r="H44" s="327"/>
-      <c r="I44" s="327"/>
-      <c r="J44" s="327"/>
+      <c r="E44" s="342"/>
+      <c r="F44" s="342"/>
+      <c r="G44" s="342"/>
+      <c r="H44" s="342"/>
+      <c r="I44" s="342"/>
+      <c r="J44" s="342"/>
     </row>
     <row r="45" spans="3:21">
-      <c r="E45" s="327"/>
-      <c r="F45" s="327"/>
-      <c r="G45" s="327"/>
-      <c r="H45" s="327"/>
-      <c r="I45" s="327"/>
-      <c r="J45" s="327"/>
-      <c r="L45" s="329"/>
-      <c r="M45" s="329"/>
-      <c r="N45" s="329"/>
-      <c r="O45" s="329"/>
-      <c r="P45" s="329"/>
-      <c r="Q45" s="329"/>
-      <c r="R45" s="329"/>
-      <c r="S45" s="329"/>
-      <c r="T45" s="329"/>
-      <c r="U45" s="329"/>
+      <c r="E45" s="342"/>
+      <c r="F45" s="342"/>
+      <c r="G45" s="342"/>
+      <c r="H45" s="342"/>
+      <c r="I45" s="342"/>
+      <c r="J45" s="342"/>
+      <c r="L45" s="332"/>
+      <c r="M45" s="332"/>
+      <c r="N45" s="332"/>
+      <c r="O45" s="332"/>
+      <c r="P45" s="332"/>
+      <c r="Q45" s="332"/>
+      <c r="R45" s="332"/>
+      <c r="S45" s="332"/>
+      <c r="T45" s="332"/>
+      <c r="U45" s="332"/>
     </row>
     <row r="46" spans="3:21">
-      <c r="E46" s="327"/>
-      <c r="F46" s="327"/>
-      <c r="G46" s="327"/>
-      <c r="H46" s="327"/>
-      <c r="I46" s="327"/>
-      <c r="J46" s="327"/>
-      <c r="L46" s="329"/>
-      <c r="M46" s="329"/>
-      <c r="N46" s="329"/>
-      <c r="O46" s="329"/>
-      <c r="P46" s="329"/>
-      <c r="Q46" s="329"/>
-      <c r="R46" s="329"/>
-      <c r="S46" s="329"/>
-      <c r="T46" s="329"/>
-      <c r="U46" s="329"/>
+      <c r="E46" s="342"/>
+      <c r="F46" s="342"/>
+      <c r="G46" s="342"/>
+      <c r="H46" s="342"/>
+      <c r="I46" s="342"/>
+      <c r="J46" s="342"/>
+      <c r="L46" s="332"/>
+      <c r="M46" s="332"/>
+      <c r="N46" s="332"/>
+      <c r="O46" s="332"/>
+      <c r="P46" s="332"/>
+      <c r="Q46" s="332"/>
+      <c r="R46" s="332"/>
+      <c r="S46" s="332"/>
+      <c r="T46" s="332"/>
+      <c r="U46" s="332"/>
     </row>
     <row r="47" spans="3:21">
-      <c r="E47" s="327"/>
-      <c r="F47" s="327"/>
-      <c r="G47" s="327"/>
-      <c r="H47" s="327"/>
-      <c r="I47" s="327"/>
-      <c r="J47" s="327"/>
-      <c r="L47" s="329"/>
-      <c r="M47" s="329"/>
-      <c r="N47" s="329"/>
-      <c r="O47" s="329"/>
-      <c r="P47" s="329"/>
-      <c r="Q47" s="329"/>
-      <c r="R47" s="329"/>
-      <c r="S47" s="329"/>
-      <c r="T47" s="329"/>
-      <c r="U47" s="329"/>
+      <c r="E47" s="342"/>
+      <c r="F47" s="342"/>
+      <c r="G47" s="342"/>
+      <c r="H47" s="342"/>
+      <c r="I47" s="342"/>
+      <c r="J47" s="342"/>
+      <c r="L47" s="332"/>
+      <c r="M47" s="332"/>
+      <c r="N47" s="332"/>
+      <c r="O47" s="332"/>
+      <c r="P47" s="332"/>
+      <c r="Q47" s="332"/>
+      <c r="R47" s="332"/>
+      <c r="S47" s="332"/>
+      <c r="T47" s="332"/>
+      <c r="U47" s="332"/>
     </row>
     <row r="48" spans="3:21">
-      <c r="E48" s="327"/>
-      <c r="F48" s="327"/>
-      <c r="G48" s="327"/>
-      <c r="H48" s="327"/>
-      <c r="I48" s="327"/>
-      <c r="J48" s="327"/>
+      <c r="E48" s="342"/>
+      <c r="F48" s="342"/>
+      <c r="G48" s="342"/>
+      <c r="H48" s="342"/>
+      <c r="I48" s="342"/>
+      <c r="J48" s="342"/>
     </row>
     <row r="49" spans="5:10">
-      <c r="E49" s="327"/>
-      <c r="F49" s="327"/>
-      <c r="G49" s="327"/>
-      <c r="H49" s="327"/>
-      <c r="I49" s="327"/>
-      <c r="J49" s="327"/>
+      <c r="E49" s="342"/>
+      <c r="F49" s="342"/>
+      <c r="G49" s="342"/>
+      <c r="H49" s="342"/>
+      <c r="I49" s="342"/>
+      <c r="J49" s="342"/>
     </row>
     <row r="50" spans="5:10">
-      <c r="E50" s="327"/>
-      <c r="F50" s="327"/>
-      <c r="G50" s="327"/>
-      <c r="H50" s="327"/>
-      <c r="I50" s="327"/>
-      <c r="J50" s="327"/>
+      <c r="E50" s="342"/>
+      <c r="F50" s="342"/>
+      <c r="G50" s="342"/>
+      <c r="H50" s="342"/>
+      <c r="I50" s="342"/>
+      <c r="J50" s="342"/>
     </row>
   </sheetData>
   <mergeCells count="58">
@@ -17746,7 +17974,6 @@
     <mergeCell ref="L3:U3"/>
     <mergeCell ref="L4:U4"/>
     <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B22:J22"/>
     <mergeCell ref="B23:J23"/>
     <mergeCell ref="B26:J26"/>
     <mergeCell ref="B27:J27"/>
@@ -17755,27 +17982,28 @@
     <mergeCell ref="B30:J30"/>
     <mergeCell ref="B31:J31"/>
     <mergeCell ref="B24:J25"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="B19:J19"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B4:J6"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B9:J9"/>
     <mergeCell ref="E41:J50"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B4:J6"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B9:J9"/>
     <mergeCell ref="B17:J17"/>
     <mergeCell ref="B18:J18"/>
     <mergeCell ref="B20:J20"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B10:J11"/>
     <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="B19:J19"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L41" r:id="rId1"/>
@@ -18236,10 +18464,10 @@
       <c r="I16" s="40"/>
       <c r="J16" s="157"/>
       <c r="K16" s="149"/>
-      <c r="L16" s="367" t="s">
+      <c r="L16" s="373" t="s">
         <v>82</v>
       </c>
-      <c r="M16" s="368"/>
+      <c r="M16" s="374"/>
     </row>
     <row r="17" spans="1:14" ht="16.5">
       <c r="A17" s="41">
@@ -18304,8 +18532,8 @@
       <c r="I20" s="40"/>
       <c r="J20" s="157"/>
       <c r="K20" s="155"/>
-      <c r="L20" s="370"/>
-      <c r="M20" s="329"/>
+      <c r="L20" s="376"/>
+      <c r="M20" s="332"/>
       <c r="N20" s="172">
         <v>-0.5</v>
       </c>
@@ -18451,13 +18679,13 @@
       <c r="G28" s="110"/>
       <c r="H28" s="174"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="371" t="s">
+      <c r="J28" s="377" t="s">
         <v>83</v>
       </c>
-      <c r="K28" s="369"/>
-      <c r="L28" s="369"/>
-      <c r="M28" s="369"/>
-      <c r="N28" s="369"/>
+      <c r="K28" s="375"/>
+      <c r="L28" s="375"/>
+      <c r="M28" s="375"/>
+      <c r="N28" s="375"/>
     </row>
     <row r="29" spans="1:14" ht="22.5" customHeight="1">
       <c r="A29" s="41">
@@ -18471,11 +18699,11 @@
       <c r="G29" s="110"/>
       <c r="H29" s="174"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="369"/>
-      <c r="K29" s="369"/>
-      <c r="L29" s="369"/>
-      <c r="M29" s="369"/>
-      <c r="N29" s="369"/>
+      <c r="J29" s="375"/>
+      <c r="K29" s="375"/>
+      <c r="L29" s="375"/>
+      <c r="M29" s="375"/>
+      <c r="N29" s="375"/>
     </row>
     <row r="30" spans="1:14" ht="21.75" customHeight="1">
       <c r="A30" s="41">
@@ -19121,8 +19349,8 @@
       <c r="I20" s="40"/>
       <c r="J20" s="157"/>
       <c r="K20" s="155"/>
-      <c r="L20" s="370"/>
-      <c r="M20" s="329"/>
+      <c r="L20" s="376"/>
+      <c r="M20" s="332"/>
       <c r="N20" s="188"/>
     </row>
     <row r="21" spans="1:14" ht="16.5">
@@ -19258,13 +19486,13 @@
       <c r="G28" s="110"/>
       <c r="H28" s="190"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="371" t="s">
+      <c r="J28" s="377" t="s">
         <v>83</v>
       </c>
-      <c r="K28" s="369"/>
-      <c r="L28" s="369"/>
-      <c r="M28" s="369"/>
-      <c r="N28" s="369"/>
+      <c r="K28" s="375"/>
+      <c r="L28" s="375"/>
+      <c r="M28" s="375"/>
+      <c r="N28" s="375"/>
     </row>
     <row r="29" spans="1:14" ht="22.5" customHeight="1">
       <c r="A29" s="41">
@@ -19278,11 +19506,11 @@
       <c r="G29" s="110"/>
       <c r="H29" s="190"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="369"/>
-      <c r="K29" s="369"/>
-      <c r="L29" s="369"/>
-      <c r="M29" s="369"/>
-      <c r="N29" s="369"/>
+      <c r="J29" s="375"/>
+      <c r="K29" s="375"/>
+      <c r="L29" s="375"/>
+      <c r="M29" s="375"/>
+      <c r="N29" s="375"/>
     </row>
     <row r="30" spans="1:14" ht="21.75" customHeight="1">
       <c r="A30" s="41">
@@ -19975,8 +20203,8 @@
       <c r="K20" s="40"/>
       <c r="L20" s="157"/>
       <c r="M20" s="155"/>
-      <c r="N20" s="370"/>
-      <c r="O20" s="329"/>
+      <c r="N20" s="376"/>
+      <c r="O20" s="332"/>
       <c r="P20" s="195"/>
     </row>
     <row r="21" spans="1:16" ht="16.5">
@@ -20127,13 +20355,13 @@
       <c r="I28" s="199"/>
       <c r="J28" s="199"/>
       <c r="K28" s="40"/>
-      <c r="L28" s="371" t="s">
+      <c r="L28" s="377" t="s">
         <v>103</v>
       </c>
-      <c r="M28" s="369"/>
-      <c r="N28" s="369"/>
-      <c r="O28" s="369"/>
-      <c r="P28" s="369"/>
+      <c r="M28" s="375"/>
+      <c r="N28" s="375"/>
+      <c r="O28" s="375"/>
+      <c r="P28" s="375"/>
     </row>
     <row r="29" spans="1:16" ht="22.5" customHeight="1">
       <c r="A29" s="41">
@@ -20149,11 +20377,11 @@
       <c r="I29" s="199"/>
       <c r="J29" s="199"/>
       <c r="K29" s="40"/>
-      <c r="L29" s="369"/>
-      <c r="M29" s="369"/>
-      <c r="N29" s="369"/>
-      <c r="O29" s="369"/>
-      <c r="P29" s="369"/>
+      <c r="L29" s="375"/>
+      <c r="M29" s="375"/>
+      <c r="N29" s="375"/>
+      <c r="O29" s="375"/>
+      <c r="P29" s="375"/>
     </row>
     <row r="30" spans="1:16" ht="21.75" customHeight="1">
       <c r="A30" s="41">
@@ -20352,12 +20580,12 @@
         <f>SUM(B3:B33)</f>
         <v>3</v>
       </c>
-      <c r="P1" s="363" t="s">
+      <c r="P1" s="369" t="s">
         <v>112</v>
       </c>
-      <c r="Q1" s="364"/>
-      <c r="R1" s="364"/>
-      <c r="S1" s="364"/>
+      <c r="Q1" s="370"/>
+      <c r="R1" s="370"/>
+      <c r="S1" s="370"/>
     </row>
     <row r="2" spans="1:19" ht="18" thickTop="1" thickBot="1">
       <c r="B2" s="211">
@@ -21167,16 +21395,16 @@
       </c>
     </row>
     <row r="41" spans="1:17">
-      <c r="N41" s="329"/>
-      <c r="O41" s="329"/>
-      <c r="P41" s="329"/>
-      <c r="Q41" s="329"/>
+      <c r="N41" s="332"/>
+      <c r="O41" s="332"/>
+      <c r="P41" s="332"/>
+      <c r="Q41" s="332"/>
     </row>
     <row r="42" spans="1:17">
-      <c r="N42" s="327"/>
-      <c r="O42" s="327"/>
-      <c r="P42" s="327"/>
-      <c r="Q42" s="327"/>
+      <c r="N42" s="342"/>
+      <c r="O42" s="342"/>
+      <c r="P42" s="342"/>
+      <c r="Q42" s="342"/>
     </row>
     <row r="43" spans="1:17">
       <c r="N43" s="46" t="s">
@@ -21347,7 +21575,7 @@
     </row>
     <row r="23" spans="4:6" ht="18.75" thickBot="1">
       <c r="D23" s="88" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E23" s="89">
         <v>22</v>
@@ -21371,7 +21599,7 @@
     </row>
     <row r="26" spans="4:6" ht="15.75" thickBot="1">
       <c r="D26" s="57" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E26" s="58">
         <v>36</v>
@@ -21379,7 +21607,7 @@
     </row>
     <row r="27" spans="4:6" ht="15.75" thickBot="1">
       <c r="D27" s="57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E27" s="58">
         <v>21</v>
@@ -21394,7 +21622,7 @@
         <v>201</v>
       </c>
       <c r="F28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="4:6" ht="15.75" thickBot="1">
@@ -21607,12 +21835,12 @@
         <f>SUM(B3:B33)</f>
         <v>50.25</v>
       </c>
-      <c r="P1" s="363" t="s">
+      <c r="P1" s="369" t="s">
         <v>112</v>
       </c>
-      <c r="Q1" s="364"/>
-      <c r="R1" s="364"/>
-      <c r="S1" s="364"/>
+      <c r="Q1" s="370"/>
+      <c r="R1" s="370"/>
+      <c r="S1" s="370"/>
     </row>
     <row r="2" spans="1:19" ht="18" thickTop="1" thickBot="1">
       <c r="A2" s="219" t="s">
@@ -22201,7 +22429,7 @@
       <c r="G17" s="110"/>
       <c r="J17" s="39"/>
       <c r="K17" s="40" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="L17" s="227" t="s">
         <v>153</v>
@@ -22229,7 +22457,7 @@
       <c r="I18" s="223"/>
       <c r="J18" s="223"/>
       <c r="K18" s="40" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="L18" s="229" t="s">
         <v>158</v>
@@ -22255,7 +22483,7 @@
       <c r="I19" s="223"/>
       <c r="J19" s="223"/>
       <c r="K19" s="40" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="L19" s="227" t="s">
         <v>151</v>
@@ -22287,7 +22515,7 @@
       <c r="I20" s="223"/>
       <c r="J20" s="223"/>
       <c r="K20" s="40" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="L20" s="230" t="s">
         <v>146</v>
@@ -22743,16 +22971,16 @@
       </c>
     </row>
     <row r="41" spans="1:17">
-      <c r="N41" s="329"/>
-      <c r="O41" s="329"/>
-      <c r="P41" s="329"/>
-      <c r="Q41" s="329"/>
+      <c r="N41" s="332"/>
+      <c r="O41" s="332"/>
+      <c r="P41" s="332"/>
+      <c r="Q41" s="332"/>
     </row>
     <row r="42" spans="1:17">
-      <c r="N42" s="327"/>
-      <c r="O42" s="327"/>
-      <c r="P42" s="327"/>
-      <c r="Q42" s="327"/>
+      <c r="N42" s="342"/>
+      <c r="O42" s="342"/>
+      <c r="P42" s="342"/>
+      <c r="Q42" s="342"/>
     </row>
     <row r="43" spans="1:17">
       <c r="N43" s="219" t="s">
@@ -22885,10 +23113,10 @@
         <f>SUM(B3:B30)</f>
         <v>36</v>
       </c>
-      <c r="P1" s="365" t="s">
+      <c r="P1" s="371" t="s">
         <v>197</v>
       </c>
-      <c r="Q1" s="365"/>
+      <c r="Q1" s="371"/>
     </row>
     <row r="2" spans="1:17" ht="16.5">
       <c r="B2" s="8">
@@ -22939,8 +23167,8 @@
         <f>SUM(C3:E30)</f>
         <v>38.5</v>
       </c>
-      <c r="P2" s="365"/>
-      <c r="Q2" s="365"/>
+      <c r="P2" s="371"/>
+      <c r="Q2" s="371"/>
     </row>
     <row r="3" spans="1:17" ht="16.5">
       <c r="A3" s="9">
@@ -23337,7 +23565,7 @@
         <v>218</v>
       </c>
       <c r="L14" s="239" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M14" s="239">
         <v>2.75</v>
@@ -23641,7 +23869,7 @@
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
       <c r="J23" s="242" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>227</v>
@@ -23715,7 +23943,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K25" s="8"/>
       <c r="L25" s="21"/>
@@ -23832,10 +24060,10 @@
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="242" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L30" s="8"/>
     </row>
@@ -24043,10 +24271,10 @@
         <f>SUM(B3:B30)</f>
         <v>44.5</v>
       </c>
-      <c r="P1" s="365" t="s">
+      <c r="P1" s="371" t="s">
         <v>197</v>
       </c>
-      <c r="Q1" s="365"/>
+      <c r="Q1" s="371"/>
     </row>
     <row r="2" spans="1:17" ht="16.5">
       <c r="B2" s="251">
@@ -24097,8 +24325,8 @@
         <f>SUM(C3:E30)</f>
         <v>36.75</v>
       </c>
-      <c r="P2" s="365"/>
-      <c r="Q2" s="365"/>
+      <c r="P2" s="371"/>
+      <c r="Q2" s="371"/>
     </row>
     <row r="3" spans="1:17" ht="16.5">
       <c r="A3" s="9">
@@ -24206,7 +24434,7 @@
         <v>30</v>
       </c>
       <c r="J5" s="251" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K5" s="246"/>
       <c r="L5" s="257" t="s">
@@ -24247,13 +24475,13 @@
         <v>17</v>
       </c>
       <c r="J6" s="251" t="s">
+        <v>243</v>
+      </c>
+      <c r="K6" s="246" t="s">
         <v>244</v>
       </c>
-      <c r="K6" s="246" t="s">
-        <v>245</v>
-      </c>
       <c r="L6" s="283" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="M6" s="266"/>
       <c r="N6" s="17" t="s">
@@ -24282,10 +24510,10 @@
         <v>15</v>
       </c>
       <c r="J7" s="246" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K7" s="282" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L7" s="257" t="s">
         <v>209</v>
@@ -24316,10 +24544,10 @@
       </c>
       <c r="H8" s="251"/>
       <c r="K8" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L8" s="257" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M8" s="280">
         <v>2.5</v>
@@ -24354,13 +24582,13 @@
         <v>24</v>
       </c>
       <c r="J9" s="251" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K9" s="273" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L9" s="257" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M9" s="265">
         <v>5</v>
@@ -24396,10 +24624,10 @@
       <c r="I10" s="270"/>
       <c r="J10" s="251"/>
       <c r="K10" s="274" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L10" s="257" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M10" s="266">
         <v>16.5</v>
@@ -24430,13 +24658,13 @@
         <v>11</v>
       </c>
       <c r="J11" s="251" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K11" s="275" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L11" s="257" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M11" s="266">
         <v>7.75</v>
@@ -24469,13 +24697,13 @@
       <c r="H12" s="222"/>
       <c r="I12" s="222"/>
       <c r="J12" s="222" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K12" s="276" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L12" s="257" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M12" s="266">
         <v>6</v>
@@ -24507,10 +24735,10 @@
       <c r="I13" s="251"/>
       <c r="J13" s="251"/>
       <c r="K13" s="275" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L13" s="257" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M13" s="266">
         <v>3</v>
@@ -24541,10 +24769,10 @@
       <c r="I14" s="251"/>
       <c r="J14" s="251"/>
       <c r="K14" s="277" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L14" s="257" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M14" s="267">
         <v>17.5</v>
@@ -24574,7 +24802,7 @@
       <c r="I15" s="251"/>
       <c r="J15" s="251"/>
       <c r="K15" s="277" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L15" s="257" t="s">
         <v>238</v>
@@ -24605,10 +24833,10 @@
       <c r="I16" s="251"/>
       <c r="J16" s="251"/>
       <c r="K16" s="277" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L16" s="257" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M16" s="266">
         <v>2</v>
@@ -24640,10 +24868,10 @@
       <c r="I17" s="251"/>
       <c r="J17" s="251"/>
       <c r="K17" s="277" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L17" s="257" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M17" s="266">
         <v>5</v>
@@ -24669,10 +24897,10 @@
       <c r="I18" s="251"/>
       <c r="J18" s="251"/>
       <c r="K18" s="277" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L18" s="257" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M18" s="266">
         <v>12</v>
@@ -24699,7 +24927,7 @@
       <c r="I19" s="251"/>
       <c r="J19" s="251"/>
       <c r="K19" s="278" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L19" s="257" t="s">
         <v>188</v>
@@ -24733,13 +24961,13 @@
       </c>
       <c r="I20" s="251"/>
       <c r="J20" s="251" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K20" s="272" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L20" s="257" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M20" s="281">
         <v>6</v>
@@ -24773,13 +25001,13 @@
       <c r="H21" s="251"/>
       <c r="I21" s="251"/>
       <c r="J21" s="251" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K21" s="286" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L21" s="257" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M21" s="268">
         <v>3.5</v>
@@ -24815,11 +25043,11 @@
       </c>
       <c r="I22" s="251"/>
       <c r="J22" s="251" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K22" s="249"/>
       <c r="L22" s="244" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M22" s="287">
         <v>5</v>
@@ -24853,13 +25081,13 @@
       <c r="H23" s="251"/>
       <c r="I23" s="251"/>
       <c r="J23" s="251" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K23" s="250" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L23" s="239" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M23" s="11">
         <v>0.5</v>
@@ -24894,7 +25122,7 @@
       <c r="I24" s="251"/>
       <c r="J24" s="251"/>
       <c r="K24" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L24" s="257" t="s">
         <v>193</v>
@@ -24926,11 +25154,11 @@
       <c r="H25" s="251"/>
       <c r="I25" s="222"/>
       <c r="J25" s="222" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K25" s="246"/>
       <c r="L25" s="21" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M25" s="11">
         <v>0.75</v>
@@ -24961,11 +25189,11 @@
       <c r="H26" s="251"/>
       <c r="I26" s="251"/>
       <c r="J26" s="251" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K26" s="246"/>
       <c r="L26" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M26" s="11">
         <v>3.5</v>
@@ -24992,13 +25220,13 @@
       <c r="H27" s="251"/>
       <c r="I27" s="251"/>
       <c r="J27" s="251" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K27" s="246" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L27" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M27" s="11">
         <v>2.5</v>
@@ -25034,10 +25262,10 @@
         <v>20</v>
       </c>
       <c r="J28" s="251" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K28" s="246" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L28" s="246"/>
     </row>
@@ -25059,7 +25287,7 @@
       <c r="I29" s="251"/>
       <c r="J29" s="251"/>
       <c r="K29" s="246" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L29" s="246"/>
     </row>
@@ -25087,14 +25315,14 @@
       <c r="I30" s="251"/>
       <c r="J30" s="251"/>
       <c r="K30" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="L30" s="366" t="s">
+        <v>309</v>
+      </c>
+      <c r="L30" s="372" t="s">
         <v>237</v>
       </c>
-      <c r="M30" s="366"/>
-      <c r="N30" s="366"/>
-      <c r="O30" s="366"/>
+      <c r="M30" s="372"/>
+      <c r="N30" s="372"/>
+      <c r="O30" s="372"/>
     </row>
     <row r="31" spans="1:16" s="247" customFormat="1" ht="16.5">
       <c r="A31" s="9">
@@ -25114,7 +25342,7 @@
       <c r="I31" s="251"/>
       <c r="J31" s="251"/>
       <c r="K31" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L31" s="248"/>
       <c r="M31" s="248"/>
@@ -25137,7 +25365,7 @@
       <c r="I32" s="251"/>
       <c r="J32" s="251"/>
       <c r="K32" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L32" s="248"/>
       <c r="M32" s="248"/>
@@ -25164,12 +25392,12 @@
       <c r="I33" s="246"/>
       <c r="J33" s="246"/>
       <c r="K33" s="244" t="s">
-        <v>301</v>
-      </c>
-      <c r="L33" s="366"/>
-      <c r="M33" s="366"/>
-      <c r="N33" s="366"/>
-      <c r="O33" s="366"/>
+        <v>300</v>
+      </c>
+      <c r="L33" s="372"/>
+      <c r="M33" s="372"/>
+      <c r="N33" s="372"/>
+      <c r="O33" s="372"/>
     </row>
     <row r="34" spans="1:15" ht="16.5">
       <c r="A34" s="246" t="s">
@@ -25189,10 +25417,10 @@
       <c r="K34" s="246" t="s">
         <v>193</v>
       </c>
-      <c r="L34" s="366"/>
-      <c r="M34" s="366"/>
-      <c r="N34" s="366"/>
-      <c r="O34" s="366"/>
+      <c r="L34" s="372"/>
+      <c r="M34" s="372"/>
+      <c r="N34" s="372"/>
+      <c r="O34" s="372"/>
     </row>
     <row r="35" spans="1:15" ht="16.5">
       <c r="A35" s="246"/>
@@ -25348,7 +25576,7 @@
         <v>195</v>
       </c>
       <c r="K1" s="291" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>2</v>
@@ -25358,38 +25586,38 @@
         <v>14</v>
       </c>
       <c r="O1" s="288">
-        <f>SUM(B3:B30)</f>
-        <v>59.75</v>
-      </c>
-      <c r="P1" s="365" t="s">
+        <f>SUM(B3:B32)</f>
+        <v>66.75</v>
+      </c>
+      <c r="P1" s="371" t="s">
         <v>197</v>
       </c>
-      <c r="Q1" s="365"/>
+      <c r="Q1" s="371"/>
     </row>
     <row r="2" spans="1:17" ht="16.5">
       <c r="B2" s="251">
         <f>SUM(B3:B33)</f>
-        <v>64.25</v>
+        <v>66.75</v>
       </c>
       <c r="C2" s="251">
         <f t="shared" ref="C2" si="0">SUM(C3:C33)</f>
-        <v>20.100000000000001</v>
+        <v>20.6</v>
       </c>
       <c r="D2" s="251">
         <f>SUM(D3:D33)</f>
-        <v>10.45</v>
+        <v>12.7</v>
       </c>
       <c r="E2" s="251">
         <f t="shared" ref="E2:H2" si="1">SUM(E3:E33)</f>
-        <v>13.05</v>
+        <v>14.05</v>
       </c>
       <c r="F2" s="251">
         <f>SUM(F3:F33)</f>
-        <v>27.5</v>
+        <v>30.75</v>
       </c>
       <c r="G2" s="251">
         <f t="shared" si="1"/>
-        <v>35.5</v>
+        <v>48.5</v>
       </c>
       <c r="H2" s="251">
         <f t="shared" si="1"/>
@@ -25397,12 +25625,12 @@
       </c>
       <c r="I2" s="251">
         <f>SUM(I3:I30)/60</f>
-        <v>5.9833333333333334</v>
+        <v>6.1</v>
       </c>
       <c r="J2" s="251"/>
       <c r="K2" s="240">
         <f>SUM(E2:G2)</f>
-        <v>76.05</v>
+        <v>93.3</v>
       </c>
       <c r="L2" s="290"/>
       <c r="M2" s="288" t="s">
@@ -25413,10 +25641,10 @@
       </c>
       <c r="O2" s="256">
         <f>SUM(C3:E30)</f>
-        <v>40.299999999999997</v>
-      </c>
-      <c r="P2" s="365"/>
-      <c r="Q2" s="365"/>
+        <v>44.05</v>
+      </c>
+      <c r="P2" s="371"/>
+      <c r="Q2" s="371"/>
     </row>
     <row r="3" spans="1:17" ht="16.5">
       <c r="A3" s="9">
@@ -25437,7 +25665,7 @@
         <v>30</v>
       </c>
       <c r="J3" s="251" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K3" s="290"/>
       <c r="L3" s="20" t="s">
@@ -25445,18 +25673,18 @@
       </c>
       <c r="M3" s="264">
         <f>SUM(M4:M28)</f>
-        <v>76.05</v>
+        <v>93.3</v>
       </c>
       <c r="N3" s="255" t="s">
         <v>16</v>
       </c>
       <c r="O3" s="255">
         <f>SUM(F3:H30)</f>
-        <v>46.5</v>
+        <v>62.75</v>
       </c>
       <c r="P3" s="288">
         <f>SUM(P4:P32)</f>
-        <v>15.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16.5">
@@ -25491,16 +25719,22 @@
       <c r="C5" s="253"/>
       <c r="D5" s="253"/>
       <c r="E5" s="253"/>
-      <c r="F5" s="253"/>
-      <c r="G5" s="251"/>
+      <c r="F5" s="253">
+        <v>2.5</v>
+      </c>
+      <c r="G5" s="251">
+        <v>7.5</v>
+      </c>
       <c r="H5" s="251"/>
       <c r="I5" s="251"/>
       <c r="J5" s="251"/>
       <c r="K5" s="290"/>
       <c r="L5" s="293" t="s">
-        <v>235</v>
-      </c>
-      <c r="M5" s="266"/>
+        <v>466</v>
+      </c>
+      <c r="M5" s="266">
+        <v>2.5</v>
+      </c>
       <c r="N5" s="288" t="s">
         <v>239</v>
       </c>
@@ -25529,11 +25763,11 @@
         <v>18</v>
       </c>
       <c r="J6" s="251" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K6" s="290"/>
       <c r="L6" s="292" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="M6" s="266"/>
       <c r="N6" s="17" t="s">
@@ -25564,13 +25798,13 @@
         <v>30</v>
       </c>
       <c r="J7" s="290" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K7" s="290" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L7" s="293" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M7" s="279">
         <v>3.3</v>
@@ -25603,13 +25837,13 @@
         <v>7</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L8" s="293" t="s">
-        <v>242</v>
+        <v>469</v>
       </c>
       <c r="M8" s="280">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="N8" s="259" t="s">
         <v>168</v>
@@ -25624,14 +25858,22 @@
       </c>
       <c r="B9" s="257"/>
       <c r="C9" s="253"/>
-      <c r="D9" s="253"/>
+      <c r="D9" s="253">
+        <v>0.25</v>
+      </c>
       <c r="E9" s="253"/>
-      <c r="F9" s="253"/>
-      <c r="G9" s="251"/>
+      <c r="F9" s="253">
+        <v>0.25</v>
+      </c>
+      <c r="G9" s="251">
+        <v>3</v>
+      </c>
       <c r="H9" s="251"/>
       <c r="I9" s="251"/>
       <c r="J9" s="251"/>
-      <c r="K9" s="273"/>
+      <c r="K9" s="273" t="s">
+        <v>470</v>
+      </c>
       <c r="L9" s="293" t="s">
         <v>151</v>
       </c>
@@ -25654,7 +25896,9 @@
       <c r="D10" s="253">
         <v>1</v>
       </c>
-      <c r="E10" s="253"/>
+      <c r="E10" s="253">
+        <v>1</v>
+      </c>
       <c r="F10" s="253"/>
       <c r="G10" s="251">
         <v>5</v>
@@ -25663,10 +25907,10 @@
       <c r="I10" s="270"/>
       <c r="J10" s="251"/>
       <c r="K10" s="274" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L10" s="293" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M10" s="266">
         <v>0.75</v>
@@ -25694,10 +25938,10 @@
       <c r="I11" s="269"/>
       <c r="J11" s="251"/>
       <c r="K11" s="275" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L11" s="293" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M11" s="266">
         <v>1.5</v>
@@ -25725,10 +25969,10 @@
       <c r="I12" s="222"/>
       <c r="J12" s="222"/>
       <c r="K12" s="276" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L12" s="293" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M12" s="266">
         <v>4.5</v>
@@ -25759,16 +26003,16 @@
       <c r="H13" s="251"/>
       <c r="I13" s="251"/>
       <c r="J13" s="251" t="s">
+        <v>318</v>
+      </c>
+      <c r="K13" s="275" t="s">
         <v>319</v>
       </c>
-      <c r="K13" s="275" t="s">
-        <v>320</v>
-      </c>
       <c r="L13" s="293" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M13" s="266">
-        <v>4.5</v>
+        <v>6.75</v>
       </c>
       <c r="N13" s="259" t="s">
         <v>177</v>
@@ -25807,16 +26051,16 @@
         <v>30</v>
       </c>
       <c r="J14" s="251" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K14" s="277" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L14" s="293" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="M14" s="267">
-        <v>8.75</v>
+        <v>9.75</v>
       </c>
       <c r="N14" s="39" t="s">
         <v>174</v>
@@ -25848,18 +26092,23 @@
       <c r="H15" s="251"/>
       <c r="I15" s="251"/>
       <c r="J15" s="251" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K15" s="277"/>
       <c r="L15" s="293" t="s">
-        <v>238</v>
-      </c>
-      <c r="M15" s="268"/>
+        <v>334</v>
+      </c>
+      <c r="M15" s="268">
+        <v>7</v>
+      </c>
       <c r="N15" s="261" t="s">
         <v>69</v>
       </c>
       <c r="O15" s="36" t="s">
         <v>3</v>
+      </c>
+      <c r="P15" s="288">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="16.5">
@@ -25885,13 +26134,13 @@
         <v>27</v>
       </c>
       <c r="J16" s="251" t="s">
+        <v>323</v>
+      </c>
+      <c r="K16" s="277" t="s">
         <v>324</v>
       </c>
-      <c r="K16" s="277" t="s">
-        <v>325</v>
-      </c>
       <c r="L16" s="293" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="M16" s="266">
         <v>2.75</v>
@@ -25907,21 +26156,27 @@
       <c r="A17" s="9">
         <v>46127</v>
       </c>
-      <c r="B17" s="257"/>
-      <c r="C17" s="253"/>
+      <c r="B17" s="257">
+        <v>0.5</v>
+      </c>
+      <c r="C17" s="253">
+        <v>0.5</v>
+      </c>
       <c r="D17" s="253"/>
       <c r="E17" s="253"/>
       <c r="F17" s="253"/>
-      <c r="G17" s="251"/>
+      <c r="G17" s="251">
+        <v>2.5</v>
+      </c>
       <c r="H17" s="251"/>
       <c r="I17" s="251"/>
       <c r="J17" s="251"/>
       <c r="K17" s="277"/>
       <c r="L17" s="293" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M17" s="266">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="N17" s="261" t="s">
         <v>179</v>
@@ -25936,16 +26191,20 @@
       </c>
       <c r="B18" s="257"/>
       <c r="C18" s="253"/>
-      <c r="D18" s="253"/>
+      <c r="D18" s="253">
+        <v>2</v>
+      </c>
       <c r="E18" s="253"/>
       <c r="F18" s="253"/>
       <c r="G18" s="251"/>
       <c r="H18" s="251"/>
       <c r="I18" s="251"/>
       <c r="J18" s="251"/>
-      <c r="K18" s="277"/>
+      <c r="K18" s="277" t="s">
+        <v>467</v>
+      </c>
       <c r="L18" s="293" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M18" s="266">
         <v>5.5</v>
@@ -25958,21 +26217,29 @@
       <c r="A19" s="9">
         <v>46129</v>
       </c>
-      <c r="B19" s="257"/>
+      <c r="B19" s="257">
+        <v>2</v>
+      </c>
       <c r="C19" s="253"/>
       <c r="D19" s="253"/>
       <c r="E19" s="253"/>
-      <c r="F19" s="253"/>
+      <c r="F19" s="253">
+        <v>0.5</v>
+      </c>
       <c r="G19" s="251"/>
       <c r="H19" s="251"/>
-      <c r="I19" s="251"/>
-      <c r="J19" s="251"/>
+      <c r="I19" s="251">
+        <v>7</v>
+      </c>
+      <c r="J19" s="251" t="s">
+        <v>468</v>
+      </c>
       <c r="K19" s="278"/>
       <c r="L19" s="293" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M19" s="279">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="N19" s="262"/>
       <c r="P19" s="289"/>
@@ -26000,13 +26267,13 @@
         <v>10</v>
       </c>
       <c r="J20" s="251" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K20" s="272" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L20" s="293" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M20" s="281">
         <v>4.75</v>
@@ -26046,13 +26313,13 @@
         <v>8</v>
       </c>
       <c r="J21" s="251" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K21" s="286" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L21" s="293" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M21" s="268">
         <v>1</v>
@@ -26090,13 +26357,13 @@
         <v>31</v>
       </c>
       <c r="J22" s="251" t="s">
+        <v>335</v>
+      </c>
+      <c r="K22" s="249" t="s">
         <v>336</v>
       </c>
-      <c r="K22" s="249" t="s">
-        <v>337</v>
-      </c>
       <c r="L22" s="294" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M22" s="287">
         <v>3</v>
@@ -26129,7 +26396,7 @@
       <c r="I23" s="251"/>
       <c r="J23" s="251"/>
       <c r="K23" s="250" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L23" s="293"/>
       <c r="M23" s="11"/>
@@ -26162,7 +26429,7 @@
         <v>18</v>
       </c>
       <c r="J24" s="251" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="293" t="s">
@@ -26196,7 +26463,7 @@
       <c r="I25" s="222"/>
       <c r="J25" s="222"/>
       <c r="K25" s="290" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L25" s="21"/>
       <c r="M25" s="11"/>
@@ -26232,10 +26499,10 @@
         <v>40</v>
       </c>
       <c r="J26" s="251" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K26" s="290" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L26" s="10"/>
       <c r="M26" s="11"/>
@@ -26265,7 +26532,7 @@
       <c r="H27" s="251"/>
       <c r="I27" s="251"/>
       <c r="K27" s="290" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L27" s="18"/>
       <c r="M27" s="11"/>
@@ -26306,10 +26573,10 @@
         <v>80</v>
       </c>
       <c r="J28" s="251" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K28" s="290" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L28" s="290"/>
     </row>
@@ -26333,10 +26600,10 @@
       </c>
       <c r="I29" s="251"/>
       <c r="J29" s="251" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L29" s="290"/>
     </row>
@@ -26365,15 +26632,15 @@
         <v>30</v>
       </c>
       <c r="J30" s="251" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K30" s="290" t="s">
-        <v>349</v>
-      </c>
-      <c r="L30" s="366"/>
-      <c r="M30" s="366"/>
-      <c r="N30" s="366"/>
-      <c r="O30" s="366"/>
+        <v>348</v>
+      </c>
+      <c r="L30" s="372"/>
+      <c r="M30" s="372"/>
+      <c r="N30" s="372"/>
+      <c r="O30" s="372"/>
     </row>
     <row r="31" spans="1:16" ht="16.5">
       <c r="A31" s="9">
@@ -26398,10 +26665,10 @@
       <c r="H31" s="251"/>
       <c r="I31" s="251"/>
       <c r="J31" s="251" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L31" s="290"/>
       <c r="M31" s="290"/>
@@ -26429,10 +26696,10 @@
         <v>13</v>
       </c>
       <c r="J32" s="251" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L32" s="290"/>
       <c r="M32" s="290"/>
@@ -26455,10 +26722,10 @@
       <c r="H33" s="290"/>
       <c r="I33" s="290"/>
       <c r="J33" s="290"/>
-      <c r="L33" s="366"/>
-      <c r="M33" s="366"/>
-      <c r="N33" s="366"/>
-      <c r="O33" s="366"/>
+      <c r="L33" s="372"/>
+      <c r="M33" s="372"/>
+      <c r="N33" s="372"/>
+      <c r="O33" s="372"/>
     </row>
     <row r="34" spans="1:15" ht="16.5">
       <c r="A34" s="290" t="s">
@@ -26476,10 +26743,10 @@
       <c r="I34" s="290"/>
       <c r="J34" s="290"/>
       <c r="K34" s="290"/>
-      <c r="L34" s="366"/>
-      <c r="M34" s="366"/>
-      <c r="N34" s="366"/>
-      <c r="O34" s="366"/>
+      <c r="L34" s="372"/>
+      <c r="M34" s="372"/>
+      <c r="N34" s="372"/>
+      <c r="O34" s="372"/>
     </row>
     <row r="35" spans="1:15" ht="16.5">
       <c r="A35" s="290"/>
@@ -26585,22 +26852,22 @@
   <dimension ref="A1:Q60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="307" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="307" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="307" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="307" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="307" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" style="307" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="307"/>
-    <col min="8" max="8" width="6.5703125" style="307" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" style="307" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" style="307" customWidth="1"/>
-    <col min="11" max="11" width="41.7109375" style="307" customWidth="1"/>
-    <col min="12" max="12" width="61.28515625" style="307" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" style="307" customWidth="1"/>
-    <col min="14" max="14" width="19.85546875" style="307" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="307" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="307"/>
+    <col min="1" max="1" width="10.85546875" style="306" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="306" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="306" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="306" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" style="306" customWidth="1"/>
+    <col min="6" max="6" width="8.28515625" style="306" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="306"/>
+    <col min="8" max="8" width="6.5703125" style="306" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" style="306" customWidth="1"/>
+    <col min="10" max="10" width="23.7109375" style="306" customWidth="1"/>
+    <col min="11" max="11" width="41.7109375" style="306" customWidth="1"/>
+    <col min="12" max="12" width="61.28515625" style="306" customWidth="1"/>
+    <col min="13" max="13" width="9.28515625" style="306" customWidth="1"/>
+    <col min="14" max="14" width="19.85546875" style="306" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="306" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="306"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="53.25" customHeight="1">
@@ -26634,8 +26901,8 @@
       <c r="J1" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="K1" s="303" t="s">
-        <v>415</v>
+      <c r="K1" s="302" t="s">
+        <v>413</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>2</v>
@@ -26648,10 +26915,10 @@
         <f>SUM(B3:B33)</f>
         <v>58.5</v>
       </c>
-      <c r="P1" s="365" t="s">
+      <c r="P1" s="371" t="s">
         <v>197</v>
       </c>
-      <c r="Q1" s="365"/>
+      <c r="Q1" s="371"/>
     </row>
     <row r="2" spans="1:17" ht="16.5">
       <c r="B2" s="251">
@@ -26668,15 +26935,15 @@
       </c>
       <c r="E2" s="251">
         <f t="shared" ref="E2:H2" si="1">SUM(E3:E33)</f>
-        <v>16.55</v>
+        <v>17.05</v>
       </c>
       <c r="F2" s="251">
         <f>SUM(F3:F33)</f>
-        <v>32</v>
+        <v>34.5</v>
       </c>
       <c r="G2" s="251">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H2" s="251">
         <f t="shared" si="1"/>
@@ -26689,10 +26956,10 @@
       <c r="J2" s="251"/>
       <c r="K2" s="240">
         <f>SUM(E2:G2)</f>
-        <v>99.55</v>
-      </c>
-      <c r="L2" s="308"/>
-      <c r="M2" s="307" t="s">
+        <v>105.55</v>
+      </c>
+      <c r="L2" s="307"/>
+      <c r="M2" s="306" t="s">
         <v>13</v>
       </c>
       <c r="N2" s="256" t="s">
@@ -26700,16 +26967,16 @@
       </c>
       <c r="O2" s="256">
         <f>SUM(C3:E30)</f>
-        <v>46.05</v>
-      </c>
-      <c r="P2" s="365"/>
-      <c r="Q2" s="365"/>
+        <v>46.55</v>
+      </c>
+      <c r="P2" s="371"/>
+      <c r="Q2" s="371"/>
     </row>
     <row r="3" spans="1:17" ht="16.5">
       <c r="A3" s="9">
         <v>46143</v>
       </c>
-      <c r="B3" s="306">
+      <c r="B3" s="305">
         <v>4</v>
       </c>
       <c r="C3" s="252">
@@ -26732,26 +26999,26 @@
         <v>26</v>
       </c>
       <c r="J3" s="251" t="s">
-        <v>367</v>
-      </c>
-      <c r="K3" s="308" t="s">
-        <v>368</v>
+        <v>365</v>
+      </c>
+      <c r="K3" s="307" t="s">
+        <v>366</v>
       </c>
       <c r="L3" s="20" t="s">
         <v>25</v>
       </c>
       <c r="M3" s="264">
         <f>SUM(M4:M28)</f>
-        <v>105.3</v>
+        <v>111.3</v>
       </c>
       <c r="N3" s="255" t="s">
         <v>16</v>
       </c>
       <c r="O3" s="255">
         <f>SUM(F3:H30)</f>
-        <v>77.25</v>
-      </c>
-      <c r="P3" s="307">
+        <v>82.75</v>
+      </c>
+      <c r="P3" s="306">
         <f>SUM(P4:P32)</f>
         <v>20</v>
       </c>
@@ -26779,18 +27046,18 @@
       <c r="H4" s="251"/>
       <c r="I4" s="251"/>
       <c r="J4" s="251" t="s">
-        <v>413</v>
-      </c>
-      <c r="K4" s="308" t="s">
-        <v>412</v>
+        <v>411</v>
+      </c>
+      <c r="K4" s="307" t="s">
+        <v>410</v>
       </c>
       <c r="L4" s="299" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M4" s="265">
         <v>12</v>
       </c>
-      <c r="P4" s="307">
+      <c r="P4" s="306">
         <v>1.5</v>
       </c>
     </row>
@@ -26823,21 +27090,21 @@
         <v>51</v>
       </c>
       <c r="J5" s="251" t="s">
-        <v>371</v>
-      </c>
-      <c r="K5" s="308" t="s">
-        <v>370</v>
+        <v>369</v>
+      </c>
+      <c r="K5" s="307" t="s">
+        <v>368</v>
       </c>
       <c r="L5" s="299" t="s">
-        <v>423</v>
+        <v>465</v>
       </c>
       <c r="M5" s="266">
-        <v>4.8</v>
-      </c>
-      <c r="N5" s="307" t="s">
+        <v>5.8</v>
+      </c>
+      <c r="N5" s="306" t="s">
         <v>239</v>
       </c>
-      <c r="P5" s="307">
+      <c r="P5" s="306">
         <v>1</v>
       </c>
     </row>
@@ -26852,26 +27119,26 @@
         <v>0.5</v>
       </c>
       <c r="D6" s="253"/>
-      <c r="E6" s="307">
+      <c r="E6" s="306">
         <v>1.5</v>
       </c>
-      <c r="F6" s="307">
+      <c r="F6" s="306">
         <v>0.25</v>
       </c>
-      <c r="G6" s="307">
+      <c r="G6" s="306">
         <v>0.5</v>
       </c>
-      <c r="I6" s="307">
+      <c r="I6" s="306">
         <v>3</v>
       </c>
       <c r="J6" s="251" t="s">
+        <v>370</v>
+      </c>
+      <c r="K6" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="K6" s="13" t="s">
-        <v>374</v>
-      </c>
       <c r="L6" s="299" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="M6" s="266"/>
       <c r="N6" s="17" t="s">
@@ -26890,14 +27157,18 @@
       <c r="D7" s="253">
         <v>0.5</v>
       </c>
-      <c r="G7" s="307">
+      <c r="G7" s="306">
         <v>3</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="L7" s="299"/>
-      <c r="M7" s="279"/>
+        <v>374</v>
+      </c>
+      <c r="L7" s="299" t="s">
+        <v>464</v>
+      </c>
+      <c r="M7" s="279">
+        <v>1.5</v>
+      </c>
       <c r="N7" s="258" t="s">
         <v>165</v>
       </c>
@@ -26912,14 +27183,14 @@
       <c r="B8" s="299"/>
       <c r="C8" s="253"/>
       <c r="D8" s="253"/>
-      <c r="G8" s="307">
+      <c r="G8" s="306">
         <v>4</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="L8" s="299" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="M8" s="280">
         <v>0.5</v>
@@ -26938,11 +27209,11 @@
       <c r="B9" s="299"/>
       <c r="C9" s="253"/>
       <c r="D9" s="253"/>
-      <c r="G9" s="307">
+      <c r="G9" s="306">
         <v>4</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L9" s="299" t="s">
         <v>151</v>
@@ -26950,10 +27221,10 @@
       <c r="M9" s="265">
         <v>0.5</v>
       </c>
-      <c r="N9" s="307" t="s">
+      <c r="N9" s="306" t="s">
         <v>169</v>
       </c>
-      <c r="O9" s="307" t="s">
+      <c r="O9" s="306" t="s">
         <v>171</v>
       </c>
     </row>
@@ -26964,14 +27235,14 @@
       <c r="B10" s="299"/>
       <c r="C10" s="253"/>
       <c r="D10" s="253"/>
-      <c r="H10" s="307">
+      <c r="H10" s="306">
         <v>3</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L10" s="299" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="M10" s="266">
         <v>1</v>
@@ -26990,14 +27261,14 @@
       <c r="B11" s="299"/>
       <c r="C11" s="253"/>
       <c r="D11" s="253"/>
-      <c r="G11" s="307">
+      <c r="G11" s="306">
         <v>10</v>
       </c>
-      <c r="K11" s="307" t="s">
-        <v>375</v>
+      <c r="K11" s="306" t="s">
+        <v>373</v>
       </c>
       <c r="L11" s="299" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="M11" s="266">
         <v>8.75</v>
@@ -27022,22 +27293,22 @@
       <c r="D12" s="253">
         <v>2.25</v>
       </c>
-      <c r="I12" s="307">
+      <c r="I12" s="306">
         <v>12</v>
       </c>
-      <c r="J12" s="307" t="s">
-        <v>380</v>
+      <c r="J12" s="306" t="s">
+        <v>378</v>
       </c>
       <c r="L12" s="299" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="M12" s="266">
         <v>11</v>
       </c>
-      <c r="N12" s="307" t="s">
+      <c r="N12" s="306" t="s">
         <v>173</v>
       </c>
-      <c r="O12" s="307" t="s">
+      <c r="O12" s="306" t="s">
         <v>80</v>
       </c>
     </row>
@@ -27048,17 +27319,17 @@
       <c r="B13" s="299"/>
       <c r="C13" s="253"/>
       <c r="D13" s="253"/>
-      <c r="H13" s="307">
+      <c r="H13" s="306">
         <v>3</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="L13" s="299" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="M13" s="266">
-        <v>9.75</v>
+        <v>10.75</v>
       </c>
       <c r="N13" s="259" t="s">
         <v>177</v>
@@ -27066,7 +27337,7 @@
       <c r="O13" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="P13" s="307">
+      <c r="P13" s="306">
         <v>6</v>
       </c>
     </row>
@@ -27078,20 +27349,20 @@
         <v>0</v>
       </c>
       <c r="C14" s="253"/>
-      <c r="E14" s="307">
+      <c r="E14" s="306">
         <v>3.5</v>
       </c>
-      <c r="F14" s="307">
+      <c r="F14" s="306">
         <v>0.75</v>
       </c>
-      <c r="K14" s="307" t="s">
-        <v>382</v>
+      <c r="K14" s="306" t="s">
+        <v>380</v>
       </c>
       <c r="L14" s="299" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M14" s="267">
-        <v>10.25</v>
+        <v>11.25</v>
       </c>
       <c r="N14" s="39" t="s">
         <v>174</v>
@@ -27109,14 +27380,14 @@
       </c>
       <c r="C15" s="253"/>
       <c r="D15" s="253"/>
-      <c r="G15" s="307">
+      <c r="G15" s="306">
         <v>2.5</v>
       </c>
-      <c r="H15" s="307">
+      <c r="H15" s="306">
         <v>1</v>
       </c>
-      <c r="K15" s="307" t="s">
-        <v>383</v>
+      <c r="K15" s="306" t="s">
+        <v>381</v>
       </c>
       <c r="L15" s="299" t="s">
         <v>238</v>
@@ -27136,23 +27407,23 @@
       <c r="B16" s="299"/>
       <c r="C16" s="253"/>
       <c r="D16" s="253"/>
-      <c r="F16" s="307">
+      <c r="F16" s="306">
         <v>0.5</v>
       </c>
-      <c r="G16" s="307">
+      <c r="G16" s="306">
         <v>2</v>
       </c>
-      <c r="H16" s="307">
+      <c r="H16" s="306">
         <v>1</v>
       </c>
-      <c r="K16" s="307" t="s">
-        <v>387</v>
+      <c r="K16" s="306" t="s">
+        <v>385</v>
       </c>
       <c r="L16" s="299" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="M16" s="266">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="N16" s="261" t="s">
         <v>178</v>
@@ -27170,11 +27441,11 @@
       <c r="D17" s="253">
         <v>1</v>
       </c>
-      <c r="G17" s="307">
+      <c r="G17" s="306">
         <v>4</v>
       </c>
-      <c r="K17" s="307" t="s">
-        <v>384</v>
+      <c r="K17" s="306" t="s">
+        <v>382</v>
       </c>
       <c r="L17" s="299" t="s">
         <v>132</v>
@@ -27200,28 +27471,28 @@
       <c r="D18" s="253">
         <v>4</v>
       </c>
-      <c r="G18" s="307">
+      <c r="G18" s="306">
         <v>1</v>
       </c>
-      <c r="H18" s="307">
+      <c r="H18" s="306">
         <v>1</v>
       </c>
-      <c r="I18" s="307">
+      <c r="I18" s="306">
         <v>10</v>
       </c>
-      <c r="J18" s="307" t="s">
-        <v>402</v>
-      </c>
-      <c r="K18" s="307" t="s">
-        <v>386</v>
+      <c r="J18" s="306" t="s">
+        <v>400</v>
+      </c>
+      <c r="K18" s="306" t="s">
+        <v>384</v>
       </c>
       <c r="L18" s="299" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="M18" s="266">
         <v>5.25</v>
       </c>
-      <c r="N18" s="307" t="s">
+      <c r="N18" s="306" t="s">
         <v>110</v>
       </c>
     </row>
@@ -27236,29 +27507,29 @@
       <c r="D19" s="253">
         <v>1</v>
       </c>
-      <c r="E19" s="307">
+      <c r="E19" s="306">
         <v>1.5</v>
       </c>
-      <c r="F19" s="307">
+      <c r="F19" s="306">
         <v>3.5</v>
       </c>
-      <c r="G19" s="307">
+      <c r="G19" s="306">
         <v>1</v>
       </c>
-      <c r="J19" s="307" t="s">
-        <v>400</v>
-      </c>
-      <c r="K19" s="307" t="s">
-        <v>401</v>
+      <c r="J19" s="306" t="s">
+        <v>398</v>
+      </c>
+      <c r="K19" s="306" t="s">
+        <v>399</v>
       </c>
       <c r="L19" s="299" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M19" s="279">
         <v>4</v>
       </c>
       <c r="N19" s="262"/>
-      <c r="P19" s="305"/>
+      <c r="P19" s="304"/>
     </row>
     <row r="20" spans="1:16" ht="16.5">
       <c r="A20" s="9">
@@ -27273,23 +27544,23 @@
       <c r="D20" s="253">
         <v>0.15</v>
       </c>
-      <c r="F20" s="307">
+      <c r="F20" s="306">
         <v>1</v>
       </c>
-      <c r="H20" s="307">
+      <c r="H20" s="306">
         <v>1</v>
       </c>
-      <c r="I20" s="307">
+      <c r="I20" s="306">
         <v>11</v>
       </c>
-      <c r="J20" s="307" t="s">
-        <v>390</v>
-      </c>
-      <c r="K20" s="307" t="s">
-        <v>389</v>
+      <c r="J20" s="306" t="s">
+        <v>388</v>
+      </c>
+      <c r="K20" s="306" t="s">
+        <v>387</v>
       </c>
       <c r="L20" s="299" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M20" s="281">
         <v>13.5</v>
@@ -27300,7 +27571,7 @@
       <c r="O20" s="164">
         <v>10</v>
       </c>
-      <c r="P20" s="305"/>
+      <c r="P20" s="304"/>
     </row>
     <row r="21" spans="1:16" ht="16.5">
       <c r="A21" s="9">
@@ -27311,23 +27582,23 @@
       </c>
       <c r="C21" s="253"/>
       <c r="D21" s="253"/>
-      <c r="E21" s="307">
+      <c r="E21" s="306">
         <v>2</v>
       </c>
-      <c r="G21" s="307">
+      <c r="G21" s="306">
         <v>0.75</v>
       </c>
-      <c r="I21" s="307">
+      <c r="I21" s="306">
         <v>10</v>
       </c>
-      <c r="J21" s="307" t="s">
-        <v>391</v>
-      </c>
-      <c r="K21" s="307" t="s">
-        <v>392</v>
+      <c r="J21" s="306" t="s">
+        <v>389</v>
+      </c>
+      <c r="K21" s="306" t="s">
+        <v>390</v>
       </c>
       <c r="L21" s="299" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M21" s="268">
         <v>4</v>
@@ -27353,23 +27624,23 @@
       <c r="D22" s="253">
         <v>1.6</v>
       </c>
-      <c r="F22" s="307">
+      <c r="F22" s="306">
         <v>0.25</v>
       </c>
-      <c r="G22" s="307">
+      <c r="G22" s="306">
         <v>1.25</v>
       </c>
-      <c r="I22" s="307">
+      <c r="I22" s="306">
         <v>16</v>
       </c>
-      <c r="J22" s="307" t="s">
-        <v>394</v>
-      </c>
-      <c r="K22" s="307" t="s">
-        <v>393</v>
+      <c r="J22" s="306" t="s">
+        <v>392</v>
+      </c>
+      <c r="K22" s="306" t="s">
+        <v>391</v>
       </c>
       <c r="L22" s="299" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="M22" s="287">
         <v>1.5</v>
@@ -27393,23 +27664,23 @@
       </c>
       <c r="C23" s="253"/>
       <c r="D23" s="253"/>
-      <c r="E23" s="307">
+      <c r="E23" s="306">
         <v>1.5</v>
       </c>
-      <c r="G23" s="307">
+      <c r="G23" s="306">
         <v>0.5</v>
       </c>
-      <c r="I23" s="307">
+      <c r="I23" s="306">
         <v>12</v>
       </c>
-      <c r="J23" s="307" t="s">
-        <v>395</v>
-      </c>
-      <c r="K23" s="301" t="s">
+      <c r="J23" s="306" t="s">
+        <v>393</v>
+      </c>
+      <c r="K23" s="300" t="s">
+        <v>394</v>
+      </c>
+      <c r="L23" s="293" t="s">
         <v>396</v>
-      </c>
-      <c r="L23" s="293" t="s">
-        <v>398</v>
       </c>
       <c r="M23" s="11">
         <v>1</v>
@@ -27449,10 +27720,10 @@
         <v>40</v>
       </c>
       <c r="J24" s="251" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="L24" s="293"/>
       <c r="M24" s="267">
@@ -27464,7 +27735,7 @@
       <c r="O24" s="165">
         <v>10</v>
       </c>
-      <c r="P24" s="307">
+      <c r="P24" s="306">
         <v>1.5</v>
       </c>
     </row>
@@ -27493,10 +27764,10 @@
         <v>20</v>
       </c>
       <c r="J25" s="222" t="s">
-        <v>408</v>
-      </c>
-      <c r="K25" s="308" t="s">
         <v>406</v>
+      </c>
+      <c r="K25" s="307" t="s">
+        <v>404</v>
       </c>
       <c r="L25" s="293" t="s">
         <v>193</v>
@@ -27536,10 +27807,10 @@
         <v>20</v>
       </c>
       <c r="J26" s="251" t="s">
-        <v>407</v>
-      </c>
-      <c r="K26" s="308" t="s">
-        <v>404</v>
+        <v>405</v>
+      </c>
+      <c r="K26" s="307" t="s">
+        <v>402</v>
       </c>
       <c r="L26" s="21"/>
       <c r="M26" s="11"/>
@@ -27561,20 +27832,20 @@
       </c>
       <c r="E27" s="253"/>
       <c r="F27" s="251">
-        <v>0.75</v>
+        <v>2.75</v>
       </c>
       <c r="G27" s="251">
         <v>0.5</v>
       </c>
       <c r="H27" s="251"/>
-      <c r="I27" s="307">
+      <c r="I27" s="306">
         <v>65</v>
       </c>
-      <c r="J27" s="307" t="s">
-        <v>410</v>
-      </c>
-      <c r="K27" s="308" t="s">
-        <v>409</v>
+      <c r="J27" s="306" t="s">
+        <v>408</v>
+      </c>
+      <c r="K27" s="307" t="s">
+        <v>407</v>
       </c>
       <c r="L27" s="10"/>
       <c r="M27" s="11"/>
@@ -27584,7 +27855,7 @@
       <c r="O27" s="167">
         <v>15</v>
       </c>
-      <c r="P27" s="307">
+      <c r="P27" s="306">
         <v>7</v>
       </c>
     </row>
@@ -27609,10 +27880,10 @@
         <v>10</v>
       </c>
       <c r="J28" s="251" t="s">
-        <v>414</v>
-      </c>
-      <c r="K28" s="308" t="s">
-        <v>420</v>
+        <v>412</v>
+      </c>
+      <c r="K28" s="307" t="s">
+        <v>418</v>
       </c>
       <c r="L28" s="18"/>
     </row>
@@ -27638,12 +27909,12 @@
         <v>30</v>
       </c>
       <c r="J29" s="251" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="L29" s="308"/>
+        <v>416</v>
+      </c>
+      <c r="L29" s="307"/>
     </row>
     <row r="30" spans="1:16" ht="16.5">
       <c r="A30" s="9">
@@ -27657,22 +27928,26 @@
       </c>
       <c r="D30" s="253"/>
       <c r="E30" s="253">
+        <v>1</v>
+      </c>
+      <c r="F30" s="251">
         <v>0.5</v>
       </c>
-      <c r="F30" s="251"/>
-      <c r="G30" s="251"/>
+      <c r="G30" s="251">
+        <v>3</v>
+      </c>
       <c r="H30" s="251"/>
       <c r="I30" s="251">
         <v>30</v>
       </c>
       <c r="J30" s="251" t="s">
-        <v>417</v>
-      </c>
-      <c r="K30" s="308"/>
-      <c r="L30" s="308"/>
-      <c r="M30" s="308"/>
-      <c r="N30" s="308"/>
-      <c r="O30" s="308"/>
+        <v>415</v>
+      </c>
+      <c r="K30" s="307"/>
+      <c r="L30" s="307"/>
+      <c r="M30" s="307"/>
+      <c r="N30" s="307"/>
+      <c r="O30" s="307"/>
     </row>
     <row r="31" spans="1:16" ht="16.5">
       <c r="A31" s="9">
@@ -27690,18 +27965,18 @@
       <c r="I31" s="251"/>
       <c r="J31" s="251"/>
       <c r="K31" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="L31" s="308"/>
-      <c r="M31" s="308"/>
-      <c r="N31" s="308"/>
-      <c r="O31" s="308"/>
+        <v>423</v>
+      </c>
+      <c r="L31" s="307"/>
+      <c r="M31" s="307"/>
+      <c r="N31" s="307"/>
+      <c r="O31" s="307"/>
     </row>
     <row r="32" spans="1:16" ht="33">
       <c r="A32" s="9">
         <v>46172</v>
       </c>
-      <c r="B32" s="306">
+      <c r="B32" s="305">
         <v>5.25</v>
       </c>
       <c r="C32" s="253">
@@ -27726,123 +28001,123 @@
         <v>16</v>
       </c>
       <c r="J32" s="251" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="L32" s="308"/>
-      <c r="M32" s="308"/>
-      <c r="N32" s="308"/>
-      <c r="O32" s="308"/>
+        <v>422</v>
+      </c>
+      <c r="L32" s="307"/>
+      <c r="M32" s="307"/>
+      <c r="N32" s="307"/>
+      <c r="O32" s="307"/>
     </row>
     <row r="33" spans="1:15" ht="16.5">
       <c r="A33" s="9">
         <v>46173</v>
       </c>
-      <c r="B33" s="306">
+      <c r="B33" s="305">
         <v>3.25</v>
       </c>
-      <c r="C33" s="308"/>
-      <c r="D33" s="308">
+      <c r="C33" s="307"/>
+      <c r="D33" s="307">
         <v>1</v>
       </c>
-      <c r="E33" s="308">
+      <c r="E33" s="307">
         <v>0.8</v>
       </c>
-      <c r="F33" s="308">
+      <c r="F33" s="307">
         <v>15</v>
       </c>
-      <c r="G33" s="308"/>
-      <c r="H33" s="308"/>
+      <c r="G33" s="307"/>
+      <c r="H33" s="307"/>
       <c r="I33" s="251">
         <v>27</v>
       </c>
-      <c r="J33" s="308" t="s">
-        <v>432</v>
-      </c>
-      <c r="L33" s="308"/>
-      <c r="M33" s="308"/>
-      <c r="N33" s="308"/>
-      <c r="O33" s="308"/>
+      <c r="J33" s="307" t="s">
+        <v>429</v>
+      </c>
+      <c r="L33" s="307"/>
+      <c r="M33" s="307"/>
+      <c r="N33" s="307"/>
+      <c r="O33" s="307"/>
     </row>
     <row r="34" spans="1:15" ht="16.5">
-      <c r="A34" s="308" t="s">
+      <c r="A34" s="307" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="308">
+      <c r="B34" s="307">
         <v>3</v>
       </c>
-      <c r="C34" s="308"/>
-      <c r="D34" s="308"/>
-      <c r="E34" s="308">
+      <c r="C34" s="307"/>
+      <c r="D34" s="307"/>
+      <c r="E34" s="307">
         <v>1</v>
       </c>
-      <c r="F34" s="308">
+      <c r="F34" s="307">
         <v>2</v>
       </c>
-      <c r="G34" s="308">
+      <c r="G34" s="307">
         <v>1.5</v>
       </c>
-      <c r="H34" s="308">
+      <c r="H34" s="307">
         <v>2.25</v>
       </c>
-      <c r="I34" s="308"/>
-      <c r="J34" s="308"/>
-      <c r="K34" s="308" t="s">
-        <v>428</v>
-      </c>
-      <c r="L34" s="308"/>
-      <c r="M34" s="308"/>
-      <c r="N34" s="308"/>
-      <c r="O34" s="308"/>
+      <c r="I34" s="307"/>
+      <c r="J34" s="307"/>
+      <c r="K34" s="307" t="s">
+        <v>425</v>
+      </c>
+      <c r="L34" s="307"/>
+      <c r="M34" s="307"/>
+      <c r="N34" s="307"/>
+      <c r="O34" s="307"/>
     </row>
     <row r="35" spans="1:15" ht="16.5">
-      <c r="A35" s="308"/>
-      <c r="B35" s="308"/>
-      <c r="C35" s="308"/>
-      <c r="D35" s="308"/>
-      <c r="E35" s="308"/>
-      <c r="F35" s="308"/>
-      <c r="G35" s="308"/>
-      <c r="H35" s="308"/>
-      <c r="I35" s="308"/>
-      <c r="J35" s="308"/>
-      <c r="K35" s="308"/>
-      <c r="L35" s="308"/>
+      <c r="A35" s="307"/>
+      <c r="B35" s="307"/>
+      <c r="C35" s="307"/>
+      <c r="D35" s="307"/>
+      <c r="E35" s="307"/>
+      <c r="F35" s="307"/>
+      <c r="G35" s="307"/>
+      <c r="H35" s="307"/>
+      <c r="I35" s="307"/>
+      <c r="J35" s="307"/>
+      <c r="K35" s="307"/>
+      <c r="L35" s="307"/>
     </row>
     <row r="36" spans="1:15" ht="16.5">
-      <c r="A36" s="308"/>
-      <c r="B36" s="308"/>
-      <c r="C36" s="308"/>
-      <c r="D36" s="308"/>
-      <c r="E36" s="308"/>
-      <c r="F36" s="308"/>
-      <c r="G36" s="308"/>
-      <c r="H36" s="308"/>
-      <c r="I36" s="308"/>
-      <c r="J36" s="308"/>
-      <c r="K36" s="308"/>
-      <c r="L36" s="308"/>
+      <c r="A36" s="307"/>
+      <c r="B36" s="307"/>
+      <c r="C36" s="307"/>
+      <c r="D36" s="307"/>
+      <c r="E36" s="307"/>
+      <c r="F36" s="307"/>
+      <c r="G36" s="307"/>
+      <c r="H36" s="307"/>
+      <c r="I36" s="307"/>
+      <c r="J36" s="307"/>
+      <c r="K36" s="307"/>
+      <c r="L36" s="307"/>
     </row>
     <row r="37" spans="1:15" ht="16.5">
-      <c r="L37" s="308"/>
+      <c r="L37" s="307"/>
     </row>
     <row r="53" spans="4:8">
-      <c r="D53" s="307" t="s">
+      <c r="D53" s="306" t="s">
         <v>20</v>
       </c>
-      <c r="H53" s="307">
+      <c r="H53" s="306">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="4:8">
-      <c r="H55" s="307">
+      <c r="H55" s="306">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="4:8">
-      <c r="H56" s="307">
+      <c r="H56" s="306">
         <v>2</v>
       </c>
     </row>
@@ -27937,8 +28212,8 @@
     <col min="6" max="6" width="8.28515625" style="296" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="296"/>
     <col min="8" max="8" width="6.5703125" style="296" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" style="296" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" style="296" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" style="322" customWidth="1"/>
+    <col min="10" max="10" width="23.7109375" style="222" customWidth="1"/>
     <col min="11" max="11" width="41.7109375" style="296" customWidth="1"/>
     <col min="12" max="12" width="61.28515625" style="296" customWidth="1"/>
     <col min="13" max="13" width="9.28515625" style="296" customWidth="1"/>
@@ -27948,92 +28223,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="53.25" customHeight="1">
-      <c r="A1" s="310" t="s">
+      <c r="A1" s="308" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="310" t="s">
+      <c r="B1" s="308" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="310" t="s">
+      <c r="C1" s="308" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="310" t="s">
+      <c r="D1" s="308" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="310" t="s">
+      <c r="E1" s="308" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="310" t="s">
+      <c r="F1" s="308" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="310" t="s">
+      <c r="G1" s="308" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="310" t="s">
+      <c r="H1" s="308" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="310" t="s">
+      <c r="I1" s="325" t="s">
         <v>113</v>
       </c>
-      <c r="J1" s="310" t="s">
+      <c r="J1" s="325" t="s">
         <v>195</v>
       </c>
-      <c r="K1" s="310" t="s">
-        <v>439</v>
+      <c r="K1" s="308" t="s">
+        <v>431</v>
       </c>
       <c r="L1" s="239" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="7"/>
-      <c r="N1" s="309" t="s">
+      <c r="N1" s="318" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="309">
+      <c r="O1" s="318">
         <f>SUM(B3:B33)</f>
-        <v>1.75</v>
-      </c>
-      <c r="P1" s="365" t="s">
+        <v>48.95</v>
+      </c>
+      <c r="P1" s="371" t="s">
         <v>197</v>
       </c>
-      <c r="Q1" s="365"/>
+      <c r="Q1" s="371"/>
     </row>
     <row r="2" spans="1:17" ht="16.5">
       <c r="B2" s="251">
         <f>SUM(B3:B33)</f>
-        <v>1.75</v>
+        <v>48.95</v>
       </c>
       <c r="C2" s="251">
         <f t="shared" ref="C2" si="0">SUM(C3:C33)</f>
-        <v>0.5</v>
+        <v>13.5</v>
       </c>
       <c r="D2" s="251">
         <f>SUM(D3:D33)</f>
-        <v>0.25</v>
+        <v>7.65</v>
       </c>
       <c r="E2" s="251">
         <f t="shared" ref="E2:H2" si="1">SUM(E3:E33)</f>
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="F2" s="251">
         <f>SUM(F3:F33)</f>
-        <v>0</v>
+        <v>26.25</v>
       </c>
       <c r="G2" s="251">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>64.75</v>
       </c>
       <c r="H2" s="251">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I2" s="251">
         <f>SUM(I3:I30)/60</f>
-        <v>8.3333333333333329E-2</v>
+        <v>6.0333333333333332</v>
       </c>
       <c r="J2" s="251"/>
       <c r="K2" s="240">
         <f>SUM(E2:G2)</f>
-        <v>0.25</v>
+        <v>107.5</v>
       </c>
       <c r="L2" s="298"/>
       <c r="M2" s="296" t="s">
@@ -28044,10 +28319,10 @@
       </c>
       <c r="O2" s="256">
         <f>SUM(C3:E30)</f>
-        <v>0.75</v>
-      </c>
-      <c r="P2" s="365"/>
-      <c r="Q2" s="365"/>
+        <v>37.65</v>
+      </c>
+      <c r="P2" s="371"/>
+      <c r="Q2" s="371"/>
     </row>
     <row r="3" spans="1:17" ht="16.5">
       <c r="A3" s="9">
@@ -28063,7 +28338,9 @@
         <v>0.25</v>
       </c>
       <c r="E3" s="252"/>
-      <c r="F3" s="252"/>
+      <c r="F3" s="252">
+        <v>0.5</v>
+      </c>
       <c r="G3" s="252">
         <v>0.25</v>
       </c>
@@ -28072,7 +28349,7 @@
         <v>5</v>
       </c>
       <c r="J3" s="251" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K3" s="298"/>
       <c r="L3" s="20" t="s">
@@ -28080,74 +28357,120 @@
       </c>
       <c r="M3" s="264">
         <f>SUM(M4:M28)</f>
-        <v>15.25</v>
+        <v>107.5</v>
       </c>
       <c r="N3" s="255" t="s">
         <v>16</v>
       </c>
       <c r="O3" s="255">
         <f>SUM(F3:H30)</f>
-        <v>0.25</v>
+        <v>82</v>
+      </c>
+      <c r="P3" s="296">
+        <f>SUM(P4:P32)</f>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="16.5">
       <c r="A4" s="9">
         <v>46175</v>
       </c>
-      <c r="B4" s="321"/>
-      <c r="C4" s="252"/>
+      <c r="B4" s="319">
+        <v>3.5</v>
+      </c>
+      <c r="C4" s="252">
+        <v>0.5</v>
+      </c>
       <c r="D4" s="252"/>
       <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
+      <c r="F4" s="252">
+        <v>0.75</v>
+      </c>
       <c r="G4" s="252"/>
       <c r="H4" s="252"/>
       <c r="I4" s="251"/>
       <c r="J4" s="251"/>
       <c r="K4" s="298"/>
-      <c r="L4" s="310" t="s">
-        <v>403</v>
-      </c>
-      <c r="M4" s="311"/>
+      <c r="L4" s="308" t="s">
+        <v>483</v>
+      </c>
+      <c r="M4" s="309">
+        <v>8.75</v>
+      </c>
     </row>
     <row r="5" spans="1:17" ht="16.5">
       <c r="A5" s="9">
         <v>46176</v>
       </c>
-      <c r="B5" s="321"/>
-      <c r="C5" s="252"/>
+      <c r="B5" s="319">
+        <v>4.75</v>
+      </c>
+      <c r="C5" s="252">
+        <v>1</v>
+      </c>
       <c r="D5" s="252"/>
       <c r="E5" s="252"/>
-      <c r="F5" s="252"/>
-      <c r="G5" s="252"/>
+      <c r="F5" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="252">
+        <v>0.8</v>
+      </c>
       <c r="H5" s="252"/>
-      <c r="I5" s="251"/>
-      <c r="J5" s="251"/>
-      <c r="K5" s="298"/>
-      <c r="L5" s="310" t="s">
-        <v>423</v>
-      </c>
-      <c r="M5" s="312"/>
+      <c r="I5" s="251">
+        <v>38</v>
+      </c>
+      <c r="J5" s="251" t="s">
+        <v>435</v>
+      </c>
+      <c r="K5" s="298" t="s">
+        <v>434</v>
+      </c>
+      <c r="L5" s="308" t="s">
+        <v>446</v>
+      </c>
+      <c r="M5" s="310">
+        <v>5.75</v>
+      </c>
       <c r="N5" s="296" t="s">
         <v>239</v>
+      </c>
+      <c r="P5" s="296">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="16.5">
       <c r="A6" s="9">
         <v>46177</v>
       </c>
-      <c r="B6" s="321"/>
-      <c r="C6" s="252"/>
-      <c r="D6" s="252"/>
+      <c r="B6" s="319">
+        <v>2.75</v>
+      </c>
+      <c r="C6" s="252">
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="252">
+        <v>0.4</v>
+      </c>
       <c r="E6" s="252"/>
-      <c r="F6" s="252"/>
-      <c r="G6" s="252"/>
+      <c r="F6" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="252">
+        <v>0.25</v>
+      </c>
       <c r="H6" s="252"/>
-      <c r="J6" s="251"/>
+      <c r="I6" s="326">
+        <v>38</v>
+      </c>
+      <c r="J6" s="251" t="s">
+        <v>437</v>
+      </c>
       <c r="K6" s="13"/>
-      <c r="L6" s="310" t="s">
-        <v>434</v>
-      </c>
-      <c r="M6" s="312"/>
+      <c r="L6" s="308" t="s">
+        <v>486</v>
+      </c>
+      <c r="M6" s="310"/>
       <c r="N6" s="17" t="s">
         <v>19</v>
       </c>
@@ -28159,17 +28482,34 @@
       <c r="A7" s="9">
         <v>46178</v>
       </c>
-      <c r="B7" s="321"/>
-      <c r="C7" s="252"/>
+      <c r="B7" s="319">
+        <v>3.5</v>
+      </c>
+      <c r="C7" s="252">
+        <v>0.25</v>
+      </c>
       <c r="D7" s="252"/>
       <c r="E7" s="252"/>
-      <c r="F7" s="252"/>
-      <c r="G7" s="252"/>
+      <c r="F7" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="252">
+        <v>1.2</v>
+      </c>
       <c r="H7" s="252"/>
-      <c r="I7" s="300"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="310"/>
-      <c r="M7" s="313"/>
+      <c r="I7" s="326"/>
+      <c r="J7" s="251" t="s">
+        <v>439</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="L7" s="308" t="s">
+        <v>455</v>
+      </c>
+      <c r="M7" s="311">
+        <v>0.75</v>
+      </c>
       <c r="N7" s="258" t="s">
         <v>165</v>
       </c>
@@ -28177,43 +28517,85 @@
         <v>216</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="16.5">
+    <row r="8" spans="1:17" ht="33">
       <c r="A8" s="9">
         <v>46179</v>
       </c>
-      <c r="B8" s="321"/>
-      <c r="C8" s="252"/>
-      <c r="D8" s="252"/>
-      <c r="E8" s="252"/>
-      <c r="F8" s="252"/>
-      <c r="G8" s="252"/>
+      <c r="B8" s="319">
+        <v>3.2</v>
+      </c>
+      <c r="C8" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="252">
+        <v>2</v>
+      </c>
+      <c r="G8" s="252">
+        <v>7</v>
+      </c>
       <c r="H8" s="252"/>
-      <c r="I8" s="300"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="309"/>
-      <c r="M8" s="314"/>
+      <c r="I8" s="251">
+        <v>23</v>
+      </c>
+      <c r="J8" s="251" t="s">
+        <v>442</v>
+      </c>
+      <c r="K8" s="321" t="s">
+        <v>441</v>
+      </c>
+      <c r="L8" s="308" t="s">
+        <v>487</v>
+      </c>
+      <c r="M8" s="312">
+        <v>2.5</v>
+      </c>
       <c r="N8" s="259" t="s">
         <v>168</v>
       </c>
       <c r="O8" s="35" t="s">
         <v>89</v>
+      </c>
+      <c r="P8" s="296">
+        <v>-6</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="16.5">
       <c r="A9" s="9">
         <v>46180</v>
       </c>
-      <c r="B9" s="321"/>
-      <c r="C9" s="252"/>
-      <c r="D9" s="252"/>
-      <c r="E9" s="252"/>
+      <c r="B9" s="319">
+        <v>1</v>
+      </c>
+      <c r="C9" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="252">
+        <v>1</v>
+      </c>
+      <c r="E9" s="252">
+        <v>3.25</v>
+      </c>
       <c r="F9" s="252"/>
-      <c r="G9" s="252"/>
+      <c r="G9" s="252">
+        <v>4</v>
+      </c>
       <c r="H9" s="252"/>
-      <c r="I9" s="300"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="310"/>
-      <c r="M9" s="311"/>
+      <c r="I9" s="326"/>
+      <c r="K9" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="L9" s="308" t="s">
+        <v>491</v>
+      </c>
+      <c r="M9" s="309">
+        <v>14</v>
+      </c>
       <c r="N9" s="296" t="s">
         <v>169</v>
       </c>
@@ -28225,19 +28607,36 @@
       <c r="A10" s="9">
         <v>46181</v>
       </c>
-      <c r="B10" s="321"/>
-      <c r="C10" s="252"/>
+      <c r="B10" s="319">
+        <v>4.5</v>
+      </c>
+      <c r="C10" s="252">
+        <v>0.5</v>
+      </c>
       <c r="D10" s="252"/>
-      <c r="E10" s="252"/>
+      <c r="E10" s="252">
+        <v>2</v>
+      </c>
       <c r="F10" s="252"/>
-      <c r="G10" s="252"/>
+      <c r="G10" s="252">
+        <v>2.25</v>
+      </c>
       <c r="H10" s="252"/>
-      <c r="I10" s="300"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="310" t="s">
-        <v>369</v>
-      </c>
-      <c r="M10" s="312"/>
+      <c r="I10" s="326">
+        <v>36</v>
+      </c>
+      <c r="J10" s="251" t="s">
+        <v>448</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="L10" s="308" t="s">
+        <v>367</v>
+      </c>
+      <c r="M10" s="310">
+        <v>1</v>
+      </c>
       <c r="N10" s="260" t="s">
         <v>170</v>
       </c>
@@ -28249,18 +28648,34 @@
       <c r="A11" s="9">
         <v>46182</v>
       </c>
-      <c r="B11" s="321"/>
-      <c r="C11" s="252"/>
+      <c r="B11" s="319">
+        <v>3</v>
+      </c>
+      <c r="C11" s="252">
+        <v>1</v>
+      </c>
       <c r="D11" s="252"/>
       <c r="E11" s="252"/>
       <c r="F11" s="252"/>
       <c r="G11" s="252"/>
-      <c r="H11" s="252"/>
-      <c r="I11" s="300"/>
-      <c r="L11" s="310" t="s">
-        <v>438</v>
-      </c>
-      <c r="M11" s="312"/>
+      <c r="H11" s="252">
+        <v>1</v>
+      </c>
+      <c r="I11" s="326">
+        <v>25</v>
+      </c>
+      <c r="J11" s="251" t="s">
+        <v>450</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="L11" s="308" t="s">
+        <v>480</v>
+      </c>
+      <c r="M11" s="310">
+        <v>1</v>
+      </c>
       <c r="N11" s="259" t="s">
         <v>167</v>
       </c>
@@ -28272,16 +28687,26 @@
       <c r="A12" s="9">
         <v>46183</v>
       </c>
-      <c r="B12" s="321"/>
+      <c r="B12" s="319">
+        <v>1.5</v>
+      </c>
       <c r="C12" s="252"/>
       <c r="D12" s="252"/>
       <c r="E12" s="252"/>
       <c r="F12" s="252"/>
-      <c r="G12" s="252"/>
-      <c r="H12" s="252"/>
-      <c r="I12" s="300"/>
-      <c r="L12" s="310"/>
-      <c r="M12" s="312"/>
+      <c r="G12" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="252">
+        <v>1</v>
+      </c>
+      <c r="I12" s="326"/>
+      <c r="L12" s="308" t="s">
+        <v>460</v>
+      </c>
+      <c r="M12" s="310">
+        <v>1.5</v>
+      </c>
       <c r="N12" s="296" t="s">
         <v>173</v>
       </c>
@@ -28289,46 +28714,81 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="16.5">
+    <row r="13" spans="1:17" ht="33">
       <c r="A13" s="9">
         <v>46184</v>
       </c>
-      <c r="B13" s="321"/>
-      <c r="C13" s="252"/>
-      <c r="D13" s="252"/>
-      <c r="E13" s="252"/>
+      <c r="B13" s="319">
+        <v>3</v>
+      </c>
+      <c r="C13" s="252">
+        <v>0.25</v>
+      </c>
+      <c r="D13" s="252">
+        <v>0.25</v>
+      </c>
+      <c r="E13" s="252">
+        <v>0.25</v>
+      </c>
       <c r="F13" s="252"/>
-      <c r="G13" s="252"/>
+      <c r="G13" s="252">
+        <v>3</v>
+      </c>
       <c r="H13" s="252"/>
-      <c r="I13" s="300"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="310" t="s">
-        <v>435</v>
-      </c>
-      <c r="M13" s="312"/>
+      <c r="I13" s="326">
+        <v>30</v>
+      </c>
+      <c r="J13" s="251" t="s">
+        <v>452</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="L13" s="308" t="s">
+        <v>476</v>
+      </c>
+      <c r="M13" s="310">
+        <v>3.25</v>
+      </c>
       <c r="N13" s="259" t="s">
         <v>177</v>
       </c>
       <c r="O13" s="44" t="s">
         <v>176</v>
+      </c>
+      <c r="P13" s="296">
+        <v>1.25</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="34.5" customHeight="1">
       <c r="A14" s="9">
         <v>46185</v>
       </c>
-      <c r="B14" s="321"/>
+      <c r="B14" s="319">
+        <v>0.25</v>
+      </c>
       <c r="C14" s="252"/>
-      <c r="D14" s="252"/>
-      <c r="E14" s="252"/>
+      <c r="D14" s="252">
+        <v>2.75</v>
+      </c>
+      <c r="E14" s="252">
+        <v>0.5</v>
+      </c>
       <c r="F14" s="252"/>
-      <c r="G14" s="252"/>
+      <c r="G14" s="252">
+        <v>0.5</v>
+      </c>
       <c r="H14" s="252"/>
-      <c r="I14" s="300"/>
-      <c r="L14" s="310" t="s">
-        <v>436</v>
-      </c>
-      <c r="M14" s="315"/>
+      <c r="I14" s="324"/>
+      <c r="K14" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="L14" s="308" t="s">
+        <v>479</v>
+      </c>
+      <c r="M14" s="313">
+        <v>8.5</v>
+      </c>
       <c r="N14" s="39" t="s">
         <v>174</v>
       </c>
@@ -28340,18 +28800,38 @@
       <c r="A15" s="9">
         <v>46186</v>
       </c>
-      <c r="B15" s="321"/>
-      <c r="C15" s="252"/>
+      <c r="B15" s="319">
+        <v>1.25</v>
+      </c>
+      <c r="C15" s="252">
+        <v>5.5</v>
+      </c>
       <c r="D15" s="252"/>
-      <c r="E15" s="252"/>
-      <c r="F15" s="252"/>
-      <c r="G15" s="252"/>
+      <c r="E15" s="252">
+        <v>3.5</v>
+      </c>
+      <c r="F15" s="252">
+        <v>1</v>
+      </c>
+      <c r="G15" s="252">
+        <v>1.75</v>
+      </c>
       <c r="H15" s="252"/>
-      <c r="I15" s="300"/>
-      <c r="L15" s="310" t="s">
-        <v>238</v>
-      </c>
-      <c r="M15" s="316"/>
+      <c r="I15" s="326">
+        <v>15</v>
+      </c>
+      <c r="J15" s="251" t="s">
+        <v>454</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="L15" s="308" t="s">
+        <v>471</v>
+      </c>
+      <c r="M15" s="314">
+        <v>10</v>
+      </c>
       <c r="N15" s="261" t="s">
         <v>69</v>
       </c>
@@ -28363,18 +28843,42 @@
       <c r="A16" s="9">
         <v>46187</v>
       </c>
-      <c r="B16" s="321"/>
-      <c r="C16" s="252"/>
-      <c r="D16" s="252"/>
-      <c r="E16" s="252"/>
-      <c r="F16" s="252"/>
-      <c r="G16" s="252"/>
-      <c r="H16" s="252"/>
-      <c r="I16" s="300"/>
-      <c r="L16" s="310" t="s">
-        <v>437</v>
-      </c>
-      <c r="M16" s="312"/>
+      <c r="B16" s="319">
+        <v>4.75</v>
+      </c>
+      <c r="C16" s="252">
+        <v>0.75</v>
+      </c>
+      <c r="D16" s="252">
+        <v>0.75</v>
+      </c>
+      <c r="E16" s="252">
+        <v>0.25</v>
+      </c>
+      <c r="F16" s="252">
+        <v>1.25</v>
+      </c>
+      <c r="G16" s="252">
+        <v>2</v>
+      </c>
+      <c r="H16" s="252">
+        <v>1</v>
+      </c>
+      <c r="I16" s="326">
+        <v>29</v>
+      </c>
+      <c r="J16" s="222" t="s">
+        <v>458</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>456</v>
+      </c>
+      <c r="L16" s="308" t="s">
+        <v>474</v>
+      </c>
+      <c r="M16" s="310">
+        <v>2.25</v>
+      </c>
       <c r="N16" s="261" t="s">
         <v>178</v>
       </c>
@@ -28386,19 +28890,41 @@
       <c r="A17" s="9">
         <v>46188</v>
       </c>
-      <c r="B17" s="321"/>
-      <c r="C17" s="252"/>
-      <c r="D17" s="252"/>
-      <c r="E17" s="252"/>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="300"/>
-      <c r="L17" s="310" t="s">
+      <c r="B17" s="319">
+        <v>3</v>
+      </c>
+      <c r="C17" s="252">
+        <v>0.25</v>
+      </c>
+      <c r="D17" s="252">
+        <v>1</v>
+      </c>
+      <c r="E17" s="252">
+        <v>0.75</v>
+      </c>
+      <c r="F17" s="252">
+        <v>0.75</v>
+      </c>
+      <c r="G17" s="252">
+        <v>1.5</v>
+      </c>
+      <c r="H17" s="252">
+        <v>3</v>
+      </c>
+      <c r="I17" s="326">
+        <v>38</v>
+      </c>
+      <c r="J17" s="222" t="s">
+        <v>463</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="L17" s="308" t="s">
         <v>132</v>
       </c>
-      <c r="M17" s="312">
-        <v>0.25</v>
+      <c r="M17" s="310">
+        <v>1</v>
       </c>
       <c r="N17" s="261" t="s">
         <v>179</v>
@@ -28406,23 +28932,33 @@
       <c r="O17" s="36" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="16.5">
+      <c r="P17" s="296">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="33">
       <c r="A18" s="9">
         <v>46189</v>
       </c>
-      <c r="B18" s="321"/>
+      <c r="B18" s="319"/>
       <c r="C18" s="252"/>
       <c r="D18" s="252"/>
       <c r="E18" s="252"/>
       <c r="F18" s="252"/>
-      <c r="G18" s="252"/>
+      <c r="G18" s="252">
+        <v>5</v>
+      </c>
       <c r="H18" s="252"/>
-      <c r="I18" s="300"/>
-      <c r="L18" s="310" t="s">
-        <v>429</v>
-      </c>
-      <c r="M18" s="312"/>
+      <c r="I18" s="326"/>
+      <c r="K18" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="L18" s="308" t="s">
+        <v>484</v>
+      </c>
+      <c r="M18" s="310">
+        <v>15.5</v>
+      </c>
       <c r="N18" s="296" t="s">
         <v>110</v>
       </c>
@@ -28431,16 +28967,25 @@
       <c r="A19" s="9">
         <v>46190</v>
       </c>
-      <c r="B19" s="321"/>
+      <c r="B19" s="319"/>
       <c r="C19" s="252"/>
       <c r="D19" s="252"/>
       <c r="E19" s="252"/>
       <c r="F19" s="252"/>
-      <c r="G19" s="252"/>
+      <c r="G19" s="252">
+        <v>5</v>
+      </c>
       <c r="H19" s="252"/>
-      <c r="I19" s="300"/>
-      <c r="L19" s="310"/>
-      <c r="M19" s="313"/>
+      <c r="I19" s="326"/>
+      <c r="K19" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="L19" s="308" t="s">
+        <v>477</v>
+      </c>
+      <c r="M19" s="311">
+        <v>1</v>
+      </c>
       <c r="N19" s="262"/>
       <c r="P19" s="297"/>
     </row>
@@ -28448,16 +28993,25 @@
       <c r="A20" s="9">
         <v>46191</v>
       </c>
-      <c r="B20" s="321"/>
+      <c r="B20" s="319"/>
       <c r="C20" s="252"/>
       <c r="D20" s="252"/>
       <c r="E20" s="252"/>
       <c r="F20" s="252"/>
-      <c r="G20" s="252"/>
+      <c r="G20" s="252">
+        <v>4</v>
+      </c>
       <c r="H20" s="252"/>
-      <c r="I20" s="300"/>
-      <c r="L20" s="310"/>
-      <c r="M20" s="317"/>
+      <c r="I20" s="326"/>
+      <c r="K20" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="L20" s="308" t="s">
+        <v>440</v>
+      </c>
+      <c r="M20" s="315">
+        <v>7</v>
+      </c>
       <c r="N20" s="263" t="s">
         <v>53</v>
       </c>
@@ -28470,16 +29024,33 @@
       <c r="A21" s="9">
         <v>46192</v>
       </c>
-      <c r="B21" s="321"/>
-      <c r="C21" s="252"/>
-      <c r="D21" s="252"/>
+      <c r="B21" s="319">
+        <v>0.75</v>
+      </c>
+      <c r="C21" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="252">
+        <v>0.25</v>
+      </c>
       <c r="E21" s="252"/>
-      <c r="F21" s="252"/>
-      <c r="G21" s="252"/>
+      <c r="F21" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="252">
+        <v>7.75</v>
+      </c>
       <c r="H21" s="252"/>
-      <c r="I21" s="300"/>
-      <c r="L21" s="310"/>
-      <c r="M21" s="316"/>
+      <c r="I21" s="326"/>
+      <c r="K21" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="L21" s="308" t="s">
+        <v>457</v>
+      </c>
+      <c r="M21" s="314">
+        <v>2.25</v>
+      </c>
       <c r="N21" s="263" t="s">
         <v>54</v>
       </c>
@@ -28492,16 +29063,36 @@
       <c r="A22" s="9">
         <v>46193</v>
       </c>
-      <c r="B22" s="321"/>
+      <c r="B22" s="319">
+        <v>5.25</v>
+      </c>
       <c r="C22" s="252"/>
       <c r="D22" s="252"/>
-      <c r="E22" s="252"/>
-      <c r="F22" s="252"/>
-      <c r="G22" s="252"/>
+      <c r="E22" s="252">
+        <v>2.5</v>
+      </c>
+      <c r="F22" s="252">
+        <v>1</v>
+      </c>
+      <c r="G22" s="252">
+        <v>2.5</v>
+      </c>
       <c r="H22" s="252"/>
-      <c r="I22" s="300"/>
-      <c r="L22" s="310"/>
-      <c r="M22" s="318"/>
+      <c r="I22" s="326">
+        <v>57</v>
+      </c>
+      <c r="J22" s="222" t="s">
+        <v>488</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="L22" s="308" t="s">
+        <v>445</v>
+      </c>
+      <c r="M22" s="316">
+        <v>3</v>
+      </c>
       <c r="N22" s="263" t="s">
         <v>78</v>
       </c>
@@ -28514,17 +29105,33 @@
       <c r="A23" s="9">
         <v>46194</v>
       </c>
-      <c r="B23" s="321"/>
-      <c r="C23" s="252"/>
-      <c r="D23" s="252"/>
-      <c r="E23" s="252"/>
-      <c r="F23" s="252"/>
-      <c r="G23" s="252"/>
+      <c r="B23" s="319"/>
+      <c r="C23" s="252">
+        <v>1</v>
+      </c>
+      <c r="D23" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="252">
+        <v>2.5</v>
+      </c>
+      <c r="F23" s="252">
+        <v>0.75</v>
+      </c>
+      <c r="G23" s="252">
+        <v>7</v>
+      </c>
       <c r="H23" s="252"/>
-      <c r="I23" s="300"/>
-      <c r="K23" s="307"/>
-      <c r="L23" s="310"/>
-      <c r="M23" s="319"/>
+      <c r="I23" s="326"/>
+      <c r="K23" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="L23" s="308" t="s">
+        <v>151</v>
+      </c>
+      <c r="M23" s="317">
+        <v>1</v>
+      </c>
       <c r="N23" s="165" t="s">
         <v>55</v>
       </c>
@@ -28537,18 +29144,28 @@
       <c r="A24" s="9">
         <v>46195</v>
       </c>
-      <c r="B24" s="321"/>
+      <c r="B24" s="319"/>
       <c r="C24" s="252"/>
       <c r="D24" s="252"/>
       <c r="E24" s="252"/>
-      <c r="F24" s="252"/>
-      <c r="G24" s="252"/>
+      <c r="F24" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="252">
+        <v>3.5</v>
+      </c>
       <c r="H24" s="252"/>
       <c r="I24" s="251"/>
       <c r="J24" s="251"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="310"/>
-      <c r="M24" s="315"/>
+      <c r="K24" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="L24" s="308" t="s">
+        <v>451</v>
+      </c>
+      <c r="M24" s="313">
+        <v>2.5</v>
+      </c>
       <c r="N24" s="165" t="s">
         <v>56</v>
       </c>
@@ -28560,20 +29177,32 @@
       <c r="A25" s="9">
         <v>46196</v>
       </c>
-      <c r="B25" s="321"/>
+      <c r="B25" s="319">
+        <v>1.25</v>
+      </c>
       <c r="C25" s="252"/>
       <c r="D25" s="252"/>
-      <c r="E25" s="252"/>
-      <c r="F25" s="252"/>
-      <c r="G25" s="252"/>
+      <c r="E25" s="252">
+        <v>0.5</v>
+      </c>
+      <c r="F25" s="252">
+        <v>0.75</v>
+      </c>
+      <c r="G25" s="252">
+        <v>1</v>
+      </c>
       <c r="H25" s="252"/>
-      <c r="I25" s="251"/>
-      <c r="J25" s="222"/>
-      <c r="K25" s="298"/>
-      <c r="L25" s="310" t="s">
-        <v>193</v>
-      </c>
-      <c r="M25" s="319">
+      <c r="I25" s="251">
+        <v>28</v>
+      </c>
+      <c r="J25" s="222" t="s">
+        <v>482</v>
+      </c>
+      <c r="K25" s="298" t="s">
+        <v>481</v>
+      </c>
+      <c r="L25" s="308"/>
+      <c r="M25" s="317">
         <v>15</v>
       </c>
       <c r="N25" s="165" t="s">
@@ -28587,17 +29216,25 @@
       <c r="A26" s="9">
         <v>46197</v>
       </c>
-      <c r="B26" s="321"/>
+      <c r="B26" s="319">
+        <v>0</v>
+      </c>
       <c r="C26" s="252"/>
       <c r="D26" s="252"/>
       <c r="E26" s="252"/>
       <c r="F26" s="252"/>
-      <c r="G26" s="252"/>
+      <c r="G26" s="252">
+        <v>4</v>
+      </c>
       <c r="H26" s="252"/>
       <c r="I26" s="251"/>
       <c r="J26" s="251"/>
-      <c r="K26" s="298"/>
-      <c r="L26" s="21"/>
+      <c r="K26" s="298" t="s">
+        <v>490</v>
+      </c>
+      <c r="L26" s="308" t="s">
+        <v>193</v>
+      </c>
       <c r="M26" s="11"/>
       <c r="N26" s="167"/>
       <c r="O26" s="167"/>
@@ -28606,16 +29243,18 @@
       <c r="A27" s="9">
         <v>46198</v>
       </c>
-      <c r="B27" s="321"/>
-      <c r="C27" s="252"/>
+      <c r="B27" s="319"/>
+      <c r="C27" s="252">
+        <v>0.25</v>
+      </c>
       <c r="D27" s="252"/>
       <c r="E27" s="252"/>
       <c r="F27" s="252"/>
       <c r="G27" s="252"/>
       <c r="H27" s="252"/>
-      <c r="I27" s="300"/>
+      <c r="I27" s="326"/>
       <c r="K27" s="298"/>
-      <c r="L27" s="10"/>
+      <c r="L27" s="21"/>
       <c r="M27" s="11"/>
       <c r="N27" s="167" t="s">
         <v>80</v>
@@ -28628,7 +29267,7 @@
       <c r="A28" s="9">
         <v>46199</v>
       </c>
-      <c r="B28" s="321"/>
+      <c r="B28" s="319"/>
       <c r="C28" s="252"/>
       <c r="D28" s="252"/>
       <c r="E28" s="252"/>
@@ -28638,13 +29277,13 @@
       <c r="I28" s="251"/>
       <c r="J28" s="251"/>
       <c r="K28" s="298"/>
-      <c r="L28" s="18"/>
+      <c r="L28" s="10"/>
     </row>
     <row r="29" spans="1:16" ht="16.5">
       <c r="A29" s="9">
         <v>46200</v>
       </c>
-      <c r="B29" s="321"/>
+      <c r="B29" s="319"/>
       <c r="C29" s="252"/>
       <c r="D29" s="252"/>
       <c r="E29" s="252"/>
@@ -28654,13 +29293,13 @@
       <c r="I29" s="251"/>
       <c r="J29" s="251"/>
       <c r="K29" s="13"/>
-      <c r="L29" s="298"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" spans="1:16" ht="16.5">
       <c r="A30" s="9">
         <v>46201</v>
       </c>
-      <c r="B30" s="321"/>
+      <c r="B30" s="319"/>
       <c r="C30" s="252"/>
       <c r="D30" s="252"/>
       <c r="E30" s="252"/>
@@ -28671,15 +29310,15 @@
       <c r="J30" s="251"/>
       <c r="K30" s="298"/>
       <c r="L30" s="298"/>
-      <c r="M30" s="302"/>
-      <c r="N30" s="302"/>
-      <c r="O30" s="302"/>
+      <c r="M30" s="301"/>
+      <c r="N30" s="301"/>
+      <c r="O30" s="301"/>
     </row>
     <row r="31" spans="1:16" ht="16.5">
       <c r="A31" s="9">
         <v>46202</v>
       </c>
-      <c r="B31" s="321"/>
+      <c r="B31" s="319"/>
       <c r="C31" s="252"/>
       <c r="D31" s="252"/>
       <c r="E31" s="252"/>
@@ -28689,7 +29328,7 @@
       <c r="I31" s="251"/>
       <c r="J31" s="251"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="302"/>
+      <c r="L31" s="298"/>
       <c r="M31" s="298"/>
       <c r="N31" s="298"/>
       <c r="O31" s="298"/>
@@ -28708,26 +29347,28 @@
       <c r="I32" s="251"/>
       <c r="J32" s="251"/>
       <c r="K32" s="5"/>
-      <c r="L32" s="298"/>
+      <c r="L32" s="301"/>
       <c r="M32" s="298"/>
       <c r="N32" s="298"/>
       <c r="O32" s="298"/>
     </row>
     <row r="33" spans="1:15" ht="16.5">
       <c r="A33" s="9"/>
-      <c r="B33" s="304"/>
+      <c r="B33" s="303"/>
       <c r="C33" s="298"/>
       <c r="D33" s="298"/>
       <c r="E33" s="298"/>
-      <c r="F33" s="298"/>
+      <c r="F33" s="298">
+        <v>15</v>
+      </c>
       <c r="G33" s="298"/>
       <c r="H33" s="298"/>
       <c r="I33" s="251"/>
-      <c r="J33" s="298"/>
+      <c r="J33" s="251"/>
       <c r="L33" s="298"/>
-      <c r="M33" s="302"/>
-      <c r="N33" s="302"/>
-      <c r="O33" s="302"/>
+      <c r="M33" s="301"/>
+      <c r="N33" s="301"/>
+      <c r="O33" s="301"/>
     </row>
     <row r="34" spans="1:15" ht="16.5">
       <c r="A34" s="298" t="s">
@@ -28739,18 +29380,18 @@
       <c r="C34" s="298"/>
       <c r="D34" s="298"/>
       <c r="E34" s="298" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F34" s="298"/>
       <c r="G34" s="298"/>
       <c r="H34" s="298"/>
-      <c r="I34" s="298"/>
-      <c r="J34" s="298"/>
+      <c r="I34" s="323"/>
+      <c r="J34" s="251"/>
       <c r="K34" s="298"/>
-      <c r="L34" s="302"/>
-      <c r="M34" s="302"/>
-      <c r="N34" s="302"/>
-      <c r="O34" s="302"/>
+      <c r="L34" s="298"/>
+      <c r="M34" s="301"/>
+      <c r="N34" s="301"/>
+      <c r="O34" s="301"/>
     </row>
     <row r="35" spans="1:15" ht="16.5">
       <c r="A35" s="298"/>
@@ -28761,10 +29402,10 @@
       <c r="F35" s="298"/>
       <c r="G35" s="298"/>
       <c r="H35" s="298"/>
-      <c r="I35" s="298"/>
-      <c r="J35" s="298"/>
+      <c r="I35" s="323"/>
+      <c r="J35" s="251"/>
       <c r="K35" s="298"/>
-      <c r="L35" s="302"/>
+      <c r="L35" s="301"/>
     </row>
     <row r="36" spans="1:15" ht="16.5">
       <c r="A36" s="298"/>
@@ -28775,13 +29416,16 @@
       <c r="F36" s="298"/>
       <c r="G36" s="298"/>
       <c r="H36" s="298"/>
-      <c r="I36" s="298"/>
-      <c r="J36" s="298"/>
+      <c r="I36" s="323"/>
+      <c r="J36" s="251"/>
       <c r="K36" s="298"/>
-      <c r="L36" s="298"/>
+      <c r="L36" s="301"/>
     </row>
     <row r="37" spans="1:15" ht="16.5">
       <c r="L37" s="298"/>
+    </row>
+    <row r="38" spans="1:15" ht="16.5">
+      <c r="L38" s="298"/>
     </row>
     <row r="53" spans="4:8">
       <c r="D53" s="296" t="s">
@@ -28832,7 +29476,7 @@
       <formula>WEEKDAY(A3,2)&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:J6 I3 J9:J11 J13:J26 I30:J32 J28:J29">
+  <conditionalFormatting sqref="I4:J6 I3 J13:J26 I30:J32 J28:J29 J7:J11">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="15"/>
@@ -29234,10 +29878,10 @@
       <c r="I16" s="40"/>
       <c r="J16" s="137"/>
       <c r="K16" s="130"/>
-      <c r="L16" s="367" t="s">
+      <c r="L16" s="373" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="368"/>
+      <c r="M16" s="374"/>
     </row>
     <row r="17" spans="1:14" ht="16.5">
       <c r="A17" s="41">
@@ -29451,13 +30095,13 @@
       <c r="G28" s="110"/>
       <c r="H28" s="147"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="369" t="s">
+      <c r="J28" s="375" t="s">
         <v>76</v>
       </c>
-      <c r="K28" s="369"/>
-      <c r="L28" s="369"/>
-      <c r="M28" s="369"/>
-      <c r="N28" s="369"/>
+      <c r="K28" s="375"/>
+      <c r="L28" s="375"/>
+      <c r="M28" s="375"/>
+      <c r="N28" s="375"/>
     </row>
     <row r="29" spans="1:14" ht="27" customHeight="1">
       <c r="A29" s="41">
@@ -29471,11 +30115,11 @@
       <c r="G29" s="110"/>
       <c r="H29" s="147"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="369"/>
-      <c r="K29" s="369"/>
-      <c r="L29" s="369"/>
-      <c r="M29" s="369"/>
-      <c r="N29" s="369"/>
+      <c r="J29" s="375"/>
+      <c r="K29" s="375"/>
+      <c r="L29" s="375"/>
+      <c r="M29" s="375"/>
+      <c r="N29" s="375"/>
     </row>
     <row r="30" spans="1:14" ht="31.5" customHeight="1">
       <c r="A30" s="41">
@@ -30027,10 +30671,10 @@
       <c r="I16" s="40"/>
       <c r="J16" s="148"/>
       <c r="K16" s="149"/>
-      <c r="L16" s="367" t="s">
+      <c r="L16" s="373" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="368"/>
+      <c r="M16" s="374"/>
     </row>
     <row r="17" spans="1:14" ht="16.5">
       <c r="A17" s="41">
@@ -30244,11 +30888,11 @@
       <c r="G28" s="110"/>
       <c r="H28" s="163"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="369"/>
-      <c r="K28" s="369"/>
-      <c r="L28" s="369"/>
-      <c r="M28" s="369"/>
-      <c r="N28" s="369"/>
+      <c r="J28" s="375"/>
+      <c r="K28" s="375"/>
+      <c r="L28" s="375"/>
+      <c r="M28" s="375"/>
+      <c r="N28" s="375"/>
     </row>
     <row r="29" spans="1:14" ht="22.5" customHeight="1">
       <c r="A29" s="41">
@@ -30262,11 +30906,11 @@
       <c r="G29" s="110"/>
       <c r="H29" s="163"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="369"/>
-      <c r="K29" s="369"/>
-      <c r="L29" s="369"/>
-      <c r="M29" s="369"/>
-      <c r="N29" s="369"/>
+      <c r="J29" s="375"/>
+      <c r="K29" s="375"/>
+      <c r="L29" s="375"/>
+      <c r="M29" s="375"/>
+      <c r="N29" s="375"/>
     </row>
     <row r="30" spans="1:14" ht="21.75" customHeight="1">
       <c r="A30" s="41">
